--- a/legacy/vivarium_gates_lsff_by_wealth_quintile/0100_data_prep/extraction/Data Extraction Sheet.xlsx
+++ b/legacy/vivarium_gates_lsff_by_wealth_quintile/0100_data_prep/extraction/Data Extraction Sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27923"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwnetid.sharepoint.com/sites/ihme_simulation_science_team/Shared Documents/Research/LSFF/04_Concept_Model_Development/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF2AFBC8-FBF7-4A84-8B4F-DA796B09EEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F747A906-2511-4A82-8D98-7291795813F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="10" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Country-Vehicle Progress" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="214">
   <si>
     <t>Country</t>
   </si>
@@ -103,6 +103,9 @@
     <t>Vehicle "fortifiability" (essentially amount industrially produced)</t>
   </si>
   <si>
+    <t>Sex</t>
+  </si>
+  <si>
     <t>Data point name</t>
   </si>
   <si>
@@ -127,7 +130,10 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>All</t>
+    <t>All (assumed same)</t>
+  </si>
+  <si>
+    <t>Female</t>
   </si>
   <si>
     <t>percentage</t>
@@ -139,15 +145,24 @@
     <t>EPHI data sent by Andy Garcia</t>
   </si>
   <si>
-    <t>Total population (?), not WRA specifically</t>
+    <t>Total population (?), not WRA specifically; Not stratified by wealth quintile</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>g/day</t>
+  </si>
+  <si>
+    <t>2022 National Nutrition Survey; Total population (?), not WRA specifically</t>
   </si>
   <si>
     <t>Lowest</t>
   </si>
   <si>
-    <t>Not stratified by wealth quintile</t>
-  </si>
-  <si>
     <t>Second</t>
   </si>
   <si>
@@ -160,15 +175,6 @@
     <t>Highest</t>
   </si>
   <si>
-    <t>mean</t>
-  </si>
-  <si>
-    <t>g/day</t>
-  </si>
-  <si>
-    <t>2022 National Nutrition Survey; Total population (?), not WRA specifically</t>
-  </si>
-  <si>
     <t>standard deviation</t>
   </si>
   <si>
@@ -178,18 +184,15 @@
     <t>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC10195378/; among all adults</t>
   </si>
   <si>
+    <t>Total population (?), not U5 specifically</t>
+  </si>
+  <si>
+    <t>2022 National Nutrition Survey; Total population (?), not U5 specifically</t>
+  </si>
+  <si>
     <t>Assumption</t>
   </si>
   <si>
-    <t>Assumed same by quintile</t>
-  </si>
-  <si>
-    <t>Total population (?), not U5 specifically</t>
-  </si>
-  <si>
-    <t>2022 National Nutrition Survey; Total population (?), not U5 specifically</t>
-  </si>
-  <si>
     <t>"Almost all households in Ethiopia have access to iodized salt." ~ National Food and Nutrition Strategy Baseline Survey</t>
   </si>
   <si>
@@ -274,6 +277,18 @@
     <t>Table 171, page 223</t>
   </si>
   <si>
+    <t>[3.8, 4.4]</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>[4.0, 4.6]</t>
+  </si>
+  <si>
+    <t>Very rough estimate using SD = IQR / 1.35 (normality assumption), IQR reported in table 171</t>
+  </si>
+  <si>
     <t>Table 169, page 220 'Percentage of Non-Pregnant Women Whose Households Consumed Bouillon (purchased, branded, and labelled as fortified) by Residence, Zone, and Wealth Quintile', using 'branded' as a proxy for fortifiable and % of households as a proxy for % of product. Values obtained by dividing percent consuming branded food by percent consuming food, which is why we don't have uncertainty. A similar thing is reported in Annex 43, page 549; 'How household obtained bouillon the last time it was obtained': 'purchased', and not by wealth quintile</t>
   </si>
   <si>
@@ -316,10 +331,7 @@
     <t>Assumption: labeled as fortified = fortified (basically true for salt). Divided "consumed food labeled as fortified" by "consumed food".</t>
   </si>
   <si>
-    <t>Maggi cubes (most popular brand and format) have 15% NRV per serving (https://www.nestle-cwa.com/en/ask-nestle/products-brands/what-is-in-the-maggi-cube)</t>
-  </si>
-  <si>
-    <t>Assumed no disparity</t>
+    <t>Maggi cubes (most popular brand and format) claim to have 15% NRV per serving (https://www.nestle-cwa.com/en/ask-nestle/products-brands/what-is-in-the-maggi-cube), but according to Jonathan Gorstein email on July 27th it is actually 12%</t>
   </si>
   <si>
     <t>There is some information on fraction labeled as fortified in NFCMS Table 169, but it Figure 71 shows that 95% of WRA have RBC folate insufficiency. Also: '61 percent of the non-pregnant women from households consumed bouillons that are labelled as fortified with iodine and/or iron.' There is some evidence that the rich have more bouillon labeled as fortified (Table 169).</t>
@@ -333,9 +345,6 @@
     <t>Originally in mg/100g; https://www.wolframalpha.com/input?i=4.25+mg+per+100+grams+in+micrograms+per+gram</t>
   </si>
   <si>
-    <t>assumed same by quintile?</t>
-  </si>
-  <si>
     <t>Originally in mcg/100g; https://www.wolframalpha.com/input?i=4.25+mg+per+100+grams+in+micrograms+per+gram</t>
   </si>
   <si>
@@ -397,6 +406,9 @@
   </si>
   <si>
     <t>Neural tube defect deaths</t>
+  </si>
+  <si>
+    <t>All</t>
   </si>
   <si>
     <t xml:space="preserve">Serum folate levels at baseline </t>
@@ -531,7 +543,7 @@
     <t>https://www.sciencedirect.com/science/article/pii/S0002916523028915; could not find anything bouillon-specific</t>
   </si>
   <si>
-    <t>g/(mg/person-day)</t>
+    <t>g/(mcg/person-day)</t>
   </si>
   <si>
     <t>Anaemia, prenatal iron use, and risk of adverse pregnancy outcomes: systematic review and meta-analysis</t>
@@ -1457,19 +1469,19 @@
         <v>12</v>
       </c>
       <c r="B5" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "All",  'Country-Vehicle Extraction'!$D$2:$D$1024, $A5, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A5, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Missing</v>
+      </c>
+      <c r="C5" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!E$2:E$1003, $A5, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
-      <c r="C5" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "&lt;&gt;All",  'Country-Vehicle Extraction'!D$2:D$1024, $A5, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Complete</v>
-      </c>
       <c r="D5" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "All",  'Country-Vehicle Extraction'!$D$2:$D$1024, $A5, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Complete</v>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A5, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Missing</v>
       </c>
       <c r="E5" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "&lt;&gt;All",  'Country-Vehicle Extraction'!$D$2:$D$1024, $A5, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A5, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="F5" t="s">
@@ -1484,19 +1496,19 @@
         <v>14</v>
       </c>
       <c r="B6" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "All",  'Country-Vehicle Extraction'!$D$2:$D$1024, $A6, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A6, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Missing</v>
+      </c>
+      <c r="C6" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!E$2:E$1003, $A6, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
-      <c r="C6" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "&lt;&gt;All",  'Country-Vehicle Extraction'!D$2:D$1024, $A6, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Complete</v>
-      </c>
       <c r="D6" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "All",  'Country-Vehicle Extraction'!$D$2:$D$1024, $A6, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Complete</v>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A6, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Missing</v>
       </c>
       <c r="E6" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "&lt;&gt;All",  'Country-Vehicle Extraction'!$D$2:$D$1024, $A6, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A6, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="F6" t="s">
@@ -1511,19 +1523,19 @@
         <v>15</v>
       </c>
       <c r="B7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "All",  'Country-Vehicle Extraction'!$D$2:$D$1024, $A7, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A7, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Missing</v>
+      </c>
+      <c r="C7" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!E$2:E$1003, $A7, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
-      <c r="C7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "&lt;&gt;All",  'Country-Vehicle Extraction'!D$2:D$1024, $A7, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Complete</v>
-      </c>
       <c r="D7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "All",  'Country-Vehicle Extraction'!$D$2:$D$1024, $A7, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Complete</v>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A7, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Missing</v>
       </c>
       <c r="E7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "&lt;&gt;All",  'Country-Vehicle Extraction'!$D$2:$D$1024, $A7, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A7, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="F7" t="s">
@@ -1538,19 +1550,19 @@
         <v>16</v>
       </c>
       <c r="B8" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "All",  'Country-Vehicle Extraction'!$D$2:$D$1024, $A8, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A8, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Missing</v>
+      </c>
+      <c r="C8" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!E$2:E$1003, $A8, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
-      <c r="C8" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "&lt;&gt;All",  'Country-Vehicle Extraction'!D$2:D$1024, $A8, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Complete</v>
-      </c>
       <c r="D8" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "All",  'Country-Vehicle Extraction'!$D$2:$D$1024, $A8, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Complete</v>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A8, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Missing</v>
       </c>
       <c r="E8" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "&lt;&gt;All",  'Country-Vehicle Extraction'!$D$2:$D$1024, $A8, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A8, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="F8" t="s">
@@ -1565,24 +1577,24 @@
         <v>17</v>
       </c>
       <c r="B9" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "All",  'Country-Vehicle Extraction'!$D$2:$D$1024, $A9, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A9, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Missing</v>
+      </c>
+      <c r="C9" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!E$2:E$1003, $A9, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
-      <c r="C9" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "&lt;&gt;All",  'Country-Vehicle Extraction'!D$2:D$1024, $A9, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+      <c r="D9" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A9, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Missing</v>
+      </c>
+      <c r="E9" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A9, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
-      <c r="D9" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "All",  'Country-Vehicle Extraction'!$D$2:$D$1024, $A9, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Complete</v>
-      </c>
-      <c r="E9" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "&lt;&gt;All",  'Country-Vehicle Extraction'!$D$2:$D$1024, $A9, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Complete</v>
-      </c>
       <c r="F9" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1024, F$1,  'Country-Vehicle Extraction'!$B$2:$B$1024, F$2,  'Country-Vehicle Extraction'!$C$2:$C$1024, "All",  'Country-Vehicle Extraction'!$D$2:$D$1024, $A9, 'Country-Vehicle Extraction'!$I$2:$I$1024, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Complete</v>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, F$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, F$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A9, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Missing</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -1653,46 +1665,46 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C3" s="32"/>
       <c r="D3" s="28" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="30" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1706,7 +1718,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B6" t="str">
         <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, B$1,  'Scenario Definition Extraction'!$B$2:$B$991, B$2,  'Scenario Definition Extraction'!$C$2:$C$991, B$3, 'Scenario Definition Extraction'!$D$2:$D$991, B$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A6) = 0, "Missing", "Complete")</f>
@@ -1735,7 +1747,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B7" t="str">
         <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, B$1,  'Scenario Definition Extraction'!$B$2:$B$991, B$2,  'Scenario Definition Extraction'!$C$2:$C$991, B$3, 'Scenario Definition Extraction'!$D$2:$D$991, B$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A7) = 0, "Missing", "Complete")</f>
@@ -1764,7 +1776,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B8" t="str">
         <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, B$1,  'Scenario Definition Extraction'!$B$2:$B$991, B$2,  'Scenario Definition Extraction'!$C$2:$C$991, B$3, 'Scenario Definition Extraction'!$D$2:$D$991, B$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A8) = 0, "Missing", "Complete")</f>
@@ -1872,28 +1884,28 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1904,28 +1916,28 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I2" s="7">
         <v>0.8</v>
       </c>
       <c r="J2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1936,28 +1948,28 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I3" s="7">
         <v>0.8</v>
       </c>
       <c r="J3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1968,28 +1980,28 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I4" s="7">
         <v>0.8</v>
       </c>
       <c r="J4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2000,28 +2012,28 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E5" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I5" s="7">
         <v>0.8</v>
       </c>
       <c r="J5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -2032,28 +2044,28 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I6" s="7">
         <v>0.8</v>
       </c>
       <c r="J6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2064,28 +2076,28 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E7" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H7" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I7" s="7">
         <v>0.8</v>
       </c>
       <c r="J7" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -2096,28 +2108,28 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E8" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I8" s="7">
         <v>0.8</v>
       </c>
       <c r="J8" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -2128,28 +2140,28 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E9" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I9" s="7">
         <v>0.8</v>
       </c>
       <c r="J9" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -2160,28 +2172,28 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E10" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I10" s="7">
         <v>0.8</v>
       </c>
       <c r="J10" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -2192,28 +2204,28 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E11" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H11" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I11" s="7">
         <v>0.8</v>
       </c>
       <c r="J11" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -2224,28 +2236,28 @@
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E12" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H12" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I12" s="7">
         <v>0.8</v>
       </c>
       <c r="J12" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -2256,28 +2268,28 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E13" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H13" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I13" s="7">
         <v>0.8</v>
       </c>
       <c r="J13" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -2288,28 +2300,28 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E14" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F14" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G14" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H14" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I14">
         <v>840</v>
       </c>
       <c r="J14" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2320,28 +2332,28 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E15" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F15" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G15" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H15" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I15">
         <v>24</v>
       </c>
       <c r="J15" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2352,28 +2364,28 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E16" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F16" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G16" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H16" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I16">
         <v>14.084507042253522</v>
       </c>
       <c r="J16" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2384,28 +2396,28 @@
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E17" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F17" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H17" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I17">
         <v>56.338028169014088</v>
       </c>
       <c r="J17" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2416,28 +2428,28 @@
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E18" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F18" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H18" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I18">
         <v>42.5</v>
       </c>
       <c r="J18" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2448,28 +2460,28 @@
         <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E19" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F19" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H19" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I19">
         <v>0.125</v>
       </c>
       <c r="J19" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -2519,36 +2531,36 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="45">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E2">
         <v>2021</v>
@@ -2556,30 +2568,30 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B4" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D4" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F4" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -2593,18 +2605,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7501F0-08E1-4A63-A382-F6741C91E79A}">
-  <dimension ref="A1:L86"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="60.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.140625" customWidth="1"/>
-    <col min="12" max="12" width="50.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="60.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="10.140625" customWidth="1"/>
+    <col min="13" max="13" width="50.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2615,10 +2629,10 @@
         <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>19</v>
@@ -2641,8 +2655,11 @@
       <c r="L1" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2650,28 +2667,31 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
-        <v>27</v>
-      </c>
       <c r="F2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="7">
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="7">
         <v>0.97</v>
       </c>
-      <c r="L2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2679,25 +2699,31 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" t="s">
         <v>31</v>
       </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="7">
-        <v>0.97</v>
-      </c>
-      <c r="L3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="J3" s="5">
+        <v>7.1</v>
+      </c>
+      <c r="M3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -2705,22 +2731,28 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -2728,22 +2760,28 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
         <v>34</v>
       </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="5">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -2751,22 +2789,28 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" t="s">
         <v>35</v>
       </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -2774,22 +2818,28 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>34</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -2797,28 +2847,28 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" t="s">
-        <v>37</v>
-      </c>
       <c r="F8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="5">
-        <v>7.1</v>
-      </c>
-      <c r="L8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+        <v>34</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -2826,25 +2876,31 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
         <v>14</v>
       </c>
-      <c r="E9" t="s">
-        <v>37</v>
-      </c>
       <c r="F9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>42</v>
+      </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -2852,25 +2908,28 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="5">
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="G10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0.97</v>
+      </c>
+      <c r="M10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -2878,25 +2937,31 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" t="s">
         <v>34</v>
       </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" t="s">
-        <v>29</v>
-      </c>
-      <c r="I11">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="5">
+        <v>7.1</v>
+      </c>
+      <c r="M11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -2904,25 +2969,28 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" t="s">
         <v>35</v>
       </c>
-      <c r="D12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" t="s">
-        <v>29</v>
-      </c>
-      <c r="I12">
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="I12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -2930,25 +2998,28 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" t="s">
-        <v>29</v>
-      </c>
-      <c r="I13">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>34</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="5">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -2956,28 +3027,28 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" t="s">
-        <v>41</v>
-      </c>
-      <c r="I14" s="5">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+        <v>34</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -2985,28 +3056,28 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" t="s">
         <v>31</v>
       </c>
-      <c r="D15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" t="s">
-        <v>38</v>
-      </c>
-      <c r="H15" t="s">
-        <v>43</v>
-      </c>
-      <c r="I15" s="5">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="L15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="J15">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -3014,25 +3085,28 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>38</v>
-      </c>
-      <c r="H16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" s="5">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+        <v>34</v>
+      </c>
+      <c r="G16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -3040,25 +3114,31 @@
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>38</v>
-      </c>
-      <c r="H17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" t="s">
         <v>43</v>
       </c>
-      <c r="I17" s="5">
+      <c r="J17" s="5">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="M17" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -3066,675 +3146,951 @@
         <v>5</v>
       </c>
       <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" t="s">
+        <v>47</v>
+      </c>
+      <c r="J18" s="7">
+        <v>1</v>
+      </c>
+      <c r="M18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19">
+        <v>2021</v>
+      </c>
+      <c r="I19" t="s">
+        <v>49</v>
+      </c>
+      <c r="J19" s="17">
+        <v>0.98099999999999998</v>
+      </c>
+      <c r="K19" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20">
+        <v>2021</v>
+      </c>
+      <c r="I20" t="s">
+        <v>49</v>
+      </c>
+      <c r="J20" s="17">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="K20" t="s">
+        <v>52</v>
+      </c>
+      <c r="M20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21">
+        <v>2021</v>
+      </c>
+      <c r="I21" t="s">
+        <v>49</v>
+      </c>
+      <c r="J21" s="17">
+        <v>0.98099999999999998</v>
+      </c>
+      <c r="K21" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22">
+        <v>2021</v>
+      </c>
+      <c r="I22" t="s">
+        <v>49</v>
+      </c>
+      <c r="J22" s="17">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="K22" t="s">
+        <v>56</v>
+      </c>
+      <c r="M22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23">
+        <v>2021</v>
+      </c>
+      <c r="I23" t="s">
+        <v>49</v>
+      </c>
+      <c r="J23" s="17">
+        <v>0.98599999999999999</v>
+      </c>
+      <c r="K23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24">
+        <v>2021</v>
+      </c>
+      <c r="I24" t="s">
+        <v>49</v>
+      </c>
+      <c r="J24" s="17">
+        <v>0.98599999999999999</v>
+      </c>
+      <c r="K24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" t="s">
         <v>35</v>
       </c>
-      <c r="D18" t="s">
+      <c r="H25">
+        <v>2021</v>
+      </c>
+      <c r="I25" t="s">
+        <v>49</v>
+      </c>
+      <c r="J25">
+        <v>6.3</v>
+      </c>
+      <c r="K25" t="s">
+        <v>60</v>
+      </c>
+      <c r="L25">
+        <v>0.1</v>
+      </c>
+      <c r="M25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" t="s">
         <v>14</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F26" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" t="s">
+        <v>35</v>
+      </c>
+      <c r="H26">
+        <v>2021</v>
+      </c>
+      <c r="I26" t="s">
+        <v>49</v>
+      </c>
+      <c r="J26">
+        <v>8.4</v>
+      </c>
+      <c r="K26" t="s">
+        <v>62</v>
+      </c>
+      <c r="L26">
+        <v>0.3</v>
+      </c>
+      <c r="M26" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" t="s">
+        <v>34</v>
+      </c>
+      <c r="G27" t="s">
+        <v>35</v>
+      </c>
+      <c r="H27">
+        <v>2021</v>
+      </c>
+      <c r="I27" t="s">
+        <v>49</v>
+      </c>
+      <c r="J27" s="18">
+        <v>8</v>
+      </c>
+      <c r="K27" t="s">
+        <v>63</v>
+      </c>
+      <c r="L27">
+        <v>0.3</v>
+      </c>
+      <c r="M27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H28">
+        <v>2021</v>
+      </c>
+      <c r="I28" t="s">
+        <v>49</v>
+      </c>
+      <c r="J28">
+        <v>5.9</v>
+      </c>
+      <c r="K28" t="s">
+        <v>65</v>
+      </c>
+      <c r="L28">
+        <v>0.3</v>
+      </c>
+      <c r="M28" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" t="s">
         <v>40</v>
       </c>
-      <c r="F18" t="s">
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" t="s">
+        <v>34</v>
+      </c>
+      <c r="G29" t="s">
+        <v>35</v>
+      </c>
+      <c r="H29">
+        <v>2021</v>
+      </c>
+      <c r="I29" t="s">
+        <v>49</v>
+      </c>
+      <c r="J29">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K29" t="s">
+        <v>67</v>
+      </c>
+      <c r="L29">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" t="s">
+        <v>34</v>
+      </c>
+      <c r="G30" t="s">
+        <v>35</v>
+      </c>
+      <c r="H30">
+        <v>2021</v>
+      </c>
+      <c r="I30" t="s">
+        <v>49</v>
+      </c>
+      <c r="J30">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="K30" t="s">
+        <v>68</v>
+      </c>
+      <c r="L30">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" t="s">
+        <v>42</v>
+      </c>
+      <c r="G31" t="s">
+        <v>35</v>
+      </c>
+      <c r="H31">
+        <v>2021</v>
+      </c>
+      <c r="I31" t="s">
+        <v>49</v>
+      </c>
+      <c r="J31">
+        <v>3.0370370370370368</v>
+      </c>
+      <c r="M31" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" t="s">
+        <v>42</v>
+      </c>
+      <c r="G32" t="s">
+        <v>35</v>
+      </c>
+      <c r="H32">
+        <v>2021</v>
+      </c>
+      <c r="I32" t="s">
+        <v>49</v>
+      </c>
+      <c r="J32">
+        <v>3.6296296296296298</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" t="s">
         <v>38</v>
       </c>
-      <c r="H18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I18" s="5">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="D33" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" t="s">
         <v>14</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F33" t="s">
+        <v>42</v>
+      </c>
+      <c r="G33" t="s">
+        <v>35</v>
+      </c>
+      <c r="H33">
+        <v>2021</v>
+      </c>
+      <c r="I33" t="s">
+        <v>49</v>
+      </c>
+      <c r="J33">
+        <v>3.1111111111111112</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" t="s">
+        <v>42</v>
+      </c>
+      <c r="G34" t="s">
+        <v>35</v>
+      </c>
+      <c r="H34">
+        <v>2021</v>
+      </c>
+      <c r="I34" t="s">
+        <v>49</v>
+      </c>
+      <c r="J34" s="18">
+        <v>2.9629629629629624</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" t="s">
+        <v>2</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" t="s">
         <v>40</v>
       </c>
-      <c r="F19" t="s">
+      <c r="D35" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" t="s">
+        <v>42</v>
+      </c>
+      <c r="G35" t="s">
+        <v>35</v>
+      </c>
+      <c r="H35">
+        <v>2021</v>
+      </c>
+      <c r="I35" t="s">
+        <v>49</v>
+      </c>
+      <c r="J35">
+        <v>2.4444444444444446</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" t="s">
+        <v>2</v>
+      </c>
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" t="s">
+        <v>42</v>
+      </c>
+      <c r="G36" t="s">
+        <v>35</v>
+      </c>
+      <c r="H36">
+        <v>2021</v>
+      </c>
+      <c r="I36" t="s">
+        <v>49</v>
+      </c>
+      <c r="J36">
+        <v>1.7037037037037035</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37" t="s">
+        <v>30</v>
+      </c>
+      <c r="H37">
+        <v>2021</v>
+      </c>
+      <c r="I37" t="s">
+        <v>49</v>
+      </c>
+      <c r="J37" s="17">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="K37" t="s">
+        <v>70</v>
+      </c>
+      <c r="M37" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" t="s">
+        <v>2</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" t="s">
+        <v>29</v>
+      </c>
+      <c r="G38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H38">
+        <v>2021</v>
+      </c>
+      <c r="I38" t="s">
+        <v>49</v>
+      </c>
+      <c r="J38" s="17">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="K38" t="s">
+        <v>52</v>
+      </c>
+      <c r="M38" s="19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" t="s">
         <v>38</v>
       </c>
-      <c r="H19" t="s">
-        <v>43</v>
-      </c>
-      <c r="I19" s="5">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="D39" t="s">
+        <v>27</v>
+      </c>
+      <c r="E39" t="s">
         <v>15</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F39" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39" t="s">
+        <v>30</v>
+      </c>
+      <c r="H39">
+        <v>2021</v>
+      </c>
+      <c r="I39" t="s">
+        <v>49</v>
+      </c>
+      <c r="J39" s="17">
+        <v>0.98099999999999998</v>
+      </c>
+      <c r="K39" t="s">
+        <v>54</v>
+      </c>
+      <c r="M39" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" t="s">
+        <v>2</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" t="s">
         <v>27</v>
       </c>
-      <c r="F20" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20" s="7">
-        <v>0.97</v>
-      </c>
-      <c r="L20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="E40" t="s">
         <v>15</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F40" t="s">
+        <v>29</v>
+      </c>
+      <c r="G40" t="s">
+        <v>30</v>
+      </c>
+      <c r="H40">
+        <v>2021</v>
+      </c>
+      <c r="I40" t="s">
+        <v>49</v>
+      </c>
+      <c r="J40" s="17">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="K40" t="s">
+        <v>56</v>
+      </c>
+      <c r="M40" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" t="s">
+        <v>2</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" t="s">
+        <v>40</v>
+      </c>
+      <c r="D41" t="s">
         <v>27</v>
       </c>
-      <c r="F21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I21" s="7">
-        <v>0.97</v>
-      </c>
-      <c r="L21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="E41" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" t="s">
+        <v>29</v>
+      </c>
+      <c r="G41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H41">
+        <v>2021</v>
+      </c>
+      <c r="I41" t="s">
+        <v>49</v>
+      </c>
+      <c r="J41" s="17">
+        <v>0.98599999999999999</v>
+      </c>
+      <c r="K41" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" t="s">
+        <v>29</v>
+      </c>
+      <c r="G42" t="s">
+        <v>30</v>
+      </c>
+      <c r="H42">
+        <v>2021</v>
+      </c>
+      <c r="I42" t="s">
+        <v>49</v>
+      </c>
+      <c r="J42" s="17">
+        <v>0.98599999999999999</v>
+      </c>
+      <c r="K42" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="A43" t="s">
+        <v>2</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" t="s">
         <v>33</v>
       </c>
-      <c r="D22" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" t="s">
-        <v>28</v>
-      </c>
-      <c r="I22" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="D43" t="s">
+        <v>33</v>
+      </c>
+      <c r="E43" t="s">
+        <v>16</v>
+      </c>
+      <c r="F43" t="s">
         <v>34</v>
       </c>
-      <c r="D23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" t="s">
-        <v>28</v>
-      </c>
-      <c r="I23" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="G43" t="s">
         <v>35</v>
       </c>
-      <c r="D24" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" t="s">
-        <v>28</v>
-      </c>
-      <c r="I24" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" t="s">
-        <v>28</v>
-      </c>
-      <c r="I25" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" t="s">
-        <v>26</v>
-      </c>
-      <c r="D26" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" t="s">
-        <v>37</v>
-      </c>
-      <c r="F26" t="s">
-        <v>38</v>
-      </c>
-      <c r="H26" t="s">
-        <v>29</v>
-      </c>
-      <c r="I26" s="5">
-        <v>7.1</v>
-      </c>
-      <c r="L26" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F27" t="s">
-        <v>38</v>
-      </c>
-      <c r="H27" t="s">
-        <v>29</v>
-      </c>
-      <c r="I27">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" t="s">
-        <v>37</v>
-      </c>
-      <c r="F28" t="s">
-        <v>38</v>
-      </c>
-      <c r="H28" t="s">
-        <v>29</v>
-      </c>
-      <c r="I28" s="5">
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" t="s">
-        <v>38</v>
-      </c>
-      <c r="H29" t="s">
-        <v>29</v>
-      </c>
-      <c r="I29">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" t="s">
-        <v>1</v>
-      </c>
-      <c r="B30" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" t="s">
-        <v>37</v>
-      </c>
-      <c r="F30" t="s">
-        <v>38</v>
-      </c>
-      <c r="H30" t="s">
-        <v>29</v>
-      </c>
-      <c r="I30">
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B31" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" t="s">
-        <v>37</v>
-      </c>
-      <c r="F31" t="s">
-        <v>38</v>
-      </c>
-      <c r="H31" t="s">
-        <v>29</v>
-      </c>
-      <c r="I31">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" t="s">
-        <v>26</v>
-      </c>
-      <c r="D32" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" t="s">
-        <v>40</v>
-      </c>
-      <c r="F32" t="s">
-        <v>38</v>
-      </c>
-      <c r="H32" t="s">
-        <v>41</v>
-      </c>
-      <c r="I32" s="5">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
-      <c r="A33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B33" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" t="s">
-        <v>31</v>
-      </c>
-      <c r="D33" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" t="s">
-        <v>40</v>
-      </c>
-      <c r="F33" t="s">
-        <v>38</v>
-      </c>
-      <c r="H33" t="s">
-        <v>43</v>
-      </c>
-      <c r="I33" s="5">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="L33" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12">
-      <c r="A34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E34" t="s">
-        <v>40</v>
-      </c>
-      <c r="F34" t="s">
-        <v>38</v>
-      </c>
-      <c r="H34" t="s">
-        <v>43</v>
-      </c>
-      <c r="I34" s="5">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
-      <c r="A35" t="s">
-        <v>1</v>
-      </c>
-      <c r="B35" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" t="s">
-        <v>34</v>
-      </c>
-      <c r="D35" t="s">
-        <v>16</v>
-      </c>
-      <c r="E35" t="s">
-        <v>40</v>
-      </c>
-      <c r="F35" t="s">
-        <v>38</v>
-      </c>
-      <c r="H35" t="s">
-        <v>43</v>
-      </c>
-      <c r="I35" s="5">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12">
-      <c r="A36" t="s">
-        <v>1</v>
-      </c>
-      <c r="B36" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" t="s">
-        <v>35</v>
-      </c>
-      <c r="D36" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36" t="s">
-        <v>40</v>
-      </c>
-      <c r="F36" t="s">
-        <v>38</v>
-      </c>
-      <c r="H36" t="s">
-        <v>43</v>
-      </c>
-      <c r="I36" s="5">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12">
-      <c r="A37" t="s">
-        <v>1</v>
-      </c>
-      <c r="B37" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" t="s">
-        <v>36</v>
-      </c>
-      <c r="D37" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37" t="s">
-        <v>40</v>
-      </c>
-      <c r="F37" t="s">
-        <v>38</v>
-      </c>
-      <c r="H37" t="s">
-        <v>43</v>
-      </c>
-      <c r="I37" s="5">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12">
-      <c r="A38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B38" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" t="s">
-        <v>26</v>
-      </c>
-      <c r="D38" t="s">
-        <v>17</v>
-      </c>
-      <c r="E38" t="s">
-        <v>27</v>
-      </c>
-      <c r="F38" t="s">
-        <v>28</v>
-      </c>
-      <c r="H38" t="s">
-        <v>43</v>
-      </c>
-      <c r="I38" s="7">
-        <v>1</v>
-      </c>
-      <c r="L38" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12">
-      <c r="A39" t="s">
-        <v>1</v>
-      </c>
-      <c r="B39" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" t="s">
-        <v>31</v>
-      </c>
-      <c r="D39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E39" t="s">
-        <v>27</v>
-      </c>
-      <c r="F39" t="s">
-        <v>28</v>
-      </c>
-      <c r="H39" t="s">
-        <v>43</v>
-      </c>
-      <c r="I39" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12">
-      <c r="A40" t="s">
-        <v>1</v>
-      </c>
-      <c r="B40" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" t="s">
-        <v>33</v>
-      </c>
-      <c r="D40" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40" t="s">
-        <v>27</v>
-      </c>
-      <c r="F40" t="s">
-        <v>28</v>
-      </c>
-      <c r="H40" t="s">
-        <v>43</v>
-      </c>
-      <c r="I40" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12">
-      <c r="A41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B41" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" t="s">
-        <v>34</v>
-      </c>
-      <c r="D41" t="s">
-        <v>17</v>
-      </c>
-      <c r="E41" t="s">
-        <v>27</v>
-      </c>
-      <c r="F41" t="s">
-        <v>28</v>
-      </c>
-      <c r="H41" t="s">
-        <v>43</v>
-      </c>
-      <c r="I41" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12">
-      <c r="A42" t="s">
-        <v>1</v>
-      </c>
-      <c r="B42" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" t="s">
-        <v>35</v>
-      </c>
-      <c r="D42" t="s">
-        <v>17</v>
-      </c>
-      <c r="E42" t="s">
-        <v>27</v>
-      </c>
-      <c r="F42" t="s">
-        <v>28</v>
-      </c>
-      <c r="H42" t="s">
-        <v>43</v>
-      </c>
-      <c r="I42" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12">
-      <c r="A43" t="s">
-        <v>1</v>
-      </c>
-      <c r="B43" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43" t="s">
-        <v>36</v>
-      </c>
-      <c r="D43" t="s">
-        <v>17</v>
-      </c>
-      <c r="E43" t="s">
-        <v>27</v>
-      </c>
-      <c r="F43" t="s">
-        <v>28</v>
-      </c>
-      <c r="H43" t="s">
-        <v>43</v>
-      </c>
-      <c r="I43" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12">
+      <c r="H43">
+        <v>2021</v>
+      </c>
+      <c r="I43" t="s">
+        <v>49</v>
+      </c>
+      <c r="J43">
+        <v>4.2</v>
+      </c>
+      <c r="K43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L43">
+        <v>0.1</v>
+      </c>
+      <c r="M43" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" t="s">
         <v>2</v>
       </c>
@@ -3742,34 +4098,37 @@
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D44" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E44" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F44" t="s">
-        <v>28</v>
-      </c>
-      <c r="G44">
+        <v>34</v>
+      </c>
+      <c r="G44" t="s">
+        <v>35</v>
+      </c>
+      <c r="H44">
         <v>2021</v>
       </c>
-      <c r="H44" t="s">
-        <v>48</v>
-      </c>
-      <c r="I44" s="17">
-        <v>0.98099999999999998</v>
-      </c>
-      <c r="J44" t="s">
+      <c r="I44" t="s">
         <v>49</v>
       </c>
-      <c r="L44" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12">
+      <c r="J44">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="K44" t="s">
+        <v>76</v>
+      </c>
+      <c r="M44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" t="s">
         <v>2</v>
       </c>
@@ -3777,34 +4136,37 @@
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D45" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="E45" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F45" t="s">
-        <v>28</v>
-      </c>
-      <c r="G45">
+        <v>34</v>
+      </c>
+      <c r="G45" t="s">
+        <v>35</v>
+      </c>
+      <c r="H45">
         <v>2021</v>
       </c>
-      <c r="H45" t="s">
-        <v>48</v>
-      </c>
-      <c r="I45" s="17">
-        <v>0.96299999999999997</v>
-      </c>
-      <c r="J45" t="s">
-        <v>51</v>
-      </c>
-      <c r="L45" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12">
+      <c r="I45" t="s">
+        <v>49</v>
+      </c>
+      <c r="J45">
+        <v>4.3</v>
+      </c>
+      <c r="K45" t="s">
+        <v>78</v>
+      </c>
+      <c r="M45" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" t="s">
         <v>2</v>
       </c>
@@ -3812,34 +4174,40 @@
         <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D46" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E46" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F46" t="s">
-        <v>28</v>
-      </c>
-      <c r="G46">
+        <v>34</v>
+      </c>
+      <c r="G46" t="s">
+        <v>35</v>
+      </c>
+      <c r="H46">
         <v>2021</v>
       </c>
-      <c r="H46" t="s">
-        <v>48</v>
-      </c>
-      <c r="I46" s="17">
-        <v>0.98099999999999998</v>
-      </c>
-      <c r="J46" t="s">
-        <v>53</v>
-      </c>
-      <c r="L46" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12">
+      <c r="I46" t="s">
+        <v>49</v>
+      </c>
+      <c r="J46">
+        <v>8.4</v>
+      </c>
+      <c r="K46" t="s">
+        <v>62</v>
+      </c>
+      <c r="L46">
+        <v>0.3</v>
+      </c>
+      <c r="M46" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" t="s">
         <v>2</v>
       </c>
@@ -3847,34 +4215,40 @@
         <v>6</v>
       </c>
       <c r="C47" t="s">
+        <v>38</v>
+      </c>
+      <c r="D47" t="s">
+        <v>27</v>
+      </c>
+      <c r="E47" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" t="s">
         <v>34</v>
       </c>
-      <c r="D47" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" t="s">
-        <v>27</v>
-      </c>
-      <c r="F47" t="s">
-        <v>28</v>
-      </c>
-      <c r="G47">
+      <c r="G47" t="s">
+        <v>35</v>
+      </c>
+      <c r="H47">
         <v>2021</v>
       </c>
-      <c r="H47" t="s">
-        <v>48</v>
-      </c>
-      <c r="I47" s="17">
-        <v>0.99199999999999999</v>
-      </c>
-      <c r="J47" t="s">
+      <c r="I47" t="s">
+        <v>49</v>
+      </c>
+      <c r="J47" s="18">
+        <v>8</v>
+      </c>
+      <c r="K47" t="s">
+        <v>63</v>
+      </c>
+      <c r="L47">
+        <v>0.3</v>
+      </c>
+      <c r="M47" t="s">
         <v>55</v>
       </c>
-      <c r="L47" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12">
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" t="s">
         <v>2</v>
       </c>
@@ -3882,31 +4256,37 @@
         <v>6</v>
       </c>
       <c r="C48" t="s">
+        <v>39</v>
+      </c>
+      <c r="D48" t="s">
+        <v>27</v>
+      </c>
+      <c r="E48" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48" t="s">
+        <v>34</v>
+      </c>
+      <c r="G48" t="s">
         <v>35</v>
       </c>
-      <c r="D48" t="s">
-        <v>12</v>
-      </c>
-      <c r="E48" t="s">
-        <v>27</v>
-      </c>
-      <c r="F48" t="s">
-        <v>28</v>
-      </c>
-      <c r="G48">
+      <c r="H48">
         <v>2021</v>
       </c>
-      <c r="H48" t="s">
-        <v>48</v>
-      </c>
-      <c r="I48" s="17">
-        <v>0.98599999999999999</v>
-      </c>
-      <c r="J48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12">
+      <c r="I48" t="s">
+        <v>49</v>
+      </c>
+      <c r="J48">
+        <v>5.9</v>
+      </c>
+      <c r="K48" t="s">
+        <v>65</v>
+      </c>
+      <c r="L48">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" t="s">
         <v>2</v>
       </c>
@@ -3914,31 +4294,37 @@
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D49" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E49" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F49" t="s">
-        <v>28</v>
-      </c>
-      <c r="G49">
+        <v>34</v>
+      </c>
+      <c r="G49" t="s">
+        <v>35</v>
+      </c>
+      <c r="H49">
         <v>2021</v>
       </c>
-      <c r="H49" t="s">
-        <v>48</v>
-      </c>
-      <c r="I49" s="17">
-        <v>0.98599999999999999</v>
-      </c>
-      <c r="J49" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12">
+      <c r="I49" t="s">
+        <v>49</v>
+      </c>
+      <c r="J49">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K49" t="s">
+        <v>67</v>
+      </c>
+      <c r="L49">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" t="s">
         <v>2</v>
       </c>
@@ -3946,37 +4332,37 @@
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D50" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E50" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>38</v>
-      </c>
-      <c r="G50">
+        <v>34</v>
+      </c>
+      <c r="G50" t="s">
+        <v>35</v>
+      </c>
+      <c r="H50">
         <v>2021</v>
       </c>
-      <c r="H50" t="s">
-        <v>48</v>
-      </c>
-      <c r="I50">
-        <v>6.3</v>
-      </c>
-      <c r="J50" t="s">
-        <v>59</v>
-      </c>
-      <c r="K50">
-        <v>0.1</v>
-      </c>
-      <c r="L50" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12">
+      <c r="I50" t="s">
+        <v>49</v>
+      </c>
+      <c r="J50">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="K50" t="s">
+        <v>68</v>
+      </c>
+      <c r="L50">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" t="s">
         <v>2</v>
       </c>
@@ -3984,37 +4370,35 @@
         <v>6</v>
       </c>
       <c r="C51" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D51" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="E51" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F51" t="s">
-        <v>38</v>
-      </c>
-      <c r="G51">
+        <v>42</v>
+      </c>
+      <c r="G51" t="s">
+        <v>35</v>
+      </c>
+      <c r="H51">
         <v>2021</v>
       </c>
-      <c r="H51" t="s">
-        <v>48</v>
-      </c>
-      <c r="I51">
-        <v>8.4</v>
-      </c>
-      <c r="J51" t="s">
-        <v>61</v>
-      </c>
-      <c r="K51">
-        <v>0.3</v>
-      </c>
-      <c r="L51" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12">
+      <c r="I51" t="s">
+        <v>49</v>
+      </c>
+      <c r="J51">
+        <f>(5.5-2.5)/1.35</f>
+        <v>2.2222222222222219</v>
+      </c>
+      <c r="M51" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" t="s">
         <v>2</v>
       </c>
@@ -4025,34 +4409,32 @@
         <v>33</v>
       </c>
       <c r="D52" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E52" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F52" t="s">
-        <v>38</v>
-      </c>
-      <c r="G52">
+        <v>42</v>
+      </c>
+      <c r="G52" t="s">
+        <v>35</v>
+      </c>
+      <c r="H52">
         <v>2021</v>
       </c>
-      <c r="H52" t="s">
-        <v>48</v>
-      </c>
-      <c r="I52" s="18">
-        <v>8</v>
-      </c>
-      <c r="J52" t="s">
-        <v>62</v>
-      </c>
-      <c r="K52">
-        <v>0.3</v>
-      </c>
-      <c r="L52" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12">
+      <c r="I52" t="s">
+        <v>49</v>
+      </c>
+      <c r="J52">
+        <f>(5.4-2.4)/1.35</f>
+        <v>2.2222222222222223</v>
+      </c>
+      <c r="M52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" t="s">
         <v>2</v>
       </c>
@@ -4060,37 +4442,35 @@
         <v>6</v>
       </c>
       <c r="C53" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D53" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="E53" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F53" t="s">
-        <v>38</v>
-      </c>
-      <c r="G53">
+        <v>42</v>
+      </c>
+      <c r="G53" t="s">
+        <v>35</v>
+      </c>
+      <c r="H53">
         <v>2021</v>
       </c>
-      <c r="H53" t="s">
-        <v>48</v>
-      </c>
-      <c r="I53">
-        <v>5.9</v>
-      </c>
-      <c r="J53" t="s">
-        <v>64</v>
-      </c>
-      <c r="K53">
-        <v>0.3</v>
-      </c>
-      <c r="L53" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12">
+      <c r="I53" t="s">
+        <v>49</v>
+      </c>
+      <c r="J53">
+        <f>(5.6-2.5)/1.35</f>
+        <v>2.2962962962962958</v>
+      </c>
+      <c r="M53" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" t="s">
         <v>2</v>
       </c>
@@ -4098,34 +4478,34 @@
         <v>6</v>
       </c>
       <c r="C54" t="s">
+        <v>37</v>
+      </c>
+      <c r="D54" t="s">
+        <v>27</v>
+      </c>
+      <c r="E54" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" t="s">
+        <v>42</v>
+      </c>
+      <c r="G54" t="s">
         <v>35</v>
       </c>
-      <c r="D54" t="s">
-        <v>14</v>
-      </c>
-      <c r="E54" t="s">
-        <v>37</v>
-      </c>
-      <c r="F54" t="s">
-        <v>38</v>
-      </c>
-      <c r="G54">
+      <c r="H54">
         <v>2021</v>
       </c>
-      <c r="H54" t="s">
-        <v>48</v>
-      </c>
-      <c r="I54">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="J54" t="s">
-        <v>66</v>
-      </c>
-      <c r="K54">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12">
+      <c r="I54" t="s">
+        <v>49</v>
+      </c>
+      <c r="J54">
+        <v>3.6296296296296298</v>
+      </c>
+      <c r="M54" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" t="s">
         <v>2</v>
       </c>
@@ -4133,34 +4513,31 @@
         <v>6</v>
       </c>
       <c r="C55" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E55" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F55" t="s">
-        <v>38</v>
-      </c>
-      <c r="G55">
+        <v>42</v>
+      </c>
+      <c r="G55" t="s">
+        <v>35</v>
+      </c>
+      <c r="H55">
         <v>2021</v>
       </c>
-      <c r="H55" t="s">
-        <v>48</v>
-      </c>
-      <c r="I55">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="J55" t="s">
-        <v>67</v>
-      </c>
-      <c r="K55">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12">
+      <c r="I55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J55">
+        <v>3.1111111111111112</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
       <c r="A56" t="s">
         <v>2</v>
       </c>
@@ -4168,31 +4545,31 @@
         <v>6</v>
       </c>
       <c r="C56" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D56" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E56" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F56" t="s">
-        <v>38</v>
-      </c>
-      <c r="G56">
+        <v>42</v>
+      </c>
+      <c r="G56" t="s">
+        <v>35</v>
+      </c>
+      <c r="H56">
         <v>2021</v>
       </c>
-      <c r="H56" t="s">
-        <v>48</v>
-      </c>
-      <c r="I56">
-        <v>3.0370370370370368</v>
-      </c>
-      <c r="L56" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12">
+      <c r="I56" t="s">
+        <v>49</v>
+      </c>
+      <c r="J56" s="18">
+        <v>2.9629629629629624</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
       <c r="A57" t="s">
         <v>2</v>
       </c>
@@ -4200,28 +4577,31 @@
         <v>6</v>
       </c>
       <c r="C57" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D57" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E57" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F57" t="s">
-        <v>38</v>
-      </c>
-      <c r="G57">
+        <v>42</v>
+      </c>
+      <c r="G57" t="s">
+        <v>35</v>
+      </c>
+      <c r="H57">
         <v>2021</v>
       </c>
-      <c r="H57" t="s">
-        <v>48</v>
-      </c>
-      <c r="I57">
-        <v>3.6296296296296298</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12">
+      <c r="I57" t="s">
+        <v>49</v>
+      </c>
+      <c r="J57">
+        <v>2.4444444444444446</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
       <c r="A58" t="s">
         <v>2</v>
       </c>
@@ -4229,28 +4609,31 @@
         <v>6</v>
       </c>
       <c r="C58" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D58" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E58" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F58" t="s">
-        <v>38</v>
-      </c>
-      <c r="G58">
+        <v>42</v>
+      </c>
+      <c r="G58" t="s">
+        <v>35</v>
+      </c>
+      <c r="H58">
         <v>2021</v>
       </c>
-      <c r="H58" t="s">
-        <v>48</v>
-      </c>
-      <c r="I58">
-        <v>3.1111111111111112</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12">
+      <c r="I58" t="s">
+        <v>49</v>
+      </c>
+      <c r="J58">
+        <v>1.7037037037037035</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13">
       <c r="A59" t="s">
         <v>2</v>
       </c>
@@ -4258,28 +4641,36 @@
         <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D59" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="E59" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F59" t="s">
-        <v>38</v>
-      </c>
-      <c r="G59">
+        <v>29</v>
+      </c>
+      <c r="G59" t="s">
+        <v>30</v>
+      </c>
+      <c r="H59">
         <v>2021</v>
       </c>
-      <c r="H59" t="s">
-        <v>48</v>
-      </c>
-      <c r="I59" s="18">
-        <v>2.9629629629629624</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12">
+      <c r="I59" t="s">
+        <v>49</v>
+      </c>
+      <c r="J59" s="21">
+        <v>0.9796126401630989</v>
+      </c>
+      <c r="K59" s="17"/>
+      <c r="L59" s="17"/>
+      <c r="M59" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
       <c r="A60" t="s">
         <v>2</v>
       </c>
@@ -4287,28 +4678,31 @@
         <v>6</v>
       </c>
       <c r="C60" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D60" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E60" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F60" t="s">
-        <v>38</v>
-      </c>
-      <c r="G60">
+        <v>29</v>
+      </c>
+      <c r="G60" t="s">
+        <v>30</v>
+      </c>
+      <c r="H60">
         <v>2021</v>
       </c>
-      <c r="H60" t="s">
-        <v>48</v>
-      </c>
-      <c r="I60">
-        <v>2.4444444444444446</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12">
+      <c r="I60" t="s">
+        <v>49</v>
+      </c>
+      <c r="J60" s="17">
+        <v>0.96573208722741444</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
       <c r="A61" t="s">
         <v>2</v>
       </c>
@@ -4316,28 +4710,31 @@
         <v>6</v>
       </c>
       <c r="C61" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D61" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E61" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F61" t="s">
-        <v>38</v>
-      </c>
-      <c r="G61">
+        <v>29</v>
+      </c>
+      <c r="G61" t="s">
+        <v>30</v>
+      </c>
+      <c r="H61">
         <v>2021</v>
       </c>
-      <c r="H61" t="s">
-        <v>48</v>
-      </c>
-      <c r="I61">
-        <v>1.7037037037037035</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12">
+      <c r="I61" t="s">
+        <v>49</v>
+      </c>
+      <c r="J61" s="7">
+        <v>0.9785932721712538</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13">
       <c r="A62" t="s">
         <v>2</v>
       </c>
@@ -4345,34 +4742,31 @@
         <v>6</v>
       </c>
       <c r="C62" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D62" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E62" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F62" t="s">
-        <v>28</v>
-      </c>
-      <c r="G62">
+        <v>29</v>
+      </c>
+      <c r="G62" t="s">
+        <v>30</v>
+      </c>
+      <c r="H62">
         <v>2021</v>
       </c>
-      <c r="H62" t="s">
-        <v>48</v>
-      </c>
-      <c r="I62" s="17">
-        <v>0.98799999999999999</v>
-      </c>
-      <c r="J62" t="s">
-        <v>69</v>
-      </c>
-      <c r="L62" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12">
+      <c r="I62" t="s">
+        <v>49</v>
+      </c>
+      <c r="J62" s="20">
+        <v>0.98084677419354838</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
       <c r="A63" t="s">
         <v>2</v>
       </c>
@@ -4380,34 +4774,31 @@
         <v>6</v>
       </c>
       <c r="C63" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D63" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E63" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F63" t="s">
-        <v>28</v>
-      </c>
-      <c r="G63">
+        <v>29</v>
+      </c>
+      <c r="G63" t="s">
+        <v>30</v>
+      </c>
+      <c r="H63">
         <v>2021</v>
       </c>
-      <c r="H63" t="s">
-        <v>48</v>
-      </c>
-      <c r="I63" s="17">
-        <v>0.96299999999999997</v>
-      </c>
-      <c r="J63" t="s">
-        <v>51</v>
-      </c>
-      <c r="L63" s="19" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12">
+      <c r="I63" t="s">
+        <v>49</v>
+      </c>
+      <c r="J63" s="7">
+        <v>0.98884381338742389</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13">
       <c r="A64" t="s">
         <v>2</v>
       </c>
@@ -4415,760 +4806,85 @@
         <v>6</v>
       </c>
       <c r="C64" t="s">
+        <v>41</v>
+      </c>
+      <c r="D64" t="s">
+        <v>27</v>
+      </c>
+      <c r="E64" t="s">
+        <v>17</v>
+      </c>
+      <c r="F64" t="s">
+        <v>29</v>
+      </c>
+      <c r="G64" t="s">
+        <v>30</v>
+      </c>
+      <c r="H64">
+        <v>2021</v>
+      </c>
+      <c r="I64" t="s">
+        <v>49</v>
+      </c>
+      <c r="J64" s="20">
+        <v>0.98377281947261663</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13">
+      <c r="A65" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" t="s">
         <v>33</v>
       </c>
-      <c r="D64" t="s">
-        <v>15</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="D65" t="s">
         <v>27</v>
       </c>
-      <c r="F64" t="s">
-        <v>28</v>
-      </c>
-      <c r="G64">
-        <v>2021</v>
-      </c>
-      <c r="H64" t="s">
-        <v>48</v>
-      </c>
-      <c r="I64" s="17">
-        <v>0.98099999999999998</v>
-      </c>
-      <c r="J64" t="s">
-        <v>53</v>
-      </c>
-      <c r="L64" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12">
-      <c r="A65" t="s">
-        <v>2</v>
-      </c>
-      <c r="B65" t="s">
-        <v>6</v>
-      </c>
-      <c r="C65" t="s">
-        <v>34</v>
-      </c>
-      <c r="D65" t="s">
-        <v>15</v>
-      </c>
       <c r="E65" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F65" t="s">
-        <v>28</v>
-      </c>
-      <c r="G65">
-        <v>2021</v>
-      </c>
-      <c r="H65" t="s">
-        <v>48</v>
-      </c>
-      <c r="I65" s="17">
-        <v>0.99199999999999999</v>
-      </c>
-      <c r="J65" t="s">
-        <v>55</v>
-      </c>
-      <c r="L65" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12">
-      <c r="A66" t="s">
-        <v>2</v>
-      </c>
-      <c r="B66" t="s">
-        <v>6</v>
-      </c>
-      <c r="C66" t="s">
-        <v>35</v>
-      </c>
-      <c r="D66" t="s">
-        <v>15</v>
-      </c>
-      <c r="E66" t="s">
-        <v>27</v>
-      </c>
-      <c r="F66" t="s">
-        <v>28</v>
-      </c>
-      <c r="G66">
-        <v>2021</v>
-      </c>
-      <c r="H66" t="s">
-        <v>48</v>
-      </c>
-      <c r="I66" s="17">
-        <v>0.98599999999999999</v>
-      </c>
-      <c r="J66" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12">
-      <c r="A67" t="s">
-        <v>2</v>
-      </c>
-      <c r="B67" t="s">
-        <v>6</v>
-      </c>
-      <c r="C67" t="s">
-        <v>36</v>
-      </c>
-      <c r="D67" t="s">
-        <v>15</v>
-      </c>
-      <c r="E67" t="s">
-        <v>27</v>
-      </c>
-      <c r="F67" t="s">
-        <v>28</v>
-      </c>
-      <c r="G67">
-        <v>2021</v>
-      </c>
-      <c r="H67" t="s">
-        <v>48</v>
-      </c>
-      <c r="I67" s="17">
-        <v>0.98599999999999999</v>
-      </c>
-      <c r="J67" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12">
-      <c r="A68" t="s">
-        <v>2</v>
-      </c>
-      <c r="B68" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" t="s">
-        <v>26</v>
-      </c>
-      <c r="D68" t="s">
-        <v>16</v>
-      </c>
-      <c r="E68" t="s">
-        <v>37</v>
-      </c>
-      <c r="F68" t="s">
-        <v>38</v>
-      </c>
-      <c r="G68">
-        <v>2021</v>
-      </c>
-      <c r="H68" t="s">
-        <v>48</v>
-      </c>
-      <c r="I68">
-        <v>4.2</v>
-      </c>
-      <c r="J68" t="s">
-        <v>73</v>
-      </c>
-      <c r="K68">
-        <v>0.1</v>
-      </c>
-      <c r="L68" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12">
-      <c r="A69" t="s">
-        <v>2</v>
-      </c>
-      <c r="B69" t="s">
-        <v>6</v>
-      </c>
-      <c r="C69" t="s">
-        <v>31</v>
-      </c>
-      <c r="D69" t="s">
-        <v>16</v>
-      </c>
-      <c r="E69" t="s">
-        <v>37</v>
-      </c>
-      <c r="F69" t="s">
-        <v>38</v>
-      </c>
-      <c r="G69">
-        <v>2021</v>
-      </c>
-      <c r="H69" t="s">
-        <v>48</v>
-      </c>
-      <c r="I69">
-        <v>8.4</v>
-      </c>
-      <c r="J69" t="s">
-        <v>61</v>
-      </c>
-      <c r="K69">
-        <v>0.3</v>
-      </c>
-      <c r="L69" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12">
-      <c r="A70" t="s">
-        <v>2</v>
-      </c>
-      <c r="B70" t="s">
-        <v>6</v>
-      </c>
-      <c r="C70" t="s">
-        <v>33</v>
-      </c>
-      <c r="D70" t="s">
-        <v>16</v>
-      </c>
-      <c r="E70" t="s">
-        <v>37</v>
-      </c>
-      <c r="F70" t="s">
-        <v>38</v>
-      </c>
-      <c r="G70">
-        <v>2021</v>
-      </c>
-      <c r="H70" t="s">
-        <v>48</v>
-      </c>
-      <c r="I70" s="18">
-        <v>8</v>
-      </c>
-      <c r="J70" t="s">
-        <v>62</v>
-      </c>
-      <c r="K70">
-        <v>0.3</v>
-      </c>
-      <c r="L70" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12">
-      <c r="A71" t="s">
-        <v>2</v>
-      </c>
-      <c r="B71" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71" t="s">
-        <v>34</v>
-      </c>
-      <c r="D71" t="s">
-        <v>16</v>
-      </c>
-      <c r="E71" t="s">
-        <v>37</v>
-      </c>
-      <c r="F71" t="s">
-        <v>38</v>
-      </c>
-      <c r="G71">
-        <v>2021</v>
-      </c>
-      <c r="H71" t="s">
-        <v>48</v>
-      </c>
-      <c r="I71">
-        <v>5.9</v>
-      </c>
-      <c r="J71" t="s">
-        <v>64</v>
-      </c>
-      <c r="K71">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12">
-      <c r="A72" t="s">
-        <v>2</v>
-      </c>
-      <c r="B72" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72" t="s">
-        <v>35</v>
-      </c>
-      <c r="D72" t="s">
-        <v>16</v>
-      </c>
-      <c r="E72" t="s">
-        <v>37</v>
-      </c>
-      <c r="F72" t="s">
-        <v>38</v>
-      </c>
-      <c r="G72">
-        <v>2021</v>
-      </c>
-      <c r="H72" t="s">
-        <v>48</v>
-      </c>
-      <c r="I72">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="J72" t="s">
-        <v>66</v>
-      </c>
-      <c r="K72">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12">
-      <c r="A73" t="s">
-        <v>2</v>
-      </c>
-      <c r="B73" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" t="s">
-        <v>36</v>
-      </c>
-      <c r="D73" t="s">
-        <v>16</v>
-      </c>
-      <c r="E73" t="s">
-        <v>37</v>
-      </c>
-      <c r="F73" t="s">
-        <v>38</v>
-      </c>
-      <c r="G73">
-        <v>2021</v>
-      </c>
-      <c r="H73" t="s">
-        <v>48</v>
-      </c>
-      <c r="I73">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="J73" t="s">
-        <v>67</v>
-      </c>
-      <c r="K73">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12">
-      <c r="A74" t="s">
-        <v>2</v>
-      </c>
-      <c r="B74" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" t="s">
-        <v>26</v>
-      </c>
-      <c r="D74" t="s">
-        <v>16</v>
-      </c>
-      <c r="E74" t="s">
-        <v>40</v>
-      </c>
-      <c r="F74" t="s">
-        <v>38</v>
-      </c>
-      <c r="G74">
-        <v>2021</v>
-      </c>
-      <c r="H74" t="s">
-        <v>48</v>
-      </c>
-      <c r="I74">
-        <f>(5.5-2.5)/1.35</f>
-        <v>2.2222222222222219</v>
-      </c>
-      <c r="L74" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12">
-      <c r="A75" t="s">
-        <v>2</v>
-      </c>
-      <c r="B75" t="s">
-        <v>6</v>
-      </c>
-      <c r="C75" t="s">
-        <v>31</v>
-      </c>
-      <c r="D75" t="s">
-        <v>16</v>
-      </c>
-      <c r="E75" t="s">
-        <v>40</v>
-      </c>
-      <c r="F75" t="s">
-        <v>38</v>
-      </c>
-      <c r="G75">
-        <v>2021</v>
-      </c>
-      <c r="H75" t="s">
-        <v>48</v>
-      </c>
-      <c r="I75">
-        <v>3.6296296296296298</v>
-      </c>
-      <c r="L75" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12">
-      <c r="A76" t="s">
-        <v>2</v>
-      </c>
-      <c r="B76" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" t="s">
-        <v>33</v>
-      </c>
-      <c r="D76" t="s">
-        <v>16</v>
-      </c>
-      <c r="E76" t="s">
-        <v>40</v>
-      </c>
-      <c r="F76" t="s">
-        <v>38</v>
-      </c>
-      <c r="G76">
-        <v>2021</v>
-      </c>
-      <c r="H76" t="s">
-        <v>48</v>
-      </c>
-      <c r="I76">
-        <v>3.1111111111111112</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12">
-      <c r="A77" t="s">
-        <v>2</v>
-      </c>
-      <c r="B77" t="s">
-        <v>6</v>
-      </c>
-      <c r="C77" t="s">
-        <v>34</v>
-      </c>
-      <c r="D77" t="s">
-        <v>16</v>
-      </c>
-      <c r="E77" t="s">
-        <v>40</v>
-      </c>
-      <c r="F77" t="s">
-        <v>38</v>
-      </c>
-      <c r="G77">
-        <v>2021</v>
-      </c>
-      <c r="H77" t="s">
-        <v>48</v>
-      </c>
-      <c r="I77" s="18">
-        <v>2.9629629629629624</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12">
-      <c r="A78" t="s">
-        <v>2</v>
-      </c>
-      <c r="B78" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" t="s">
-        <v>35</v>
-      </c>
-      <c r="D78" t="s">
-        <v>16</v>
-      </c>
-      <c r="E78" t="s">
-        <v>40</v>
-      </c>
-      <c r="F78" t="s">
-        <v>38</v>
-      </c>
-      <c r="G78">
-        <v>2021</v>
-      </c>
-      <c r="H78" t="s">
-        <v>48</v>
-      </c>
-      <c r="I78">
-        <v>2.4444444444444446</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12">
-      <c r="A79" t="s">
-        <v>2</v>
-      </c>
-      <c r="B79" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" t="s">
-        <v>36</v>
-      </c>
-      <c r="D79" t="s">
-        <v>16</v>
-      </c>
-      <c r="E79" t="s">
-        <v>40</v>
-      </c>
-      <c r="F79" t="s">
-        <v>38</v>
-      </c>
-      <c r="G79">
-        <v>2021</v>
-      </c>
-      <c r="H79" t="s">
-        <v>48</v>
-      </c>
-      <c r="I79">
-        <v>1.7037037037037035</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12">
-      <c r="A80" t="s">
-        <v>2</v>
-      </c>
-      <c r="B80" t="s">
-        <v>6</v>
-      </c>
-      <c r="C80" t="s">
-        <v>26</v>
-      </c>
-      <c r="D80" t="s">
-        <v>17</v>
-      </c>
-      <c r="E80" t="s">
-        <v>27</v>
-      </c>
-      <c r="F80" t="s">
-        <v>28</v>
-      </c>
-      <c r="G80">
-        <v>2021</v>
-      </c>
-      <c r="H80" t="s">
-        <v>48</v>
-      </c>
-      <c r="I80" s="21">
-        <v>0.9796126401630989</v>
-      </c>
-      <c r="J80" s="17"/>
-      <c r="K80" s="17"/>
-      <c r="L80" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12">
-      <c r="A81" t="s">
-        <v>2</v>
-      </c>
-      <c r="B81" t="s">
-        <v>6</v>
-      </c>
-      <c r="C81" t="s">
-        <v>31</v>
-      </c>
-      <c r="D81" t="s">
-        <v>17</v>
-      </c>
-      <c r="E81" t="s">
-        <v>27</v>
-      </c>
-      <c r="F81" t="s">
-        <v>28</v>
-      </c>
-      <c r="G81">
-        <v>2021</v>
-      </c>
-      <c r="H81" t="s">
-        <v>48</v>
-      </c>
-      <c r="I81" s="17">
-        <v>0.96573208722741444</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12">
-      <c r="A82" t="s">
-        <v>2</v>
-      </c>
-      <c r="B82" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82" t="s">
-        <v>33</v>
-      </c>
-      <c r="D82" t="s">
-        <v>17</v>
-      </c>
-      <c r="E82" t="s">
-        <v>27</v>
-      </c>
-      <c r="F82" t="s">
-        <v>28</v>
-      </c>
-      <c r="G82">
-        <v>2021</v>
-      </c>
-      <c r="H82" t="s">
-        <v>48</v>
-      </c>
-      <c r="I82" s="7">
-        <v>0.9785932721712538</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12">
-      <c r="A83" t="s">
-        <v>2</v>
-      </c>
-      <c r="B83" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83" t="s">
-        <v>34</v>
-      </c>
-      <c r="D83" t="s">
-        <v>17</v>
-      </c>
-      <c r="E83" t="s">
-        <v>27</v>
-      </c>
-      <c r="F83" t="s">
-        <v>28</v>
-      </c>
-      <c r="G83">
-        <v>2021</v>
-      </c>
-      <c r="H83" t="s">
-        <v>48</v>
-      </c>
-      <c r="I83" s="20">
-        <v>0.98084677419354838</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12">
-      <c r="A84" t="s">
-        <v>2</v>
-      </c>
-      <c r="B84" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" t="s">
-        <v>35</v>
-      </c>
-      <c r="D84" t="s">
-        <v>17</v>
-      </c>
-      <c r="E84" t="s">
-        <v>27</v>
-      </c>
-      <c r="F84" t="s">
-        <v>28</v>
-      </c>
-      <c r="G84">
-        <v>2021</v>
-      </c>
-      <c r="H84" t="s">
-        <v>48</v>
-      </c>
-      <c r="I84" s="7">
-        <v>0.98884381338742389</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12">
-      <c r="A85" t="s">
-        <v>2</v>
-      </c>
-      <c r="B85" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" t="s">
-        <v>36</v>
-      </c>
-      <c r="D85" t="s">
-        <v>17</v>
-      </c>
-      <c r="E85" t="s">
-        <v>27</v>
-      </c>
-      <c r="F85" t="s">
-        <v>28</v>
-      </c>
-      <c r="G85">
-        <v>2021</v>
-      </c>
-      <c r="H85" t="s">
-        <v>48</v>
-      </c>
-      <c r="I85" s="20">
-        <v>0.98377281947261663</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12">
-      <c r="A86" t="s">
-        <v>3</v>
-      </c>
-      <c r="B86" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" t="s">
-        <v>26</v>
-      </c>
-      <c r="D86" t="s">
-        <v>17</v>
-      </c>
-      <c r="E86" t="s">
-        <v>27</v>
-      </c>
-      <c r="F86" t="s">
-        <v>28</v>
-      </c>
-      <c r="G86">
+        <v>29</v>
+      </c>
+      <c r="G65" t="s">
+        <v>30</v>
+      </c>
+      <c r="H65">
         <v>2024</v>
       </c>
-      <c r="H86" t="s">
-        <v>76</v>
-      </c>
-      <c r="I86" s="21">
+      <c r="I65" t="s">
+        <v>81</v>
+      </c>
+      <c r="J65" s="21">
         <v>0.51300000000000001</v>
       </c>
-      <c r="L86" t="s">
-        <v>77</v>
+      <c r="M65" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:C1" xr:uid="{E441A666-11EF-40F7-A6AA-2528D8D84D13}"/>
+  <dataValidations count="5">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:B1" xr:uid="{E441A666-11EF-40F7-A6AA-2528D8D84D13}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{01C8494E-7753-4018-8855-0065C3105F7C}">
+      <formula1>"All (assumed same),Total,Lowest,Second,Middle,Fourth,Highest"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576" xr:uid="{4703F569-7426-4F3E-8C55-3036695499EA}">
       <formula1>"Nigeria,Ethiopia,India"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{BCD02A3B-B123-4319-A864-E9F403043D84}">
       <formula1>"Bouillon,Salt,Rice"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{9D6075CA-7D74-4E4D-8B56-0DD52E93158E}">
-      <formula1>"All,Lowest,Second,Middle,Fourth,Highest"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{B90BD4BA-C5F9-49E4-AC00-AAF7476800DC}">
+      <formula1>"All (assumed same),Total,Female,Male"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="L44" r:id="rId1" xr:uid="{43FE6AF0-C443-4A48-A269-5B73EB396FB6}"/>
-    <hyperlink ref="L14" r:id="rId2" xr:uid="{57C7F0B9-B50C-49CF-A5F5-C51B2423D2C4}"/>
-    <hyperlink ref="L32" r:id="rId3" xr:uid="{1650080F-1085-40E4-8BD5-886F921DD675}"/>
+    <hyperlink ref="M19" r:id="rId1" xr:uid="{43FE6AF0-C443-4A48-A269-5B73EB396FB6}"/>
+    <hyperlink ref="M9" r:id="rId2" xr:uid="{57C7F0B9-B50C-49CF-A5F5-C51B2423D2C4}"/>
+    <hyperlink ref="M17" r:id="rId3" xr:uid="{1650080F-1085-40E4-8BD5-886F921DD675}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -5178,7 +4894,7 @@
           <x14:formula1>
             <xm:f>'Country-Vehicle Progress'!$A$5:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D1048576</xm:sqref>
+          <xm:sqref>E2:E1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5247,30 +4963,30 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C3" s="32"/>
       <c r="D3" s="32" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E3" s="32"/>
       <c r="F3" s="32" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G3" s="32"/>
       <c r="H3" s="32" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I3" s="32"/>
       <c r="J3" s="32" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K3" s="32"/>
       <c r="L3" s="32" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="M3" s="32"/>
     </row>
@@ -5328,32 +5044,32 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H6" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$973, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$973, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$973, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$973, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$973, $A6, 'Country-Vehicle-Fort Extraction'!$J$2:$J$973, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Complete</v>
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$938, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$938, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$938, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$938, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$938, $A6, 'Country-Vehicle-Fort Extraction'!$J$2:$J$938, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Missing</v>
       </c>
       <c r="I6" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$973, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$973, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$973, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$973, "&lt;&gt;All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$973, $A6, 'Country-Vehicle-Fort Extraction'!$J$2:$J$973, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$938, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$938, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$938, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$938, "&lt;&gt;All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$938, $A6, 'Country-Vehicle-Fort Extraction'!$J$2:$J$938, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="J6" t="s">
@@ -5371,47 +5087,47 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F7" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$973, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$973, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$973, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$973, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$973, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$973, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Complete</v>
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$938, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$938, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$938, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$938, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$938, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$938, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Missing</v>
       </c>
       <c r="I7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$973, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$973, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$973, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$973, "&lt;&gt;All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$973, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$973, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
-        <v>Complete</v>
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$938, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$938, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$938, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$938, "&lt;&gt;All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$938, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$938, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
+        <v>Missing</v>
       </c>
       <c r="J7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$973, J$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$973, J$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$973, J$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$973, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$973, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$973, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Complete</v>
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$938, J$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$938, J$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$938, J$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$938, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$938, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$938, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Missing</v>
       </c>
       <c r="K7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="L7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$973, J$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$973, J$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$973, L$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$973, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$973, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$973, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Complete</v>
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$938, J$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$938, J$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$938, L$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$938, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$938, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$938, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Missing</v>
       </c>
       <c r="M7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -5440,11 +5156,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC26D125-533B-4E2C-8B10-83B96EF6CBCB}">
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="52.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -5459,7 +5176,7 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>10</v>
@@ -5468,25 +5185,25 @@
         <v>11</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -5497,22 +5214,22 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J2" s="7">
         <v>0</v>
@@ -5526,1419 +5243,370 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="I3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" s="7">
+        <v>47</v>
+      </c>
+      <c r="J3" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J4" s="7">
-        <v>0</v>
+        <v>0.61875637104994907</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J5" s="7">
-        <v>0</v>
-      </c>
+        <v>0.51921079958463134</v>
+      </c>
+      <c r="L5" s="9"/>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J6" s="7">
-        <v>0</v>
-      </c>
+        <v>0.58409785932721714</v>
+      </c>
+      <c r="L6" s="9"/>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J7" s="7">
-        <v>0</v>
-      </c>
+        <v>0.63810483870967738</v>
+      </c>
+      <c r="L7" s="9"/>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="I8" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" s="10">
-        <v>0</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0.66937119675456391</v>
+      </c>
+      <c r="L8" s="9"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="I9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" s="10">
-        <v>0</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0.69979716024340777</v>
+      </c>
+      <c r="L9" s="9"/>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F10" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J10" s="10">
-        <v>0</v>
+        <v>650</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="I11" t="s">
-        <v>43</v>
-      </c>
-      <c r="J11" s="10">
+        <v>47</v>
+      </c>
+      <c r="J11" s="7">
         <v>0</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F12" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I12" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J12" s="10">
         <v>0</v>
       </c>
+      <c r="L12" s="9"/>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F13" t="s">
-        <v>86</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>87</v>
+        <v>91</v>
+      </c>
+      <c r="G13" t="s">
+        <v>92</v>
       </c>
       <c r="I13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J13" s="10">
-        <v>0</v>
+        <v>96</v>
+      </c>
+      <c r="J13">
+        <v>42.5</v>
+      </c>
+      <c r="L13" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F14" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>28</v>
+        <v>91</v>
+      </c>
+      <c r="G14" t="s">
+        <v>92</v>
       </c>
       <c r="I14" t="s">
-        <v>43</v>
-      </c>
-      <c r="J14" s="7">
-        <v>0.61875637104994907</v>
+        <v>96</v>
+      </c>
+      <c r="J14">
+        <v>0.125</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" t="s">
-        <v>81</v>
-      </c>
-      <c r="F15" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I15" t="s">
-        <v>43</v>
-      </c>
-      <c r="J15" s="7">
-        <v>0.51921079958463134</v>
-      </c>
-      <c r="L15" s="9"/>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" t="s">
-        <v>2</v>
-      </c>
-      <c r="B16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" t="s">
-        <v>81</v>
-      </c>
-      <c r="F16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" t="s">
-        <v>43</v>
-      </c>
-      <c r="J16" s="7">
-        <v>0.58409785932721714</v>
-      </c>
-      <c r="L16" s="9"/>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" t="s">
-        <v>2</v>
-      </c>
-      <c r="B17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" t="s">
-        <v>81</v>
-      </c>
-      <c r="F17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" t="s">
-        <v>43</v>
-      </c>
-      <c r="J17" s="7">
-        <v>0.63810483870967738</v>
-      </c>
-      <c r="L17" s="9"/>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" t="s">
-        <v>81</v>
-      </c>
-      <c r="F18" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" t="s">
-        <v>43</v>
-      </c>
-      <c r="J18" s="7">
-        <v>0.66937119675456391</v>
-      </c>
-      <c r="L18" s="9"/>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" t="s">
-        <v>2</v>
-      </c>
-      <c r="B19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" t="s">
-        <v>81</v>
-      </c>
-      <c r="F19" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" t="s">
-        <v>43</v>
-      </c>
-      <c r="J19" s="7">
-        <v>0.69979716024340777</v>
-      </c>
-      <c r="L19" s="9"/>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" t="s">
-        <v>2</v>
-      </c>
-      <c r="B20" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20" t="s">
-        <v>86</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I20" t="s">
-        <v>43</v>
-      </c>
-      <c r="J20" s="10">
-        <v>525</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" t="s">
-        <v>2</v>
-      </c>
-      <c r="B21" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" t="s">
-        <v>84</v>
-      </c>
-      <c r="F21" t="s">
-        <v>86</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I21" t="s">
-        <v>43</v>
-      </c>
-      <c r="J21" s="10">
-        <v>525</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" t="s">
-        <v>2</v>
-      </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" t="s">
-        <v>84</v>
-      </c>
-      <c r="F22" t="s">
-        <v>86</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I22" t="s">
-        <v>43</v>
-      </c>
-      <c r="J22" s="10">
-        <v>525</v>
-      </c>
-      <c r="L22" s="9"/>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" t="s">
-        <v>2</v>
-      </c>
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" t="s">
-        <v>34</v>
-      </c>
-      <c r="E23" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" t="s">
-        <v>86</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I23" t="s">
-        <v>43</v>
-      </c>
-      <c r="J23" s="10">
-        <v>525</v>
-      </c>
-      <c r="L23" s="9"/>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" t="s">
-        <v>2</v>
-      </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" t="s">
-        <v>80</v>
-      </c>
-      <c r="D24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" t="s">
-        <v>84</v>
-      </c>
-      <c r="F24" t="s">
-        <v>86</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I24" t="s">
-        <v>43</v>
-      </c>
-      <c r="J24" s="10">
-        <v>525</v>
-      </c>
-      <c r="L24" s="9"/>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" t="s">
-        <v>2</v>
-      </c>
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" t="s">
-        <v>84</v>
-      </c>
-      <c r="F25" t="s">
-        <v>86</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I25" t="s">
-        <v>43</v>
-      </c>
-      <c r="J25" s="10">
-        <v>525</v>
-      </c>
-      <c r="L25" s="9"/>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" t="s">
-        <v>2</v>
-      </c>
-      <c r="B26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" t="s">
-        <v>81</v>
-      </c>
-      <c r="F26" t="s">
-        <v>27</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I26" t="s">
-        <v>43</v>
-      </c>
-      <c r="J26" s="7">
-        <v>0</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" t="s">
-        <v>2</v>
-      </c>
-      <c r="B27" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F27" t="s">
-        <v>27</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I27" t="s">
-        <v>43</v>
-      </c>
-      <c r="J27" s="7">
-        <v>0</v>
-      </c>
-      <c r="L27" s="9"/>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" t="s">
-        <v>33</v>
-      </c>
-      <c r="E28" t="s">
-        <v>81</v>
-      </c>
-      <c r="F28" t="s">
-        <v>27</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28" t="s">
-        <v>43</v>
-      </c>
-      <c r="J28" s="7">
-        <v>0</v>
-      </c>
-      <c r="L28" s="9"/>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" t="s">
-        <v>2</v>
-      </c>
-      <c r="B29" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29" t="s">
-        <v>34</v>
-      </c>
-      <c r="E29" t="s">
-        <v>81</v>
-      </c>
-      <c r="F29" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I29" t="s">
-        <v>43</v>
-      </c>
-      <c r="J29" s="7">
-        <v>0</v>
-      </c>
-      <c r="L29" s="9"/>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" t="s">
-        <v>2</v>
-      </c>
-      <c r="B30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" t="s">
-        <v>79</v>
-      </c>
-      <c r="D30" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" t="s">
-        <v>81</v>
-      </c>
-      <c r="F30" t="s">
-        <v>27</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I30" t="s">
-        <v>43</v>
-      </c>
-      <c r="J30" s="7">
-        <v>0</v>
-      </c>
-      <c r="L30" s="9"/>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" t="s">
-        <v>2</v>
-      </c>
-      <c r="B31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" t="s">
-        <v>79</v>
-      </c>
-      <c r="D31" t="s">
-        <v>36</v>
-      </c>
-      <c r="E31" t="s">
-        <v>81</v>
-      </c>
-      <c r="F31" t="s">
-        <v>27</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I31" t="s">
-        <v>43</v>
-      </c>
-      <c r="J31" s="7">
-        <v>0</v>
-      </c>
-      <c r="L31" s="9"/>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" t="s">
-        <v>2</v>
-      </c>
-      <c r="B32" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" t="s">
-        <v>84</v>
-      </c>
-      <c r="F32" t="s">
-        <v>86</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I32" t="s">
-        <v>43</v>
-      </c>
-      <c r="J32" s="10">
-        <v>0</v>
-      </c>
-      <c r="L32" s="9"/>
-    </row>
-    <row r="33" spans="1:12">
-      <c r="A33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" t="s">
-        <v>79</v>
-      </c>
-      <c r="D33" t="s">
-        <v>31</v>
-      </c>
-      <c r="E33" t="s">
-        <v>84</v>
-      </c>
-      <c r="F33" t="s">
-        <v>86</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I33" t="s">
-        <v>43</v>
-      </c>
-      <c r="J33" s="10">
-        <v>0</v>
-      </c>
-      <c r="L33" s="9"/>
-    </row>
-    <row r="34" spans="1:12">
-      <c r="A34" t="s">
-        <v>2</v>
-      </c>
-      <c r="B34" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" t="s">
-        <v>79</v>
-      </c>
-      <c r="D34" t="s">
-        <v>33</v>
-      </c>
-      <c r="E34" t="s">
-        <v>84</v>
-      </c>
-      <c r="F34" t="s">
-        <v>86</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I34" t="s">
-        <v>43</v>
-      </c>
-      <c r="J34" s="10">
-        <v>0</v>
-      </c>
-      <c r="L34" s="9"/>
-    </row>
-    <row r="35" spans="1:12">
-      <c r="A35" t="s">
-        <v>2</v>
-      </c>
-      <c r="B35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35" t="s">
-        <v>34</v>
-      </c>
-      <c r="E35" t="s">
-        <v>84</v>
-      </c>
-      <c r="F35" t="s">
-        <v>86</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I35" t="s">
-        <v>43</v>
-      </c>
-      <c r="J35" s="10">
-        <v>0</v>
-      </c>
-      <c r="L35" s="9"/>
-    </row>
-    <row r="36" spans="1:12">
-      <c r="A36" t="s">
-        <v>2</v>
-      </c>
-      <c r="B36" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" t="s">
-        <v>79</v>
-      </c>
-      <c r="D36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E36" t="s">
-        <v>84</v>
-      </c>
-      <c r="F36" t="s">
-        <v>86</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I36" t="s">
-        <v>43</v>
-      </c>
-      <c r="J36" s="10">
-        <v>0</v>
-      </c>
-      <c r="L36" s="9"/>
-    </row>
-    <row r="37" spans="1:12">
-      <c r="A37" t="s">
-        <v>2</v>
-      </c>
-      <c r="B37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" t="s">
-        <v>79</v>
-      </c>
-      <c r="D37" t="s">
-        <v>36</v>
-      </c>
-      <c r="E37" t="s">
-        <v>84</v>
-      </c>
-      <c r="F37" t="s">
-        <v>86</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I37" t="s">
-        <v>43</v>
-      </c>
-      <c r="J37" s="10">
-        <v>0</v>
-      </c>
-      <c r="L37" s="9"/>
-    </row>
-    <row r="38" spans="1:12">
-      <c r="A38" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" t="s">
-        <v>84</v>
-      </c>
-      <c r="F38" t="s">
-        <v>86</v>
-      </c>
-      <c r="G38" t="s">
-        <v>87</v>
-      </c>
-      <c r="I38" t="s">
-        <v>92</v>
-      </c>
-      <c r="J38">
-        <v>42.5</v>
-      </c>
-      <c r="L38" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12">
-      <c r="A39" t="s">
-        <v>3</v>
-      </c>
-      <c r="B39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" t="s">
-        <v>31</v>
-      </c>
-      <c r="E39" t="s">
-        <v>84</v>
-      </c>
-      <c r="F39" t="s">
-        <v>86</v>
-      </c>
-      <c r="G39" t="s">
-        <v>87</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J39">
-        <v>42.5</v>
-      </c>
-      <c r="L39" s="9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12">
-      <c r="A40" t="s">
-        <v>3</v>
-      </c>
-      <c r="B40" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E40" t="s">
-        <v>84</v>
-      </c>
-      <c r="F40" t="s">
-        <v>86</v>
-      </c>
-      <c r="G40" t="s">
-        <v>87</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J40">
-        <v>42.5</v>
-      </c>
-      <c r="L40" s="9"/>
-    </row>
-    <row r="41" spans="1:12">
-      <c r="A41" t="s">
-        <v>3</v>
-      </c>
-      <c r="B41" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" t="s">
-        <v>80</v>
-      </c>
-      <c r="D41" t="s">
-        <v>34</v>
-      </c>
-      <c r="E41" t="s">
-        <v>84</v>
-      </c>
-      <c r="F41" t="s">
-        <v>86</v>
-      </c>
-      <c r="G41" t="s">
-        <v>87</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J41">
-        <v>42.5</v>
-      </c>
-      <c r="L41" s="9"/>
-    </row>
-    <row r="42" spans="1:12">
-      <c r="A42" t="s">
-        <v>3</v>
-      </c>
-      <c r="B42" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" t="s">
-        <v>80</v>
-      </c>
-      <c r="D42" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" t="s">
-        <v>84</v>
-      </c>
-      <c r="F42" t="s">
-        <v>86</v>
-      </c>
-      <c r="G42" t="s">
-        <v>87</v>
-      </c>
-      <c r="I42" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J42">
-        <v>42.5</v>
-      </c>
-      <c r="L42" s="9"/>
-    </row>
-    <row r="43" spans="1:12">
-      <c r="A43" t="s">
-        <v>3</v>
-      </c>
-      <c r="B43" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" t="s">
-        <v>80</v>
-      </c>
-      <c r="D43" t="s">
-        <v>36</v>
-      </c>
-      <c r="E43" t="s">
-        <v>84</v>
-      </c>
-      <c r="F43" t="s">
-        <v>86</v>
-      </c>
-      <c r="G43" t="s">
-        <v>87</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J43">
-        <v>42.5</v>
-      </c>
-      <c r="L43" s="9"/>
-    </row>
-    <row r="44" spans="1:12">
-      <c r="A44" t="s">
-        <v>3</v>
-      </c>
-      <c r="B44" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" t="s">
-        <v>79</v>
-      </c>
-      <c r="D44" t="s">
-        <v>26</v>
-      </c>
-      <c r="E44" t="s">
-        <v>84</v>
-      </c>
-      <c r="F44" t="s">
-        <v>86</v>
-      </c>
-      <c r="G44" t="s">
-        <v>87</v>
-      </c>
-      <c r="I44" t="s">
-        <v>92</v>
-      </c>
-      <c r="J44">
-        <v>0.125</v>
-      </c>
-      <c r="L44" s="9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12">
-      <c r="A45" t="s">
-        <v>3</v>
-      </c>
-      <c r="B45" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" t="s">
-        <v>79</v>
-      </c>
-      <c r="D45" t="s">
-        <v>31</v>
-      </c>
-      <c r="E45" t="s">
-        <v>84</v>
-      </c>
-      <c r="F45" t="s">
-        <v>86</v>
-      </c>
-      <c r="G45" t="s">
-        <v>87</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J45">
-        <v>0.125</v>
-      </c>
-      <c r="L45" s="9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12">
-      <c r="A46" t="s">
-        <v>3</v>
-      </c>
-      <c r="B46" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" t="s">
-        <v>79</v>
-      </c>
-      <c r="D46" t="s">
-        <v>33</v>
-      </c>
-      <c r="E46" t="s">
-        <v>84</v>
-      </c>
-      <c r="F46" t="s">
-        <v>86</v>
-      </c>
-      <c r="G46" t="s">
-        <v>87</v>
-      </c>
-      <c r="I46" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J46">
-        <v>0.125</v>
-      </c>
-      <c r="L46" s="9"/>
-    </row>
-    <row r="47" spans="1:12">
-      <c r="A47" t="s">
-        <v>3</v>
-      </c>
-      <c r="B47" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" t="s">
-        <v>79</v>
-      </c>
-      <c r="D47" t="s">
-        <v>34</v>
-      </c>
-      <c r="E47" t="s">
-        <v>84</v>
-      </c>
-      <c r="F47" t="s">
-        <v>86</v>
-      </c>
-      <c r="G47" t="s">
-        <v>87</v>
-      </c>
-      <c r="I47" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J47">
-        <v>0.125</v>
-      </c>
-      <c r="L47" s="9"/>
-    </row>
-    <row r="48" spans="1:12">
-      <c r="A48" t="s">
-        <v>3</v>
-      </c>
-      <c r="B48" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" t="s">
-        <v>79</v>
-      </c>
-      <c r="D48" t="s">
-        <v>35</v>
-      </c>
-      <c r="E48" t="s">
-        <v>84</v>
-      </c>
-      <c r="F48" t="s">
-        <v>86</v>
-      </c>
-      <c r="G48" t="s">
-        <v>87</v>
-      </c>
-      <c r="I48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J48">
-        <v>0.125</v>
-      </c>
-      <c r="L48" s="9"/>
-    </row>
-    <row r="49" spans="1:12">
-      <c r="A49" t="s">
-        <v>3</v>
-      </c>
-      <c r="B49" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" t="s">
-        <v>79</v>
-      </c>
-      <c r="D49" t="s">
-        <v>36</v>
-      </c>
-      <c r="E49" t="s">
-        <v>84</v>
-      </c>
-      <c r="F49" t="s">
-        <v>86</v>
-      </c>
-      <c r="G49" t="s">
-        <v>87</v>
-      </c>
-      <c r="I49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J49">
-        <v>0.125</v>
-      </c>
-      <c r="L49" s="9"/>
+        <v>98</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:B1 D1" xr:uid="{9985B5D0-2CB3-40F4-BBCF-DD35FD2F4902}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{D186C371-0E74-48C9-B141-A7799B8ADFB8}">
-      <formula1>"All,Lowest,Second,Middle,Fourth,Highest"</formula1>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:B1" xr:uid="{9985B5D0-2CB3-40F4-BBCF-DD35FD2F4902}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{44CBE152-7074-417E-B67D-9B79208CCBB6}">
       <formula1>"Bouillon,Salt,Rice"</formula1>
     </dataValidation>
@@ -6947,6 +5615,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576" xr:uid="{ECE251AE-F610-4F87-83BC-7241E0D9DF39}">
       <formula1>"Nigeria,Ethiopia,India"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{2F700A34-1ECA-4D69-A428-33E0DFA6A819}">
+      <formula1>"All (assumed same),Total,Lowest,Second,Middle,Fourth,Highest"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6994,7 +5665,7 @@
       </c>
       <c r="G1" s="33"/>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -7030,30 +5701,30 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B5" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$2:$A$980, B$1,  'Country Extraction'!$B$2:$B$980, "All",  'Country Extraction'!$C$2:$C$980, $A5) = 0, "Missing", "Complete")</f>
@@ -7082,7 +5753,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B6" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$2:$A$980, B$1,  'Country Extraction'!$B$2:$B$980, "All",  'Country Extraction'!$C$2:$C$980, $A6) = 0, "Missing", "Complete")</f>
@@ -7111,226 +5782,226 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F7" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" t="s">
         <v>102</v>
-      </c>
-      <c r="B7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E7" t="s">
-        <v>98</v>
-      </c>
-      <c r="F7" t="s">
-        <v>97</v>
-      </c>
-      <c r="G7" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F9" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E10" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$1:$A$995, F$1, 'Country Extraction'!$B$1:$B$995, "&lt;&gt;All", 'Country Extraction'!$C$1:$C$995, $A10, 'Country Extraction'!$H$1:$H$995, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="F10" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G10" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$1:$A$995, H$1, 'Country Extraction'!$B$1:$B$995, "&lt;&gt;All", 'Country Extraction'!$C$1:$C$995, $A10, 'Country Extraction'!$H$1:$H$995, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E11" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$1:$A$995, F$1, 'Country Extraction'!$B$1:$B$995, "&lt;&gt;All", 'Country Extraction'!$C$1:$C$995, $A11, 'Country Extraction'!$H$1:$H$995, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="F11" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H11" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F12" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H13" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F14" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G14" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H14" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C15" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$1:$A$995, D$1, 'Country Extraction'!$B$1:$B$995, "&lt;&gt;All", 'Country Extraction'!$C$1:$C$995, $A15, 'Country Extraction'!$H$1:$H$995, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E15" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$1:$A$995, F$1, 'Country Extraction'!$B$1:$B$995, "&lt;&gt;All", 'Country Extraction'!$C$1:$C$995, $A15, 'Country Extraction'!$H$1:$H$995, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="F15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G15" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$1:$A$995, H$1, 'Country Extraction'!$B$1:$B$995, "&lt;&gt;All", 'Country Extraction'!$C$1:$C$995, $A15, 'Country Extraction'!$H$1:$H$995, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
@@ -7375,25 +6046,25 @@
         <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.75">
@@ -7401,19 +6072,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="32.25" customHeight="1">
@@ -7421,19 +6092,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -7441,16 +6112,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -7458,16 +6129,16 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -7475,16 +6146,16 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G6" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -7492,118 +6163,118 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G7" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>116</v>
-      </c>
       <c r="E8" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G8" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>116</v>
-      </c>
       <c r="E9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>116</v>
-      </c>
       <c r="E10" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G10" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>116</v>
-      </c>
       <c r="E11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>116</v>
-      </c>
       <c r="E12" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G12" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>116</v>
-      </c>
       <c r="E13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -7611,16 +6282,16 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E14" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G14" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -7628,16 +6299,16 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E15" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G15" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -7645,16 +6316,16 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E16" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G16" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -7662,16 +6333,16 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G17" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -7679,16 +6350,16 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G18" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -7696,16 +6367,16 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E19" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G19" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.75">
@@ -7713,19 +6384,19 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="C20" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G20" t="s">
         <v>121</v>
       </c>
-      <c r="E20" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G20" t="s">
-        <v>117</v>
-      </c>
       <c r="J20" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -7733,19 +6404,19 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C21" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G21" t="s">
         <v>121</v>
       </c>
-      <c r="E21" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G21" t="s">
-        <v>117</v>
-      </c>
       <c r="J21" s="8" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -7753,16 +6424,16 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C22" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G22" t="s">
         <v>121</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G22" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -7770,16 +6441,16 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C23" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G23" t="s">
         <v>121</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G23" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -7787,16 +6458,16 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C24" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G24" t="s">
         <v>121</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G24" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -7804,118 +6475,118 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C25" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G25" t="s">
         <v>121</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G25" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="C26" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G26" t="s">
         <v>121</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G26" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C27" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" t="s">
         <v>121</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G27" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C28" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G28" t="s">
         <v>121</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G28" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C29" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G29" t="s">
         <v>121</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G29" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C30" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G30" t="s">
         <v>121</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G30" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C31" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G31" t="s">
         <v>121</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G31" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -7923,16 +6594,16 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="C32" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G32" t="s">
         <v>121</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G32" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -7940,16 +6611,16 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C33" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G33" t="s">
         <v>121</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G33" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -7957,16 +6628,16 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C34" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G34" t="s">
         <v>121</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G34" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -7974,16 +6645,16 @@
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C35" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G35" t="s">
         <v>121</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G35" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -7991,16 +6662,16 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C36" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G36" t="s">
         <v>121</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G36" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -8008,16 +6679,16 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C37" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G37" t="s">
         <v>121</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G37" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -8025,13 +6696,13 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -8039,13 +6710,13 @@
         <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -8053,13 +6724,13 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -8067,13 +6738,13 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -8081,13 +6752,13 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -8095,97 +6766,97 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B45" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G45" s="14" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B46" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B47" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B48" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B49" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -8193,13 +6864,13 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -8207,13 +6878,13 @@
         <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G51" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -8221,13 +6892,13 @@
         <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G52" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -8235,13 +6906,13 @@
         <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G53" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -8249,13 +6920,13 @@
         <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G54" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -8263,13 +6934,13 @@
         <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G55" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -8277,13 +6948,13 @@
         <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="C56" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G56" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="45">
@@ -8291,13 +6962,13 @@
         <v>1</v>
       </c>
       <c r="B57" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15.75">
@@ -8305,13 +6976,13 @@
         <v>1</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C58" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="15.75">
@@ -8319,10 +6990,10 @@
         <v>1</v>
       </c>
       <c r="B59" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C59" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="J59" s="12"/>
     </row>
@@ -8331,10 +7002,10 @@
         <v>1</v>
       </c>
       <c r="B60" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -8342,79 +7013,79 @@
         <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C61" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="C62" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G62" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B63" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C63" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B64" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C64" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B65" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C65" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B66" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C66" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B67" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C67" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -8422,13 +7093,13 @@
         <v>3</v>
       </c>
       <c r="B68" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="C68" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G68" s="15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -8436,10 +7107,10 @@
         <v>3</v>
       </c>
       <c r="B69" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C69" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -8447,10 +7118,10 @@
         <v>3</v>
       </c>
       <c r="B70" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C70" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -8458,10 +7129,10 @@
         <v>3</v>
       </c>
       <c r="B71" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C71" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -8469,10 +7140,10 @@
         <v>3</v>
       </c>
       <c r="B72" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C72" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -8480,10 +7151,10 @@
         <v>3</v>
       </c>
       <c r="B73" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C73" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="30">
@@ -8491,36 +7162,36 @@
         <v>1</v>
       </c>
       <c r="B74" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="C74" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D74" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G74" s="12" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="J74" s="14" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B75" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="C75" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D75" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="J75" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -8528,23 +7199,23 @@
         <v>3</v>
       </c>
       <c r="B76" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="C76" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D76" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:B1" xr:uid="{BFAED2E7-42FF-47EE-A350-515996667CA3}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1" xr:uid="{BFAED2E7-42FF-47EE-A350-515996667CA3}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576" xr:uid="{765137EE-2B5F-4BF2-8796-3258E42F6754}">
       <formula1>"Nigeria,Ethiopia,India"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{AF50A314-33A5-4CDD-B699-9855AF398BFC}">
-      <formula1>"All,Lowest,Second,Middle,Fourth,Highest"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{BB07608A-2826-4857-9323-F84A772BA92F}">
+      <formula1>"All (assumed same),Total,Lowest,Second,Middle,Fourth,Highest"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -8598,7 +7269,7 @@
         <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8610,10 +7281,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C3" t="str">
         <f>IF(COUNTIFS('Vehicle Extraction'!$A$2:$A$904, C$1,  'Vehicle Extraction'!$B$2:$B$904, $A3) = 0, "Missing", "Complete")</f>
@@ -8626,10 +7297,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C4" t="str">
         <f>IF(COUNTIFS('Vehicle Extraction'!$A$2:$A$904, C$1,  'Vehicle Extraction'!$B$2:$B$904, $A4) = 0, "Missing", "Complete")</f>
@@ -8671,25 +7342,25 @@
         <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="115.5">
@@ -8697,28 +7368,28 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G2" s="26">
         <v>3.25</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -8726,28 +7397,28 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E3">
         <v>2021</v>
       </c>
       <c r="F3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G3">
         <v>4.4000000000000004</v>
       </c>
       <c r="H3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -8755,28 +7426,28 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E4">
         <v>2012</v>
       </c>
       <c r="F4" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G4">
         <v>4.2</v>
       </c>
       <c r="H4" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -8784,28 +7455,28 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D5" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E5">
         <v>2013</v>
       </c>
       <c r="F5" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G5">
         <v>16.7</v>
       </c>
       <c r="H5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -8813,28 +7484,28 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E6">
         <v>2013</v>
       </c>
       <c r="F6" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G6">
         <v>16.7</v>
       </c>
       <c r="H6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -8882,31 +7553,31 @@
         <v>11</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H1" s="22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="26" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -8919,59 +7590,59 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="26" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D3" s="26">
         <v>2018</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F3" s="26">
         <v>4.3</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I3" s="23"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="26" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D4" s="26">
         <v>2015</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F4" s="26">
         <v>6</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H4" s="23"/>
       <c r="I4" s="23"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="26" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B5" s="26"/>
       <c r="C5" s="26"/>
@@ -8984,18 +7655,18 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="26" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G6" s="26"/>
       <c r="H6" s="23"/>
@@ -9003,18 +7674,18 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="26" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
       <c r="E7" s="26" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G7" s="26"/>
       <c r="H7" s="23"/>
@@ -9022,22 +7693,22 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="26" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
       <c r="E8" s="26" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="23" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="I8" s="23"/>
     </row>

--- a/legacy/vivarium_gates_lsff_by_wealth_quintile/0100_data_prep/extraction/Data Extraction Sheet.xlsx
+++ b/legacy/vivarium_gates_lsff_by_wealth_quintile/0100_data_prep/extraction/Data Extraction Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwnetid.sharepoint.com/sites/ihme_simulation_science_team/Shared Documents/Research/LSFF/04_Concept_Model_Development/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F747A906-2511-4A82-8D98-7291795813F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC6D7F9C-56D5-4A5D-BAA4-9192B6B9B393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Country-Vehicle Progress" sheetId="1" r:id="rId1"/>
@@ -543,7 +543,7 @@
     <t>https://www.sciencedirect.com/science/article/pii/S0002916523028915; could not find anything bouillon-specific</t>
   </si>
   <si>
-    <t>g/(mcg/person-day)</t>
+    <t>g/(mg/person-day)</t>
   </si>
   <si>
     <t>Anaemia, prenatal iron use, and risk of adverse pregnancy outcomes: systematic review and meta-analysis</t>

--- a/legacy/vivarium_gates_lsff_by_wealth_quintile/0100_data_prep/extraction/Data Extraction Sheet.xlsx
+++ b/legacy/vivarium_gates_lsff_by_wealth_quintile/0100_data_prep/extraction/Data Extraction Sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27930"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwnetid.sharepoint.com/sites/ihme_simulation_science_team/Shared Documents/Research/LSFF/04_Concept_Model_Development/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC6D7F9C-56D5-4A5D-BAA4-9192B6B9B393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F48EAE2D-6B6A-4FFF-A505-D5D23FEECF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Country-Vehicle Progress" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="216">
   <si>
     <t>Country</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>Baseline effective % of fortified</t>
   </si>
   <si>
     <t>concentration</t>
@@ -346,6 +349,9 @@
   </si>
   <si>
     <t>Originally in mcg/100g; https://www.wolframalpha.com/input?i=4.25+mg+per+100+grams+in+micrograms+per+gram</t>
+  </si>
+  <si>
+    <t>Same as intervention, for now</t>
   </si>
   <si>
     <t>Pregnant people hemoglobin levels at baseline</t>
@@ -642,7 +648,7 @@
     <t>Intervention coverage % of fortifiable and unfortified</t>
   </si>
   <si>
-    <t>Intervention effective % of newly fortified</t>
+    <t>Intervention effective % of fortified</t>
   </si>
   <si>
     <t>Andy Garcia email 7/26</t>
@@ -927,7 +933,17 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1610,7 +1626,7 @@
     <mergeCell ref="F2:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:G9">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"Missing"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1686,25 +1702,25 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="30" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1718,7 +1734,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B6" t="str">
         <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, B$1,  'Scenario Definition Extraction'!$B$2:$B$991, B$2,  'Scenario Definition Extraction'!$C$2:$C$991, B$3, 'Scenario Definition Extraction'!$D$2:$D$991, B$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A6) = 0, "Missing", "Complete")</f>
@@ -1747,7 +1763,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B7" t="str">
         <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, B$1,  'Scenario Definition Extraction'!$B$2:$B$991, B$2,  'Scenario Definition Extraction'!$C$2:$C$991, B$3, 'Scenario Definition Extraction'!$D$2:$D$991, B$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A7) = 0, "Missing", "Complete")</f>
@@ -1776,7 +1792,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B8" t="str">
         <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, B$1,  'Scenario Definition Extraction'!$B$2:$B$991, B$2,  'Scenario Definition Extraction'!$C$2:$C$991, B$3, 'Scenario Definition Extraction'!$D$2:$D$991, B$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A8) = 0, "Missing", "Complete")</f>
@@ -1887,7 +1903,7 @@
         <v>83</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>11</v>
@@ -1919,10 +1935,10 @@
         <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F2" t="s">
         <v>29</v>
@@ -1931,13 +1947,13 @@
         <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I2" s="7">
         <v>0.8</v>
       </c>
       <c r="J2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1951,10 +1967,10 @@
         <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F3" t="s">
         <v>29</v>
@@ -1963,13 +1979,13 @@
         <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I3" s="7">
         <v>0.8</v>
       </c>
       <c r="J3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1983,10 +1999,10 @@
         <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F4" t="s">
         <v>29</v>
@@ -1995,13 +2011,13 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I4" s="7">
         <v>0.8</v>
       </c>
       <c r="J4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2015,10 +2031,10 @@
         <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F5" t="s">
         <v>29</v>
@@ -2027,13 +2043,13 @@
         <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I5" s="7">
         <v>0.8</v>
       </c>
       <c r="J5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -2047,10 +2063,10 @@
         <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F6" t="s">
         <v>29</v>
@@ -2059,13 +2075,13 @@
         <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I6" s="7">
         <v>0.8</v>
       </c>
       <c r="J6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2079,10 +2095,10 @@
         <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F7" t="s">
         <v>29</v>
@@ -2091,13 +2107,13 @@
         <v>30</v>
       </c>
       <c r="H7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I7" s="7">
         <v>0.8</v>
       </c>
       <c r="J7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -2111,10 +2127,10 @@
         <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E8" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F8" t="s">
         <v>29</v>
@@ -2123,13 +2139,13 @@
         <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I8" s="7">
         <v>0.8</v>
       </c>
       <c r="J8" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -2143,10 +2159,10 @@
         <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F9" t="s">
         <v>29</v>
@@ -2155,13 +2171,13 @@
         <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I9" s="7">
         <v>0.8</v>
       </c>
       <c r="J9" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -2175,10 +2191,10 @@
         <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F10" t="s">
         <v>29</v>
@@ -2187,13 +2203,13 @@
         <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I10" s="7">
         <v>0.8</v>
       </c>
       <c r="J10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -2207,10 +2223,10 @@
         <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F11" t="s">
         <v>29</v>
@@ -2219,13 +2235,13 @@
         <v>30</v>
       </c>
       <c r="H11" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I11" s="7">
         <v>0.8</v>
       </c>
       <c r="J11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -2239,10 +2255,10 @@
         <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F12" t="s">
         <v>29</v>
@@ -2251,13 +2267,13 @@
         <v>30</v>
       </c>
       <c r="H12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I12" s="7">
         <v>0.8</v>
       </c>
       <c r="J12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -2271,10 +2287,10 @@
         <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E13" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F13" t="s">
         <v>29</v>
@@ -2283,13 +2299,13 @@
         <v>30</v>
       </c>
       <c r="H13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I13" s="7">
         <v>0.8</v>
       </c>
       <c r="J13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -2303,25 +2319,25 @@
         <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E14" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I14">
         <v>840</v>
       </c>
       <c r="J14" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2335,25 +2351,25 @@
         <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E15" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H15" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I15">
         <v>24</v>
       </c>
       <c r="J15" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2367,25 +2383,25 @@
         <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I16">
         <v>14.084507042253522</v>
       </c>
       <c r="J16" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2399,25 +2415,25 @@
         <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E17" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H17" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I17">
         <v>56.338028169014088</v>
       </c>
       <c r="J17" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2431,25 +2447,25 @@
         <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E18" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I18">
         <v>42.5</v>
       </c>
       <c r="J18" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2463,25 +2479,25 @@
         <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E19" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H19" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I19">
         <v>0.125</v>
       </c>
       <c r="J19" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -2531,22 +2547,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="45">
@@ -2554,13 +2570,13 @@
         <v>49</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E2">
         <v>2021</v>
@@ -2568,30 +2584,30 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -4904,7 +4920,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EC50408-61D8-4A10-93E8-9867356C2F54}">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.42578125" bestFit="1" customWidth="1"/>
@@ -5065,11 +5081,11 @@
         <v>87</v>
       </c>
       <c r="H6" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$938, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$938, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$938, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$938, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$938, $A6, 'Country-Vehicle-Fort Extraction'!$J$2:$J$938, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Missing</v>
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "Total",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A6, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
       </c>
       <c r="I6" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$938, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$938, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$938, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$938, "&lt;&gt;All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$938, $A6, 'Country-Vehicle-Fort Extraction'!$J$2:$J$938, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "&lt;&gt;All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A6, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="J6" t="s">
@@ -5108,25 +5124,70 @@
         <v>87</v>
       </c>
       <c r="H7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$938, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$938, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$938, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$938, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$938, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$938, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "Total",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="I7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$938, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$938, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$938, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$938, "&lt;&gt;All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$938, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$938, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "&lt;&gt;Total",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="J7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$938, J$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$938, J$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$938, J$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$938, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$938, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$938, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, J$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, J$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, J$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="K7" t="s">
         <v>90</v>
       </c>
       <c r="L7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$938, J$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$938, J$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$938, L$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$938, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$938, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$938, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, J$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, J$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, L$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="M7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H8" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "Total",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A8, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Missing</v>
+      </c>
+      <c r="I8" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "&lt;&gt;Total",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A8, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
+        <v>Missing</v>
+      </c>
+      <c r="J8" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, J$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, J$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, J$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A8, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Missing</v>
+      </c>
+      <c r="K8" t="s">
+        <v>90</v>
+      </c>
+      <c r="L8" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, J$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, J$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, L$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A8, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Missing</v>
+      </c>
+      <c r="M8" t="s">
         <v>90</v>
       </c>
     </row>
@@ -5146,7 +5207,12 @@
     <mergeCell ref="H3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:M6 B7:I7 I6:M7">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="7" operator="equal">
+      <formula>"Missing"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H8:M8">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"Missing"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5156,7 +5222,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC26D125-533B-4E2C-8B10-83B96EF6CBCB}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -5252,10 +5318,10 @@
         <v>89</v>
       </c>
       <c r="F3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I3" t="s">
         <v>47</v>
@@ -5293,7 +5359,7 @@
         <v>0.61875637104994907</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -5463,10 +5529,10 @@
         <v>89</v>
       </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I10" t="s">
         <v>47</v>
@@ -5475,7 +5541,7 @@
         <v>650</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -5507,7 +5573,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -5527,10 +5593,10 @@
         <v>89</v>
       </c>
       <c r="F12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I12" t="s">
         <v>47</v>
@@ -5540,7 +5606,7 @@
       </c>
       <c r="L12" s="9"/>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" ht="43.5">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -5557,19 +5623,19 @@
         <v>89</v>
       </c>
       <c r="F13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J13">
         <v>42.5</v>
       </c>
-      <c r="L13" t="s">
-        <v>97</v>
+      <c r="L13" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -5589,19 +5655,135 @@
         <v>89</v>
       </c>
       <c r="F14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J14">
         <v>0.125</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="L15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J16" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="L16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" t="s">
+        <v>91</v>
+      </c>
+      <c r="F17" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J17" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="L17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J18" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="L18" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -5701,7 +5883,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s">
         <v>88</v>
@@ -5710,21 +5892,21 @@
         <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B5" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$2:$A$980, B$1,  'Country Extraction'!$B$2:$B$980, "All",  'Country Extraction'!$C$2:$C$980, $A5) = 0, "Missing", "Complete")</f>
@@ -5753,7 +5935,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B6" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$2:$A$980, B$1,  'Country Extraction'!$B$2:$B$980, "All",  'Country Extraction'!$C$2:$C$980, $A6) = 0, "Missing", "Complete")</f>
@@ -5782,7 +5964,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s">
         <v>88</v>
@@ -5791,21 +5973,21 @@
         <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s">
         <v>88</v>
@@ -5814,21 +5996,21 @@
         <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s">
         <v>88</v>
@@ -5837,24 +6019,24 @@
         <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B10" t="s">
         <v>88</v>
@@ -5863,26 +6045,26 @@
         <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E10" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$1:$A$995, F$1, 'Country Extraction'!$B$1:$B$995, "&lt;&gt;All", 'Country Extraction'!$C$1:$C$995, $A10, 'Country Extraction'!$H$1:$H$995, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="F10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G10" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$1:$A$995, H$1, 'Country Extraction'!$B$1:$B$995, "&lt;&gt;All", 'Country Extraction'!$C$1:$C$995, $A10, 'Country Extraction'!$H$1:$H$995, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s">
         <v>88</v>
@@ -5891,25 +6073,25 @@
         <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E11" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$1:$A$995, F$1, 'Country Extraction'!$B$1:$B$995, "&lt;&gt;All", 'Country Extraction'!$C$1:$C$995, $A11, 'Country Extraction'!$H$1:$H$995, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="F11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B12" t="s">
         <v>88</v>
@@ -5918,21 +6100,21 @@
         <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s">
         <v>88</v>
@@ -5941,24 +6123,24 @@
         <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B14" t="s">
         <v>88</v>
@@ -5967,41 +6149,41 @@
         <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H14" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C15" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$1:$A$995, D$1, 'Country Extraction'!$B$1:$B$995, "&lt;&gt;All", 'Country Extraction'!$C$1:$C$995, $A15, 'Country Extraction'!$H$1:$H$995, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E15" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$1:$A$995, F$1, 'Country Extraction'!$B$1:$B$995, "&lt;&gt;All", 'Country Extraction'!$C$1:$C$995, $A15, 'Country Extraction'!$H$1:$H$995, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="F15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G15" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$1:$A$995, H$1, 'Country Extraction'!$B$1:$B$995, "&lt;&gt;All", 'Country Extraction'!$C$1:$C$995, $A15, 'Country Extraction'!$H$1:$H$995, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
@@ -6072,19 +6254,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="32.25" customHeight="1">
@@ -6095,16 +6277,16 @@
         <v>37</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6115,13 +6297,13 @@
         <v>38</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6132,13 +6314,13 @@
         <v>39</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6149,13 +6331,13 @@
         <v>40</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6166,115 +6348,115 @@
         <v>41</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B9" t="s">
         <v>37</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B10" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B11" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B12" t="s">
         <v>40</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s">
         <v>41</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6282,16 +6464,16 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E14" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G14" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6302,13 +6484,13 @@
         <v>37</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -6319,13 +6501,13 @@
         <v>38</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -6336,13 +6518,13 @@
         <v>39</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E17" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G17" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -6353,13 +6535,13 @@
         <v>40</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G18" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -6370,13 +6552,13 @@
         <v>41</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E19" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G19" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.75">
@@ -6384,19 +6566,19 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G20" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -6407,16 +6589,16 @@
         <v>37</v>
       </c>
       <c r="C21" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G21" t="s">
+        <v>123</v>
+      </c>
+      <c r="J21" s="8" t="s">
         <v>125</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="G21" t="s">
-        <v>121</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -6427,13 +6609,13 @@
         <v>38</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G22" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -6444,13 +6626,13 @@
         <v>39</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G23" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -6461,13 +6643,13 @@
         <v>40</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G24" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -6478,115 +6660,115 @@
         <v>41</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G25" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G26" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G27" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B28" t="s">
         <v>38</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B29" t="s">
         <v>39</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G29" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B30" t="s">
         <v>40</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B31" t="s">
         <v>41</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G31" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -6594,16 +6776,16 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G32" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -6614,13 +6796,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -6631,13 +6813,13 @@
         <v>38</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G34" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -6648,13 +6830,13 @@
         <v>39</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G35" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -6665,13 +6847,13 @@
         <v>40</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G36" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -6682,13 +6864,13 @@
         <v>41</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G37" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -6696,13 +6878,13 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -6713,10 +6895,10 @@
         <v>37</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -6727,10 +6909,10 @@
         <v>38</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -6741,10 +6923,10 @@
         <v>39</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -6755,10 +6937,10 @@
         <v>40</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -6769,94 +6951,94 @@
         <v>41</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B44" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B45" t="s">
         <v>37</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G45" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B46" t="s">
         <v>38</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B47" t="s">
         <v>39</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B48" t="s">
         <v>40</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B49" t="s">
         <v>41</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -6864,13 +7046,13 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -6881,10 +7063,10 @@
         <v>37</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G51" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -6895,10 +7077,10 @@
         <v>38</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G52" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -6909,10 +7091,10 @@
         <v>39</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G53" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -6923,10 +7105,10 @@
         <v>40</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G54" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -6937,10 +7119,10 @@
         <v>41</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G55" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -6948,13 +7130,13 @@
         <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C56" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G56" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="45">
@@ -6965,10 +7147,10 @@
         <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15.75">
@@ -6979,10 +7161,10 @@
         <v>38</v>
       </c>
       <c r="C58" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="15.75">
@@ -6993,7 +7175,7 @@
         <v>39</v>
       </c>
       <c r="C59" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J59" s="12"/>
     </row>
@@ -7005,7 +7187,7 @@
         <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -7016,76 +7198,76 @@
         <v>41</v>
       </c>
       <c r="C61" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B62" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C62" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G62" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B63" t="s">
         <v>37</v>
       </c>
       <c r="C63" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B64" t="s">
         <v>38</v>
       </c>
       <c r="C64" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B65" t="s">
         <v>39</v>
       </c>
       <c r="C65" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B66" t="s">
         <v>40</v>
       </c>
       <c r="C66" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B67" t="s">
         <v>41</v>
       </c>
       <c r="C67" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -7093,13 +7275,13 @@
         <v>3</v>
       </c>
       <c r="B68" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C68" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G68" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -7110,7 +7292,7 @@
         <v>37</v>
       </c>
       <c r="C69" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -7121,7 +7303,7 @@
         <v>38</v>
       </c>
       <c r="C70" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -7132,7 +7314,7 @@
         <v>39</v>
       </c>
       <c r="C71" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -7143,7 +7325,7 @@
         <v>40</v>
       </c>
       <c r="C72" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -7154,7 +7336,7 @@
         <v>41</v>
       </c>
       <c r="C73" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="30">
@@ -7162,36 +7344,36 @@
         <v>1</v>
       </c>
       <c r="B74" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C74" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D74" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G74" s="12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J74" s="14" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B75" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C75" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D75" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J75" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -7199,13 +7381,13 @@
         <v>3</v>
       </c>
       <c r="B76" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C76" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D76" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -7281,7 +7463,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B3" t="s">
         <v>88</v>
@@ -7297,7 +7479,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B4" t="s">
         <v>88</v>
@@ -7368,28 +7550,28 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G2" s="26">
         <v>3.25</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -7397,28 +7579,28 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E3">
         <v>2021</v>
       </c>
       <c r="F3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G3">
         <v>4.4000000000000004</v>
       </c>
       <c r="H3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -7426,28 +7608,28 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E4">
         <v>2012</v>
       </c>
       <c r="F4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G4">
         <v>4.2</v>
       </c>
       <c r="H4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -7455,28 +7637,28 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E5">
         <v>2013</v>
       </c>
       <c r="F5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G5">
         <v>16.7</v>
       </c>
       <c r="H5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -7484,28 +7666,28 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E6">
         <v>2013</v>
       </c>
       <c r="F6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G6">
         <v>16.7</v>
       </c>
       <c r="H6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -7577,7 +7759,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="26" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -7590,59 +7772,59 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="26" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D3" s="26">
         <v>2018</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F3" s="26">
         <v>4.3</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I3" s="23"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="26" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D4" s="26">
         <v>2015</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F4" s="26">
         <v>6</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H4" s="23"/>
       <c r="I4" s="23"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="26" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B5" s="26"/>
       <c r="C5" s="26"/>
@@ -7655,18 +7837,18 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="26" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G6" s="26"/>
       <c r="H6" s="23"/>
@@ -7674,18 +7856,18 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="26" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
       <c r="E7" s="26" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G7" s="26"/>
       <c r="H7" s="23"/>
@@ -7693,22 +7875,22 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="26" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
       <c r="E8" s="26" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="23" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I8" s="23"/>
     </row>
@@ -7787,6 +7969,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100447C4EFE3BCDC24F9D43FB479AF7E97A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="710ccc9eba0c031f4d3c8297a7da4be2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="19a3940c-c740-4699-845a-46837f99845a" xmlns:ns3="539a68f6-d0ac-4a73-9041-e1fa437c4cee" xmlns:ns4="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a67399e28ae6312d8947be2cafff42c1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="19a3940c-c740-4699-845a-46837f99845a"/>
@@ -8040,7 +8231,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a" xsi:nil="true"/>
@@ -8051,23 +8242,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44149C33-81B0-4C8D-A8B9-4C0F99EB683B}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{302FEEF7-88D6-41D4-B999-EFF8511D95B1}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4173999B-2FEB-4E5B-A6C7-6E33DD5EA2F7}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44149C33-81B0-4C8D-A8B9-4C0F99EB683B}"/>
 </file>
--- a/legacy/vivarium_gates_lsff_by_wealth_quintile/0100_data_prep/extraction/Data Extraction Sheet.xlsx
+++ b/legacy/vivarium_gates_lsff_by_wealth_quintile/0100_data_prep/extraction/Data Extraction Sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwnetid.sharepoint.com/sites/ihme_simulation_science_team/Shared Documents/Research/LSFF/04_Concept_Model_Development/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F48EAE2D-6B6A-4FFF-A505-D5D23FEECF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8CA6867-1011-45AB-BB75-EE63C249175B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="216">
   <si>
     <t>Country</t>
   </si>
@@ -5222,7 +5222,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC26D125-533B-4E2C-8B10-83B96EF6CBCB}">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -5783,6 +5783,35 @@
         <v>0.8</v>
       </c>
       <c r="L18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="L19" t="s">
         <v>100</v>
       </c>
     </row>
@@ -7969,15 +7998,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100447C4EFE3BCDC24F9D43FB479AF7E97A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="710ccc9eba0c031f4d3c8297a7da4be2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="19a3940c-c740-4699-845a-46837f99845a" xmlns:ns3="539a68f6-d0ac-4a73-9041-e1fa437c4cee" xmlns:ns4="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a67399e28ae6312d8947be2cafff42c1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="19a3940c-c740-4699-845a-46837f99845a"/>
@@ -8231,6 +8251,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -8243,11 +8272,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44149C33-81B0-4C8D-A8B9-4C0F99EB683B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{302FEEF7-88D6-41D4-B999-EFF8511D95B1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{302FEEF7-88D6-41D4-B999-EFF8511D95B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44149C33-81B0-4C8D-A8B9-4C0F99EB683B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/legacy/vivarium_gates_lsff_by_wealth_quintile/0100_data_prep/extraction/Data Extraction Sheet.xlsx
+++ b/legacy/vivarium_gates_lsff_by_wealth_quintile/0100_data_prep/extraction/Data Extraction Sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28005"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwnetid.sharepoint.com/sites/ihme_simulation_science_team/Shared Documents/Research/LSFF/04_Concept_Model_Development/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8CA6867-1011-45AB-BB75-EE63C249175B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7934BE7B-3755-4AC0-B316-CDC44E903342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -555,7 +555,7 @@
     <t>Anaemia, prenatal iron use, and risk of adverse pregnancy outcomes: systematic review and meta-analysis</t>
   </si>
   <si>
-    <t>7.29 to 26.11</t>
+    <t>0.729 to 2.611</t>
   </si>
   <si>
     <t>https://www.bmj.com/content/346/bmj.f3443; study of supplementation at higher doses than fortification; selected the effect among trials &lt;66mg/day as all fortification would fall in this range</t>
@@ -7542,6 +7542,7 @@
     <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="6" max="6" width="34.140625" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="50.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7681,7 +7682,7 @@
         <v>160</v>
       </c>
       <c r="G5">
-        <v>16.7</v>
+        <v>1.67</v>
       </c>
       <c r="H5" t="s">
         <v>161</v>
@@ -7710,7 +7711,7 @@
         <v>160</v>
       </c>
       <c r="G6">
-        <v>16.7</v>
+        <v>1.67</v>
       </c>
       <c r="H6" t="s">
         <v>161</v>
@@ -7998,6 +7999,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="19a3940c-c740-4699-845a-46837f99845a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100447C4EFE3BCDC24F9D43FB479AF7E97A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="710ccc9eba0c031f4d3c8297a7da4be2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="19a3940c-c740-4699-845a-46837f99845a" xmlns:ns3="539a68f6-d0ac-4a73-9041-e1fa437c4cee" xmlns:ns4="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a67399e28ae6312d8947be2cafff42c1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="19a3940c-c740-4699-845a-46837f99845a"/>
@@ -8251,28 +8272,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="19a3940c-c740-4699-845a-46837f99845a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{302FEEF7-88D6-41D4-B999-EFF8511D95B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4173999B-2FEB-4E5B-A6C7-6E33DD5EA2F7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8280,5 +8281,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4173999B-2FEB-4E5B-A6C7-6E33DD5EA2F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{302FEEF7-88D6-41D4-B999-EFF8511D95B1}"/>
 </file>
--- a/legacy/vivarium_gates_lsff_by_wealth_quintile/0100_data_prep/extraction/Data Extraction Sheet.xlsx
+++ b/legacy/vivarium_gates_lsff_by_wealth_quintile/0100_data_prep/extraction/Data Extraction Sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28005"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwnetid.sharepoint.com/sites/ihme_simulation_science_team/Shared Documents/Research/LSFF/04_Concept_Model_Development/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7934BE7B-3755-4AC0-B316-CDC44E903342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54404D2C-A9C5-464C-AB2F-9C86216971E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -334,7 +334,7 @@
     <t>Assumption: labeled as fortified = fortified (basically true for salt). Divided "consumed food labeled as fortified" by "consumed food".</t>
   </si>
   <si>
-    <t>Maggi cubes (most popular brand and format) claim to have 15% NRV per serving (https://www.nestle-cwa.com/en/ask-nestle/products-brands/what-is-in-the-maggi-cube), but according to Jonathan Gorstein email on July 27th it is actually 12%</t>
+    <t>Maggi cubes (most popular brand and format) claim to have 15% NRV per serving (https://www.nestle-cwa.com/en/ask-nestle/products-brands/what-is-in-the-maggi-cube), but according to Jonathan Gorstein email on July 27th it is actually 12%; https://www.wolframalpha.com/input?i=12%25+of+14mg+per+4+grams+in+mcg%2Fg</t>
   </si>
   <si>
     <t>There is some information on fraction labeled as fortified in NFCMS Table 169, but it Figure 71 shows that 95% of WRA have RBC folate insufficiency. Also: '61 percent of the non-pregnant women from households consumed bouillons that are labelled as fortified with iodine and/or iron.' There is some evidence that the rich have more bouillon labeled as fortified (Table 169).</t>
@@ -657,10 +657,10 @@
     <t>Same across all vehicles/countries/fortificants</t>
   </si>
   <si>
-    <t>15% Codex (2100mcg) per 2.5 grams; I think the 2.5 grams might be in error</t>
-  </si>
-  <si>
-    <t>15% Codex (60mcg) per 2.5 grams; I think the 2.5 grams might be in error</t>
+    <t>15% Nigeria-specific NRV per 2.5 grams; https://www.wolframalpha.com/input?i=15%25+of+22mg+per+2.5+grams+in+mcg%2Fg</t>
+  </si>
+  <si>
+    <t>15% Codex (60mcg) per 2.5 grams; https://www.wolframalpha.com/input?i=15%25+of+400mcg+per+2.5+grams+in+mcg%2Fg</t>
   </si>
   <si>
     <t>25% Codex (100mcg) per 7.1 grams</t>
@@ -871,7 +871,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -921,6 +921,9 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1418,35 +1421,35 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32" t="s">
+      <c r="C1" s="33"/>
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32" t="s">
+      <c r="E1" s="33"/>
+      <c r="F1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="32"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32" t="s">
+      <c r="C2" s="33"/>
+      <c r="D2" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="32"/>
+      <c r="G2" s="33"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
@@ -1649,44 +1652,44 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32" t="s">
+      <c r="C1" s="33"/>
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32" t="s">
+      <c r="E1" s="33"/>
+      <c r="F1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="32"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32" t="s">
+      <c r="C2" s="33"/>
+      <c r="D2" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="32"/>
+      <c r="G2" s="33"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="32"/>
+      <c r="C3" s="33"/>
       <c r="D3" s="28" t="s">
         <v>84</v>
       </c>
@@ -2308,7 +2311,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="43.5">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -2334,13 +2337,13 @@
         <v>193</v>
       </c>
       <c r="I14">
-        <v>840</v>
-      </c>
-      <c r="J14" t="s">
+        <v>1320</v>
+      </c>
+      <c r="J14" s="5" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="43.5">
       <c r="A15" t="s">
         <v>2</v>
       </c>
@@ -2368,7 +2371,7 @@
       <c r="I15">
         <v>24</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="5" t="s">
         <v>196</v>
       </c>
     </row>
@@ -4715,7 +4718,7 @@
         <v>49</v>
       </c>
       <c r="J60" s="17">
-        <v>0.96573208722741444</v>
+        <v>0.96573208722741399</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -4935,76 +4938,76 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32" t="s">
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="33" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32" t="s">
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32" t="s">
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32" t="s">
+      <c r="C3" s="33"/>
+      <c r="D3" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32" t="s">
+      <c r="E3" s="33"/>
+      <c r="F3" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32" t="s">
+      <c r="G3" s="33"/>
+      <c r="H3" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32" t="s">
+      <c r="I3" s="33"/>
+      <c r="J3" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32" t="s">
+      <c r="K3" s="33"/>
+      <c r="L3" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="M3" s="32"/>
+      <c r="M3" s="33"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="3" t="s">
@@ -5512,7 +5515,7 @@
       </c>
       <c r="L9" s="9"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" ht="101.25">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -5538,9 +5541,9 @@
         <v>47</v>
       </c>
       <c r="J10" s="10">
-        <v>650</v>
-      </c>
-      <c r="L10" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="L10" s="32" t="s">
         <v>95</v>
       </c>
     </row>
@@ -5863,18 +5866,18 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32" t="s">
+      <c r="C1" s="33"/>
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="33" t="s">
+      <c r="E1" s="33"/>
+      <c r="F1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="33"/>
+      <c r="G1" s="34"/>
       <c r="H1" s="1" t="s">
         <v>26</v>
       </c>
@@ -7591,7 +7594,7 @@
       <c r="E2" t="s">
         <v>149</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="5" t="s">
         <v>150</v>
       </c>
       <c r="G2" s="26">
@@ -7999,17 +8002,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="19a3940c-c740-4699-845a-46837f99845a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -8018,7 +8010,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100447C4EFE3BCDC24F9D43FB479AF7E97A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="710ccc9eba0c031f4d3c8297a7da4be2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="19a3940c-c740-4699-845a-46837f99845a" xmlns:ns3="539a68f6-d0ac-4a73-9041-e1fa437c4cee" xmlns:ns4="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a67399e28ae6312d8947be2cafff42c1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="19a3940c-c740-4699-845a-46837f99845a"/>
@@ -8272,14 +8264,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="19a3940c-c740-4699-845a-46837f99845a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4173999B-2FEB-4E5B-A6C7-6E33DD5EA2F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44149C33-81B0-4C8D-A8B9-4C0F99EB683B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44149C33-81B0-4C8D-A8B9-4C0F99EB683B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{302FEEF7-88D6-41D4-B999-EFF8511D95B1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{302FEEF7-88D6-41D4-B999-EFF8511D95B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4173999B-2FEB-4E5B-A6C7-6E33DD5EA2F7}"/>
 </file>
--- a/legacy/vivarium_gates_lsff_by_wealth_quintile/0100_data_prep/extraction/Data Extraction Sheet.xlsx
+++ b/legacy/vivarium_gates_lsff_by_wealth_quintile/0100_data_prep/extraction/Data Extraction Sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28014"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwnetid.sharepoint.com/sites/ihme_simulation_science_team/Shared Documents/Research/LSFF/04_Concept_Model_Development/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54404D2C-A9C5-464C-AB2F-9C86216971E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEE2F6E1-E1CF-4143-BFE9-DE017E788A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Country-Vehicle Progress" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="218">
   <si>
     <t>Country</t>
   </si>
@@ -292,10 +292,7 @@
     <t>Table 169, page 220 'Percentage of Non-Pregnant Women Whose Households Consumed Bouillon (purchased, branded, and labelled as fortified) by Residence, Zone, and Wealth Quintile', using 'branded' as a proxy for fortifiable and % of households as a proxy for % of product. Values obtained by dividing percent consuming branded food by percent consuming food, which is why we don't have uncertainty. A similar thing is reported in Annex 43, page 549; 'How household obtained bouillon the last time it was obtained': 'purchased', and not by wealth quintile</t>
   </si>
   <si>
-    <t>M4N Database</t>
-  </si>
-  <si>
-    <t>"Industry consolidation" sent by Jonathan Gorstein in a spreadsheet on 7/19</t>
+    <t>51.3% "Industry consolidation" sent by Jonathan Gorstein in a spreadsheet on 7/19 according to M4N Database, but on 8/15 we agreed to consider all open-market rice unfortifiable</t>
   </si>
   <si>
     <t>Fortificant</t>
@@ -348,7 +345,10 @@
     <t>Originally in mg/100g; https://www.wolframalpha.com/input?i=4.25+mg+per+100+grams+in+micrograms+per+gram</t>
   </si>
   <si>
-    <t>Originally in mcg/100g; https://www.wolframalpha.com/input?i=4.25+mg+per+100+grams+in+micrograms+per+gram</t>
+    <t>Originally in mcg/100g; https://www.wolframalpha.com/input?i=12.5+mcg+per+100+grams+in+micrograms+per+gram</t>
+  </si>
+  <si>
+    <t>Jonathan Gorstein, 8/15</t>
   </si>
   <si>
     <t>Same as intervention, for now</t>
@@ -645,7 +645,7 @@
     <t>Vehicle fortification in intervention -- amount among fortified</t>
   </si>
   <si>
-    <t>Intervention coverage % of fortifiable and unfortified</t>
+    <t>Intervention coverage % of fortifiable</t>
   </si>
   <si>
     <t>Intervention effective % of fortified</t>
@@ -654,7 +654,7 @@
     <t>Andy Garcia email 7/26</t>
   </si>
   <si>
-    <t>Same across all vehicles/countries/fortificants</t>
+    <t>Confirmed by Jonathan Gorstein, 8/15</t>
   </si>
   <si>
     <t>15% Nigeria-specific NRV per 2.5 grams; https://www.wolframalpha.com/input?i=15%25+of+22mg+per+2.5+grams+in+mcg%2Fg</t>
@@ -673,6 +673,12 @@
   </si>
   <si>
     <t>Same as baseline, PDS rice; see county-vehicle-fort extraction</t>
+  </si>
+  <si>
+    <t>https://nyaspubs.onlinelibrary.wiley.com/doi/full/10.1111/nyas.12478</t>
+  </si>
+  <si>
+    <t>https://www.wolframalpha.com/input?i=0.13+mg%2F100g+in+mcg%2Fg</t>
   </si>
   <si>
     <t>Name</t>
@@ -936,87 +942,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1408,7 +1334,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="58.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -1629,7 +1555,7 @@
     <mergeCell ref="F2:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:G9">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"Missing"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1640,7 +1566,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB686F86-0F1B-4E3A-8BF6-0236059233BB}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="52.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
@@ -1684,23 +1610,23 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="33" t="s">
         <v>83</v>
-      </c>
-      <c r="B3" s="33" t="s">
-        <v>84</v>
       </c>
       <c r="C3" s="33"/>
       <c r="D3" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="E3" s="28" t="s">
-        <v>85</v>
-      </c>
       <c r="F3" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="28" t="s">
         <v>84</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1832,47 +1758,7 @@
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F6:F8">
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
-      <formula>"Missing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
-      <formula>"Missing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6:G8">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
-      <formula>"Missing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6:B8">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>"Missing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"Missing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:C8">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"Missing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D6:D8">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"Missing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D8">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"Missing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E8">
+  <conditionalFormatting sqref="B6:G8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Missing"</formula>
     </cfRule>
@@ -1884,7 +1770,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797B3B46-8F2E-4C67-A115-D7583B1B84DB}">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -1903,7 +1789,7 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>186</v>
@@ -1935,7 +1821,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
         <v>189</v>
@@ -1950,13 +1836,10 @@
         <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>193</v>
+        <v>99</v>
       </c>
       <c r="I2" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="J2" t="s">
-        <v>194</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1967,7 +1850,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
         <v>189</v>
@@ -1982,13 +1865,10 @@
         <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>193</v>
+        <v>99</v>
       </c>
       <c r="I3" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="J3" t="s">
-        <v>194</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1999,7 +1879,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
         <v>187</v>
@@ -2031,7 +1911,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
         <v>188</v>
@@ -2063,7 +1943,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
         <v>189</v>
@@ -2095,7 +1975,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
         <v>189</v>
@@ -2127,7 +2007,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
         <v>189</v>
@@ -2142,13 +2022,10 @@
         <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>193</v>
+        <v>99</v>
       </c>
       <c r="I8" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="J8" t="s">
-        <v>194</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -2159,7 +2036,7 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
         <v>189</v>
@@ -2174,13 +2051,10 @@
         <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>193</v>
+        <v>99</v>
       </c>
       <c r="I9" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="J9" t="s">
-        <v>194</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -2191,7 +2065,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
         <v>187</v>
@@ -2206,13 +2080,10 @@
         <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>193</v>
+        <v>99</v>
       </c>
       <c r="I10" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="J10" t="s">
-        <v>194</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -2223,7 +2094,7 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
         <v>188</v>
@@ -2238,13 +2109,10 @@
         <v>30</v>
       </c>
       <c r="H11" t="s">
-        <v>193</v>
+        <v>99</v>
       </c>
       <c r="I11" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="J11" t="s">
-        <v>194</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -2255,7 +2123,7 @@
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
         <v>189</v>
@@ -2274,9 +2142,6 @@
       </c>
       <c r="I12" s="7">
         <v>0.8</v>
-      </c>
-      <c r="J12" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -2287,7 +2152,7 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
         <v>189</v>
@@ -2306,9 +2171,6 @@
       </c>
       <c r="I13" s="7">
         <v>0.8</v>
-      </c>
-      <c r="J13" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="43.5">
@@ -2319,7 +2181,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
         <v>189</v>
@@ -2328,10 +2190,10 @@
         <v>190</v>
       </c>
       <c r="F14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" t="s">
         <v>92</v>
-      </c>
-      <c r="G14" t="s">
-        <v>93</v>
       </c>
       <c r="H14" t="s">
         <v>193</v>
@@ -2351,7 +2213,7 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
         <v>189</v>
@@ -2360,10 +2222,10 @@
         <v>190</v>
       </c>
       <c r="F15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" t="s">
         <v>92</v>
-      </c>
-      <c r="G15" t="s">
-        <v>93</v>
       </c>
       <c r="H15" t="s">
         <v>193</v>
@@ -2383,7 +2245,7 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
         <v>187</v>
@@ -2392,10 +2254,10 @@
         <v>190</v>
       </c>
       <c r="F16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16" t="s">
         <v>92</v>
-      </c>
-      <c r="G16" t="s">
-        <v>93</v>
       </c>
       <c r="H16" t="s">
         <v>193</v>
@@ -2415,7 +2277,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
         <v>188</v>
@@ -2424,10 +2286,10 @@
         <v>190</v>
       </c>
       <c r="F17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" t="s">
         <v>92</v>
-      </c>
-      <c r="G17" t="s">
-        <v>93</v>
       </c>
       <c r="H17" t="s">
         <v>193</v>
@@ -2447,7 +2309,7 @@
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
         <v>189</v>
@@ -2456,10 +2318,10 @@
         <v>190</v>
       </c>
       <c r="F18" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" t="s">
         <v>92</v>
-      </c>
-      <c r="G18" t="s">
-        <v>93</v>
       </c>
       <c r="H18" t="s">
         <v>199</v>
@@ -2471,7 +2333,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" ht="15">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -2479,7 +2341,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
         <v>189</v>
@@ -2488,19 +2350,19 @@
         <v>190</v>
       </c>
       <c r="F19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G19" t="s">
         <v>92</v>
       </c>
-      <c r="G19" t="s">
-        <v>93</v>
-      </c>
-      <c r="H19" t="s">
-        <v>199</v>
+      <c r="H19" s="6" t="s">
+        <v>201</v>
       </c>
       <c r="I19">
-        <v>0.125</v>
-      </c>
-      <c r="J19" t="s">
-        <v>200</v>
+        <v>1.3</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -2516,6 +2378,10 @@
       <formula1>"Bouillon,Salt,Rice"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="J19" r:id="rId1" xr:uid="{8B29D165-A493-48F3-B663-85CB453EE758}"/>
+    <hyperlink ref="H19" r:id="rId2" xr:uid="{3DC1B296-F88E-408E-956F-0351AD5F515E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -2541,7 +2407,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{062B00F0-B806-4CE9-A08D-6C78F3C15B86}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="40.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -2550,36 +2416,36 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="45">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="43.5">
       <c r="A2" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E2">
         <v>2021</v>
@@ -2587,30 +2453,30 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -2625,7 +2491,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7501F0-08E1-4A63-A382-F6741C91E79A}">
   <dimension ref="A1:M65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -4849,7 +4715,7 @@
         <v>0.98377281947261663</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" ht="57.75">
       <c r="A65" t="s">
         <v>3</v>
       </c>
@@ -4875,13 +4741,13 @@
         <v>2024</v>
       </c>
       <c r="I65" t="s">
+        <v>47</v>
+      </c>
+      <c r="J65" s="21">
+        <v>0</v>
+      </c>
+      <c r="M65" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="J65" s="21">
-        <v>0.51300000000000001</v>
-      </c>
-      <c r="M65" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -4924,7 +4790,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EC50408-61D8-4A10-93E8-9867356C2F54}">
   <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="52.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -4982,30 +4848,30 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="33" t="s">
         <v>83</v>
-      </c>
-      <c r="B3" s="33" t="s">
-        <v>84</v>
       </c>
       <c r="C3" s="33"/>
       <c r="D3" s="33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E3" s="33"/>
       <c r="F3" s="33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G3" s="33"/>
       <c r="H3" s="33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I3" s="33"/>
       <c r="J3" s="33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K3" s="33"/>
       <c r="L3" s="33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M3" s="33"/>
     </row>
@@ -5063,25 +4929,25 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" t="s">
         <v>86</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" t="s">
         <v>87</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>87</v>
       </c>
-      <c r="D6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" t="s">
-        <v>88</v>
-      </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H6" t="str">
         <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "Total",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A6, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
@@ -5106,25 +4972,25 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" t="s">
         <v>87</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>87</v>
       </c>
-      <c r="D7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" t="s">
-        <v>88</v>
-      </c>
       <c r="F7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H7" t="str">
         <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "Total",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
@@ -5139,37 +5005,37 @@
         <v>Missing</v>
       </c>
       <c r="K7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L7" t="str">
         <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, J$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, J$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, L$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="M7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" t="s">
         <v>87</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>87</v>
       </c>
-      <c r="D8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" t="s">
-        <v>88</v>
-      </c>
       <c r="F8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H8" t="str">
         <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "Total",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A8, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
@@ -5184,14 +5050,14 @@
         <v>Missing</v>
       </c>
       <c r="K8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L8" t="str">
         <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, J$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, J$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, L$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A8, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="M8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -5209,13 +5075,13 @@
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="H3:I3"/>
   </mergeCells>
-  <conditionalFormatting sqref="B6:M6 B7:I7 I6:M7">
-    <cfRule type="cellIs" dxfId="12" priority="7" operator="equal">
+  <conditionalFormatting sqref="B6:M6 I6:M7 B7:I7">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"Missing"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:M8">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Missing"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5226,7 +5092,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC26D125-533B-4E2C-8B10-83B96EF6CBCB}">
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
@@ -5245,7 +5111,7 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>10</v>
@@ -5283,13 +5149,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F2" t="s">
         <v>29</v>
@@ -5312,19 +5178,19 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
         <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>92</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>93</v>
       </c>
       <c r="I3" t="s">
         <v>47</v>
@@ -5341,13 +5207,13 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F4" t="s">
         <v>29</v>
@@ -5362,7 +5228,7 @@
         <v>0.61875637104994907</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -5373,13 +5239,13 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
         <v>37</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F5" t="s">
         <v>29</v>
@@ -5403,13 +5269,13 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
         <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s">
         <v>29</v>
@@ -5433,13 +5299,13 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
         <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F7" t="s">
         <v>29</v>
@@ -5463,13 +5329,13 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
         <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F8" t="s">
         <v>29</v>
@@ -5493,13 +5359,13 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
         <v>41</v>
       </c>
       <c r="E9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F9" t="s">
         <v>29</v>
@@ -5515,7 +5381,7 @@
       </c>
       <c r="L9" s="9"/>
     </row>
-    <row r="10" spans="1:12" ht="101.25">
+    <row r="10" spans="1:12" ht="101.45">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -5523,19 +5389,19 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
         <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>92</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>93</v>
       </c>
       <c r="I10" t="s">
         <v>47</v>
@@ -5544,7 +5410,7 @@
         <v>420</v>
       </c>
       <c r="L10" s="32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -5555,13 +5421,13 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
         <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F11" t="s">
         <v>29</v>
@@ -5576,7 +5442,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -5587,19 +5453,19 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
         <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>92</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>93</v>
       </c>
       <c r="I12" t="s">
         <v>47</v>
@@ -5617,31 +5483,31 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
         <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G13" t="s">
         <v>92</v>
       </c>
-      <c r="G13" t="s">
-        <v>93</v>
-      </c>
       <c r="I13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J13">
         <v>42.5</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="43.5">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -5649,28 +5515,28 @@
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
         <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" t="s">
         <v>92</v>
       </c>
-      <c r="G14" t="s">
-        <v>93</v>
-      </c>
       <c r="I14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J14">
         <v>0.125</v>
       </c>
-      <c r="L14" s="9" t="s">
-        <v>99</v>
+      <c r="L14" s="32" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -5681,13 +5547,13 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
         <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F15" t="s">
         <v>29</v>
@@ -5695,11 +5561,14 @@
       <c r="G15" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J15" s="7">
-        <v>0.8</v>
+      <c r="I15" t="s">
+        <v>47</v>
+      </c>
+      <c r="J15" s="20">
+        <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -5710,13 +5579,13 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
         <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F16" t="s">
         <v>29</v>
@@ -5724,11 +5593,14 @@
       <c r="G16" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J16" s="7">
-        <v>0.8</v>
+      <c r="I16" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" s="20">
+        <v>0</v>
       </c>
       <c r="L16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -5739,13 +5611,13 @@
         <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
         <v>27</v>
       </c>
       <c r="E17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F17" t="s">
         <v>29</v>
@@ -5768,13 +5640,13 @@
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
         <v>27</v>
       </c>
       <c r="E18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F18" t="s">
         <v>29</v>
@@ -5797,13 +5669,13 @@
         <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
         <v>27</v>
       </c>
       <c r="E19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F19" t="s">
         <v>29</v>
@@ -5853,7 +5725,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B8AA13D-2CC0-4240-A9BF-02BB80A27D5D}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="52.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -5918,10 +5790,10 @@
         <v>101</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
         <v>102</v>
@@ -5999,10 +5871,10 @@
         <v>107</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
         <v>102</v>
@@ -6022,10 +5894,10 @@
         <v>108</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
         <v>102</v>
@@ -6045,10 +5917,10 @@
         <v>109</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
         <v>102</v>
@@ -6071,10 +5943,10 @@
         <v>111</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
         <v>102</v>
@@ -6099,10 +5971,10 @@
         <v>113</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
         <v>102</v>
@@ -6126,10 +5998,10 @@
         <v>115</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
         <v>102</v>
@@ -6149,10 +6021,10 @@
         <v>116</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
         <v>102</v>
@@ -6175,10 +6047,10 @@
         <v>118</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
         <v>102</v>
@@ -6229,7 +6101,7 @@
     <mergeCell ref="F1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:G15">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Missing"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6240,7 +6112,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F427D668-6E74-4989-9A76-CA42E7F92A98}">
   <dimension ref="A1:J76"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40.42578125" customWidth="1"/>
@@ -6281,7 +6153,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75">
+    <row r="2" spans="1:10" ht="15.95">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -6593,7 +6465,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15.75">
+    <row r="20" spans="1:10" ht="15.95">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -7171,7 +7043,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="45">
+    <row r="57" spans="1:10" ht="43.5">
       <c r="A57" t="s">
         <v>1</v>
       </c>
@@ -7185,7 +7057,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="15.75">
+    <row r="58" spans="1:10" ht="15.95">
       <c r="A58" t="s">
         <v>1</v>
       </c>
@@ -7199,7 +7071,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="15.75">
+    <row r="59" spans="1:10" ht="15.95">
       <c r="A59" t="s">
         <v>1</v>
       </c>
@@ -7371,7 +7243,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="30">
+    <row r="74" spans="1:10" ht="29.45">
       <c r="A74" t="s">
         <v>1</v>
       </c>
@@ -7461,7 +7333,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4E519DD-7070-48BB-9F21-242D1E473943}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="52.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -7498,7 +7370,7 @@
         <v>145</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C3" t="str">
         <f>IF(COUNTIFS('Vehicle Extraction'!$A$2:$A$904, C$1,  'Vehicle Extraction'!$B$2:$B$904, $A3) = 0, "Missing", "Complete")</f>
@@ -7514,7 +7386,7 @@
         <v>146</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C4" t="str">
         <f>IF(COUNTIFS('Vehicle Extraction'!$A$2:$A$904, C$1,  'Vehicle Extraction'!$B$2:$B$904, $A4) = 0, "Missing", "Complete")</f>
@@ -7527,7 +7399,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3:D4">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Missing"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7538,7 +7410,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BE8E890-3EB7-493D-B8C3-05E861B2DBA4}">
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="46.42578125" bestFit="1" customWidth="1"/>
@@ -7578,7 +7450,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="115.5">
+    <row r="2" spans="1:9" ht="101.45">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -7755,7 +7627,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{259F6A5D-CF80-41BD-979A-295E7564EADB}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="56.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
@@ -8002,15 +7874,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100447C4EFE3BCDC24F9D43FB479AF7E97A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="710ccc9eba0c031f4d3c8297a7da4be2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="19a3940c-c740-4699-845a-46837f99845a" xmlns:ns3="539a68f6-d0ac-4a73-9041-e1fa437c4cee" xmlns:ns4="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a67399e28ae6312d8947be2cafff42c1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="19a3940c-c740-4699-845a-46837f99845a"/>
@@ -8264,7 +8127,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a" xsi:nil="true"/>
@@ -8275,14 +8138,23 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44149C33-81B0-4C8D-A8B9-4C0F99EB683B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{302FEEF7-88D6-41D4-B999-EFF8511D95B1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{302FEEF7-88D6-41D4-B999-EFF8511D95B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4173999B-2FEB-4E5B-A6C7-6E33DD5EA2F7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4173999B-2FEB-4E5B-A6C7-6E33DD5EA2F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44149C33-81B0-4C8D-A8B9-4C0F99EB683B}"/>
 </file>
--- a/legacy/vivarium_gates_lsff_by_wealth_quintile/0100_data_prep/extraction/Data Extraction Sheet.xlsx
+++ b/legacy/vivarium_gates_lsff_by_wealth_quintile/0100_data_prep/extraction/Data Extraction Sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28014"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwnetid.sharepoint.com/sites/ihme_simulation_science_team/Shared Documents/Research/LSFF/04_Concept_Model_Development/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEE2F6E1-E1CF-4143-BFE9-DE017E788A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6519260-0061-43D4-999E-ACB54C4C2F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="3" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Country-Vehicle Progress" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="229">
   <si>
     <t>Country</t>
   </si>
@@ -295,6 +295,27 @@
     <t>51.3% "Industry consolidation" sent by Jonathan Gorstein in a spreadsheet on 7/19 according to M4N Database, but on 8/15 we agreed to consider all open-market rice unfortifiable</t>
   </si>
   <si>
+    <t>Jonathan Gorstein email 8/30</t>
+  </si>
+  <si>
+    <t>Table 172, page 224; based on email from Jonathan Gorstein 8/31 we have assumed the number reported is among consumers, so have multiplied it by coverage here</t>
+  </si>
+  <si>
+    <t>INTAKE</t>
+  </si>
+  <si>
+    <t>INTAKE tabulation of NFCMS (?) shared by Jonathan Gorstein on 8/30; presumably in WRA</t>
+  </si>
+  <si>
+    <t>Very rough estimate using SD = IQR / 1.35 (normality assumption), IQR reported in table 172</t>
+  </si>
+  <si>
+    <t>Table 173, page 224; based on email from Jonathan Gorstein 8/31 we have assumed the number reported is among consumers, so have multiplied it by coverage here</t>
+  </si>
+  <si>
+    <t>Very rough estimate using SD = IQR / 1.35 (normality assumption), IQR reported in table 173</t>
+  </si>
+  <si>
     <t>Fortificant</t>
   </si>
   <si>
@@ -326,6 +347,9 @@
   </si>
   <si>
     <t>mcg/g</t>
+  </si>
+  <si>
+    <t>Jonathan Gorstein, 8/30</t>
   </si>
   <si>
     <t>Assumption: labeled as fortified = fortified (basically true for salt). Divided "consumed food labeled as fortified" by "consumed food".</t>
@@ -352,6 +376,9 @@
   </si>
   <si>
     <t>Same as intervention, for now</t>
+  </si>
+  <si>
+    <t>Does not matter, no baseline fortification</t>
   </si>
   <si>
     <t>Pregnant people hemoglobin levels at baseline</t>
@@ -661,6 +688,12 @@
   </si>
   <si>
     <t>15% Codex (60mcg) per 2.5 grams; https://www.wolframalpha.com/input?i=15%25+of+400mcg+per+2.5+grams+in+mcg%2Fg</t>
+  </si>
+  <si>
+    <t>https://www.wolframalpha.com/input?i=4+mg%2F100g+in+mcg%2Fg</t>
+  </si>
+  <si>
+    <t>https://www.wolframalpha.com/input?i=0.169+mg%2F100g+in+mcg%2Fg</t>
   </si>
   <si>
     <t>25% Codex (100mcg) per 7.1 grams</t>
@@ -1333,17 +1366,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="58.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9" ht="15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1355,12 +1388,14 @@
         <v>2</v>
       </c>
       <c r="E1" s="33"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="I1" s="33"/>
+    </row>
+    <row r="2" spans="1:9" ht="15">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1376,8 +1411,12 @@
         <v>7</v>
       </c>
       <c r="G2" s="33"/>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="33"/>
+    </row>
+    <row r="3" spans="1:9" ht="15">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1399,8 +1438,14 @@
       <c r="G3" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -1408,153 +1453,196 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" ht="15">
       <c r="A5" t="s">
         <v>12</v>
       </c>
       <c r="B5" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A5, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "Total",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A5, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="C5" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!E$2:E$1003, $A5, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "&lt;&gt;All",  'Country-Vehicle Extraction'!E$2:E$1009, $A5, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="D5" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A5, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Missing</v>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "Total",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A5, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
       </c>
       <c r="E5" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A5, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A5, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, F$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "Total",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A5, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
+      </c>
+      <c r="G5" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, F$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A5, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
+      </c>
+      <c r="H5" t="s">
         <v>13</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" ht="15">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="B6" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A6, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Missing</v>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "Total",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A6, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
       </c>
       <c r="C6" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!E$2:E$1003, $A6, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "&lt;&gt;All",  'Country-Vehicle Extraction'!E$2:E$1009, $A6, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="D6" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A6, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Missing</v>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "Total",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A6, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
       </c>
       <c r="E6" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A6, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A6, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, F$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "Total",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A6, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
+      </c>
+      <c r="G6" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, F$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A6, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
+      </c>
+      <c r="H6" t="s">
         <v>13</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" ht="15">
       <c r="A7" t="s">
         <v>15</v>
       </c>
       <c r="B7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A7, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "Total",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A7, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="C7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!E$2:E$1003, $A7, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "&lt;&gt;All",  'Country-Vehicle Extraction'!E$2:E$1009, $A7, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="D7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A7, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Missing</v>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "Total",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A7, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
       </c>
       <c r="E7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A7, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A7, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, F$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "Total",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A7, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
+      </c>
+      <c r="G7" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, F$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A7, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
+      </c>
+      <c r="H7" t="s">
         <v>13</v>
       </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:9" ht="15">
       <c r="A8" t="s">
         <v>16</v>
       </c>
       <c r="B8" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A8, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Missing</v>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "Total",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A8, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
       </c>
       <c r="C8" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!E$2:E$1003, $A8, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "&lt;&gt;All",  'Country-Vehicle Extraction'!E$2:E$1009, $A8, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="D8" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A8, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Missing</v>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "Total",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A8, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
       </c>
       <c r="E8" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A8, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A8, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, F$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "Total",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A8, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
+      </c>
+      <c r="G8" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, F$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A8, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
+      </c>
+      <c r="H8" t="s">
         <v>13</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:9" ht="15">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A9, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "Total",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A9, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="C9" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!E$2:E$1003, $A9, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, B$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, B$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "&lt;&gt;All",  'Country-Vehicle Extraction'!E$2:E$1009, $A9, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="D9" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A9, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "Total",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A9, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
+      </c>
+      <c r="E9" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A9, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
+      </c>
+      <c r="F9" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, F$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "Total",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A9, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
-      <c r="E9" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, D$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A9, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+      <c r="G9" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, D$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, F$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "&lt;&gt;All",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A9, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
-      <c r="F9" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1003, F$1,  'Country-Vehicle Extraction'!$B$2:$B$1003, F$2,  'Country-Vehicle Extraction'!$C$2:$C$1003, "All",  'Country-Vehicle Extraction'!$E$2:$E$1003, $A9, 'Country-Vehicle Extraction'!$J$2:$J$1003, "&lt;&gt;") = 0, "Missing", "Complete")</f>
-        <v>Missing</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="H9" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle Extraction'!$A$2:$A$1009, H$1,  'Country-Vehicle Extraction'!$B$2:$B$1009, H$2,  'Country-Vehicle Extraction'!$C$2:$C$1009, "Total",  'Country-Vehicle Extraction'!$E$2:$E$1009, $A9, 'Country-Vehicle Extraction'!$J$2:$J$1009, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
+      </c>
+      <c r="I9" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D1:E1"/>
     <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="F2:G2"/>
+    <mergeCell ref="D1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:G9">
+  <conditionalFormatting sqref="B5:I9">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"Missing"</formula>
     </cfRule>
@@ -1565,16 +1653,18 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB686F86-0F1B-4E3A-8BF6-0236059233BB}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="52.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.42578125" customWidth="1"/>
+    <col min="8" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9" ht="15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1586,12 +1676,14 @@
         <v>2</v>
       </c>
       <c r="E1" s="33"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="I1" s="33"/>
+    </row>
+    <row r="2" spans="1:9" ht="15">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1607,158 +1699,199 @@
         <v>7</v>
       </c>
       <c r="G2" s="33"/>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="33"/>
+    </row>
+    <row r="3" spans="1:9" ht="15">
       <c r="A3" s="3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C3" s="33"/>
       <c r="D3" s="28" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>91</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15">
       <c r="A4" s="30" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>198</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" ht="15">
       <c r="A6" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B6" t="str">
-        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, B$1,  'Scenario Definition Extraction'!$B$2:$B$991, B$2,  'Scenario Definition Extraction'!$C$2:$C$991, B$3, 'Scenario Definition Extraction'!$D$2:$D$991, B$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A6) = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, B$1,  'Scenario Definition Extraction'!$B$2:$B$997, B$2,  'Scenario Definition Extraction'!$C$2:$C$997, B$3, 'Scenario Definition Extraction'!$D$2:$D$997, B$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A6) = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="C6" t="str">
-        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, B$1,  'Scenario Definition Extraction'!$B$2:$B$991, B$2,  'Scenario Definition Extraction'!$C$2:$C$991, B$3, 'Scenario Definition Extraction'!$D$2:$D$991, C$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A6) = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, B$1,  'Scenario Definition Extraction'!$B$2:$B$997, B$2,  'Scenario Definition Extraction'!$C$2:$C$997, B$3, 'Scenario Definition Extraction'!$D$2:$D$997, C$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A6) = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="D6" t="str">
-        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, D$1,  'Scenario Definition Extraction'!$B$2:$B$991, D$2,  'Scenario Definition Extraction'!$C$2:$C$991, D$3, 'Scenario Definition Extraction'!$D$2:$D$991, D$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A6) = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, D$1,  'Scenario Definition Extraction'!$B$2:$B$997, D$2,  'Scenario Definition Extraction'!$C$2:$C$997, D$3, 'Scenario Definition Extraction'!$D$2:$D$997, D$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A6) = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="E6" t="str">
-        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, D$1,  'Scenario Definition Extraction'!$B$2:$B$991, D$2,  'Scenario Definition Extraction'!$C$2:$C$991, E$3, 'Scenario Definition Extraction'!$D$2:$D$991, E$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A6) = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, D$1,  'Scenario Definition Extraction'!$B$2:$B$997, D$2,  'Scenario Definition Extraction'!$C$2:$C$997, E$3, 'Scenario Definition Extraction'!$D$2:$D$997, E$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A6) = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="F6" t="str">
-        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, F$1,  'Scenario Definition Extraction'!$B$2:$B$991, F$2,  'Scenario Definition Extraction'!$C$2:$C$991, F$3, 'Scenario Definition Extraction'!$D$2:$D$991, F$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A6) = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, D$1,  'Scenario Definition Extraction'!$B$2:$B$997, F$2,  'Scenario Definition Extraction'!$C$2:$C$997, F$3, 'Scenario Definition Extraction'!$D$2:$D$997, F$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A6) = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="G6" t="str">
-        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, F$1,  'Scenario Definition Extraction'!$B$2:$B$991, F$2,  'Scenario Definition Extraction'!$C$2:$C$991, G$3, 'Scenario Definition Extraction'!$D$2:$D$991, G$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A6) = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, D$1,  'Scenario Definition Extraction'!$B$2:$B$997, F$2,  'Scenario Definition Extraction'!$C$2:$C$997, G$3, 'Scenario Definition Extraction'!$D$2:$D$997, G$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A6) = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6" t="str">
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, H$1,  'Scenario Definition Extraction'!$B$2:$B$997, H$2,  'Scenario Definition Extraction'!$C$2:$C$997, H$3, 'Scenario Definition Extraction'!$D$2:$D$997, H$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A6) = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
+      </c>
+      <c r="I6" t="str">
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, H$1,  'Scenario Definition Extraction'!$B$2:$B$997, H$2,  'Scenario Definition Extraction'!$C$2:$C$997, I$3, 'Scenario Definition Extraction'!$D$2:$D$997, I$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A6) = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15">
       <c r="A7" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B7" t="str">
-        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, B$1,  'Scenario Definition Extraction'!$B$2:$B$991, B$2,  'Scenario Definition Extraction'!$C$2:$C$991, B$3, 'Scenario Definition Extraction'!$D$2:$D$991, B$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A7) = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, B$1,  'Scenario Definition Extraction'!$B$2:$B$997, B$2,  'Scenario Definition Extraction'!$C$2:$C$997, B$3, 'Scenario Definition Extraction'!$D$2:$D$997, B$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A7) = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="C7" t="str">
-        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, B$1,  'Scenario Definition Extraction'!$B$2:$B$991, B$2,  'Scenario Definition Extraction'!$C$2:$C$991, B$3, 'Scenario Definition Extraction'!$D$2:$D$991, C$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A7) = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, B$1,  'Scenario Definition Extraction'!$B$2:$B$997, B$2,  'Scenario Definition Extraction'!$C$2:$C$997, B$3, 'Scenario Definition Extraction'!$D$2:$D$997, C$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A7) = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="D7" t="str">
-        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, D$1,  'Scenario Definition Extraction'!$B$2:$B$991, D$2,  'Scenario Definition Extraction'!$C$2:$C$991, D$3, 'Scenario Definition Extraction'!$D$2:$D$991, D$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A7) = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, D$1,  'Scenario Definition Extraction'!$B$2:$B$997, D$2,  'Scenario Definition Extraction'!$C$2:$C$997, D$3, 'Scenario Definition Extraction'!$D$2:$D$997, D$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A7) = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="E7" t="str">
-        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, D$1,  'Scenario Definition Extraction'!$B$2:$B$991, D$2,  'Scenario Definition Extraction'!$C$2:$C$991, E$3, 'Scenario Definition Extraction'!$D$2:$D$991, E$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A7) = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, D$1,  'Scenario Definition Extraction'!$B$2:$B$997, D$2,  'Scenario Definition Extraction'!$C$2:$C$997, E$3, 'Scenario Definition Extraction'!$D$2:$D$997, E$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A7) = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="F7" t="str">
-        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, F$1,  'Scenario Definition Extraction'!$B$2:$B$991, F$2,  'Scenario Definition Extraction'!$C$2:$C$991, F$3, 'Scenario Definition Extraction'!$D$2:$D$991, F$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A7) = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, D$1,  'Scenario Definition Extraction'!$B$2:$B$997, F$2,  'Scenario Definition Extraction'!$C$2:$C$997, F$3, 'Scenario Definition Extraction'!$D$2:$D$997, F$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A7) = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="G7" t="str">
-        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, F$1,  'Scenario Definition Extraction'!$B$2:$B$991, F$2,  'Scenario Definition Extraction'!$C$2:$C$991, G$3, 'Scenario Definition Extraction'!$D$2:$D$991, G$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A7) = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, D$1,  'Scenario Definition Extraction'!$B$2:$B$997, F$2,  'Scenario Definition Extraction'!$C$2:$C$997, G$3, 'Scenario Definition Extraction'!$D$2:$D$997, G$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A7) = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7" t="str">
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, H$1,  'Scenario Definition Extraction'!$B$2:$B$997, H$2,  'Scenario Definition Extraction'!$C$2:$C$997, H$3, 'Scenario Definition Extraction'!$D$2:$D$997, H$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A7) = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
+      </c>
+      <c r="I7" t="str">
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, H$1,  'Scenario Definition Extraction'!$B$2:$B$997, H$2,  'Scenario Definition Extraction'!$C$2:$C$997, I$3, 'Scenario Definition Extraction'!$D$2:$D$997, I$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A7) = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15">
       <c r="A8" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B8" t="str">
-        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, B$1,  'Scenario Definition Extraction'!$B$2:$B$991, B$2,  'Scenario Definition Extraction'!$C$2:$C$991, B$3, 'Scenario Definition Extraction'!$D$2:$D$991, B$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A8) = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, B$1,  'Scenario Definition Extraction'!$B$2:$B$997, B$2,  'Scenario Definition Extraction'!$C$2:$C$997, B$3, 'Scenario Definition Extraction'!$D$2:$D$997, B$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A8) = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="C8" t="str">
-        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, B$1,  'Scenario Definition Extraction'!$B$2:$B$991, B$2,  'Scenario Definition Extraction'!$C$2:$C$991, B$3, 'Scenario Definition Extraction'!$D$2:$D$991, C$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A8) = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, B$1,  'Scenario Definition Extraction'!$B$2:$B$997, B$2,  'Scenario Definition Extraction'!$C$2:$C$997, B$3, 'Scenario Definition Extraction'!$D$2:$D$997, C$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A8) = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="D8" t="str">
-        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, D$1,  'Scenario Definition Extraction'!$B$2:$B$991, D$2,  'Scenario Definition Extraction'!$C$2:$C$991, D$3, 'Scenario Definition Extraction'!$D$2:$D$991, D$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A8) = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, D$1,  'Scenario Definition Extraction'!$B$2:$B$997, D$2,  'Scenario Definition Extraction'!$C$2:$C$997, D$3, 'Scenario Definition Extraction'!$D$2:$D$997, D$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A8) = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="E8" t="str">
-        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, D$1,  'Scenario Definition Extraction'!$B$2:$B$991, D$2,  'Scenario Definition Extraction'!$C$2:$C$991, E$3, 'Scenario Definition Extraction'!$D$2:$D$991, E$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A8) = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, D$1,  'Scenario Definition Extraction'!$B$2:$B$997, D$2,  'Scenario Definition Extraction'!$C$2:$C$997, E$3, 'Scenario Definition Extraction'!$D$2:$D$997, E$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A8) = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="F8" t="str">
-        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, F$1,  'Scenario Definition Extraction'!$B$2:$B$991, F$2,  'Scenario Definition Extraction'!$C$2:$C$991, F$3, 'Scenario Definition Extraction'!$D$2:$D$991, F$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A8) = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, D$1,  'Scenario Definition Extraction'!$B$2:$B$997, F$2,  'Scenario Definition Extraction'!$C$2:$C$997, F$3, 'Scenario Definition Extraction'!$D$2:$D$997, F$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A8) = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="G8" t="str">
-        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$991, F$1,  'Scenario Definition Extraction'!$B$2:$B$991, F$2,  'Scenario Definition Extraction'!$C$2:$C$991, G$3, 'Scenario Definition Extraction'!$D$2:$D$991, G$4, 'Scenario Definition Extraction'!$E$2:$E$991, $A8) = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, D$1,  'Scenario Definition Extraction'!$B$2:$B$997, F$2,  'Scenario Definition Extraction'!$C$2:$C$997, G$3, 'Scenario Definition Extraction'!$D$2:$D$997, G$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A8) = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
+      <c r="H8" t="str">
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, H$1,  'Scenario Definition Extraction'!$B$2:$B$997, H$2,  'Scenario Definition Extraction'!$C$2:$C$997, H$3, 'Scenario Definition Extraction'!$D$2:$D$997, H$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A8) = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
+      </c>
+      <c r="I8" t="str">
+        <f>IF(COUNTIFS('Scenario Definition Extraction'!$A$2:$A$997, H$1,  'Scenario Definition Extraction'!$B$2:$B$997, H$2,  'Scenario Definition Extraction'!$C$2:$C$997, I$3, 'Scenario Definition Extraction'!$D$2:$D$997, I$4, 'Scenario Definition Extraction'!$E$2:$E$997, $A8) = 0, "Missing", "Complete")</f>
+        <v>Complete</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F2:G2"/>
+  <mergeCells count="8">
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="D1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B6:G8">
+  <conditionalFormatting sqref="B6:I8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Missing"</formula>
     </cfRule>
@@ -1769,7 +1902,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797B3B46-8F2E-4C67-A115-D7583B1B84DB}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -1777,7 +1910,7 @@
     <col min="4" max="4" width="26.7109375" customWidth="1"/>
     <col min="5" max="5" width="52.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="50.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1789,10 +1922,10 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>11</v>
@@ -1821,13 +1954,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="E2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F2" t="s">
         <v>29</v>
@@ -1836,7 +1969,7 @@
         <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="I2" s="7">
         <v>0.9</v>
@@ -1850,13 +1983,13 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="E3" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F3" t="s">
         <v>29</v>
@@ -1865,27 +1998,27 @@
         <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="I3" s="7">
         <v>0.9</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" ht="15">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="E4" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F4" t="s">
         <v>29</v>
@@ -1894,30 +2027,27 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>193</v>
+        <v>100</v>
       </c>
       <c r="I4" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="J4" t="s">
-        <v>194</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="E5" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F5" t="s">
         <v>29</v>
@@ -1926,30 +2056,27 @@
         <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>193</v>
+        <v>100</v>
       </c>
       <c r="I5" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="J5" t="s">
-        <v>194</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E6" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F6" t="s">
         <v>29</v>
@@ -1958,30 +2085,30 @@
         <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="I6" s="7">
         <v>0.8</v>
       </c>
       <c r="J6" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="E7" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F7" t="s">
         <v>29</v>
@@ -1990,30 +2117,30 @@
         <v>30</v>
       </c>
       <c r="H7" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="I7" s="7">
         <v>0.8</v>
       </c>
       <c r="J7" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="E8" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="F8" t="s">
         <v>29</v>
@@ -2022,27 +2149,30 @@
         <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>99</v>
+        <v>202</v>
       </c>
       <c r="I8" s="7">
-        <v>0.9</v>
+        <v>0.8</v>
+      </c>
+      <c r="J8" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="E9" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="F9" t="s">
         <v>29</v>
@@ -2051,27 +2181,30 @@
         <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>99</v>
+        <v>202</v>
       </c>
       <c r="I9" s="7">
-        <v>0.9</v>
+        <v>0.8</v>
+      </c>
+      <c r="J9" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="E10" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="F10" t="s">
         <v>29</v>
@@ -2080,7 +2213,7 @@
         <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="I10" s="7">
         <v>0.9</v>
@@ -2088,19 +2221,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="E11" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="F11" t="s">
         <v>29</v>
@@ -2109,7 +2242,7 @@
         <v>30</v>
       </c>
       <c r="H11" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="I11" s="7">
         <v>0.9</v>
@@ -2117,19 +2250,19 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="E12" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="F12" t="s">
         <v>29</v>
@@ -2138,27 +2271,27 @@
         <v>30</v>
       </c>
       <c r="H12" t="s">
-        <v>193</v>
+        <v>100</v>
       </c>
       <c r="I12" s="7">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="E13" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="F13" t="s">
         <v>29</v>
@@ -2167,202 +2300,382 @@
         <v>30</v>
       </c>
       <c r="H13" t="s">
-        <v>193</v>
+        <v>100</v>
       </c>
       <c r="I13" s="7">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="43.5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E14" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="F14" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="G14" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="H14" t="s">
-        <v>193</v>
-      </c>
-      <c r="I14">
-        <v>1320</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="43.5">
+        <v>107</v>
+      </c>
+      <c r="I14" s="7">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="E15" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="F15" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="G15" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="H15" t="s">
-        <v>193</v>
-      </c>
-      <c r="I15">
-        <v>24</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>196</v>
+        <v>107</v>
+      </c>
+      <c r="I15" s="7">
+        <v>0.9</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="E16" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="F16" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="G16" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="H16" t="s">
-        <v>193</v>
-      </c>
-      <c r="I16">
-        <v>14.084507042253522</v>
-      </c>
-      <c r="J16" t="s">
-        <v>197</v>
+        <v>202</v>
+      </c>
+      <c r="I16" s="7">
+        <v>0.8</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" t="s">
+        <v>198</v>
+      </c>
+      <c r="E17" t="s">
+        <v>201</v>
+      </c>
+      <c r="F17" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" t="s">
+        <v>202</v>
+      </c>
+      <c r="I17" s="7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="43.5">
+      <c r="A18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" t="s">
+        <v>198</v>
+      </c>
+      <c r="E18" t="s">
+        <v>199</v>
+      </c>
+      <c r="F18" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" t="s">
+        <v>202</v>
+      </c>
+      <c r="I18">
+        <v>1320</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="43.5">
+      <c r="A19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" t="s">
+        <v>198</v>
+      </c>
+      <c r="E19" t="s">
+        <v>199</v>
+      </c>
+      <c r="F19" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" t="s">
+        <v>99</v>
+      </c>
+      <c r="H19" t="s">
+        <v>202</v>
+      </c>
+      <c r="I19">
+        <v>24</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="29.25">
+      <c r="A20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" t="s">
+        <v>198</v>
+      </c>
+      <c r="E20" t="s">
+        <v>199</v>
+      </c>
+      <c r="F20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" t="s">
+        <v>82</v>
+      </c>
+      <c r="I20">
+        <v>40</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="29.25">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" t="s">
+        <v>198</v>
+      </c>
+      <c r="E21" t="s">
+        <v>199</v>
+      </c>
+      <c r="F21" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H21" t="s">
+        <v>82</v>
+      </c>
+      <c r="I21">
+        <v>1.69</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
         <v>1</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B22" t="s">
         <v>5</v>
       </c>
-      <c r="C17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" t="s">
-        <v>188</v>
-      </c>
-      <c r="E17" t="s">
-        <v>190</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="C22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" t="s">
+        <v>196</v>
+      </c>
+      <c r="E22" t="s">
+        <v>199</v>
+      </c>
+      <c r="F22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" t="s">
+        <v>99</v>
+      </c>
+      <c r="H22" t="s">
+        <v>202</v>
+      </c>
+      <c r="I22">
+        <v>14.084507042253522</v>
+      </c>
+      <c r="J22" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" t="s">
+        <v>197</v>
+      </c>
+      <c r="E23" t="s">
+        <v>199</v>
+      </c>
+      <c r="F23" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" t="s">
+        <v>99</v>
+      </c>
+      <c r="H23" t="s">
+        <v>202</v>
+      </c>
+      <c r="I23">
+        <v>56.338028169014088</v>
+      </c>
+      <c r="J23" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
         <v>91</v>
       </c>
-      <c r="G17" t="s">
-        <v>92</v>
-      </c>
-      <c r="H17" t="s">
-        <v>193</v>
-      </c>
-      <c r="I17">
-        <v>56.338028169014088</v>
-      </c>
-      <c r="J17" t="s">
+      <c r="D24" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" t="s">
+      <c r="E24" t="s">
+        <v>199</v>
+      </c>
+      <c r="F24" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" t="s">
+        <v>99</v>
+      </c>
+      <c r="H24" t="s">
+        <v>210</v>
+      </c>
+      <c r="I24">
+        <v>42.5</v>
+      </c>
+      <c r="J24" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15">
+      <c r="A25" t="s">
         <v>3</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B25" t="s">
         <v>7</v>
       </c>
-      <c r="C18" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" t="s">
-        <v>189</v>
-      </c>
-      <c r="E18" t="s">
-        <v>190</v>
-      </c>
-      <c r="F18" t="s">
-        <v>91</v>
-      </c>
-      <c r="G18" t="s">
-        <v>92</v>
-      </c>
-      <c r="H18" t="s">
+      <c r="C25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" t="s">
+        <v>198</v>
+      </c>
+      <c r="E25" t="s">
         <v>199</v>
       </c>
-      <c r="I18">
-        <v>42.5</v>
-      </c>
-      <c r="J18" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15">
-      <c r="A19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E19" t="s">
-        <v>190</v>
-      </c>
-      <c r="F19" t="s">
-        <v>91</v>
-      </c>
-      <c r="G19" t="s">
-        <v>92</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="I19">
+      <c r="F25" t="s">
+        <v>98</v>
+      </c>
+      <c r="G25" t="s">
+        <v>99</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="I25">
         <v>1.3</v>
       </c>
-      <c r="J19" s="6" t="s">
-        <v>202</v>
+      <c r="J25" s="6" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -2379,8 +2692,10 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="J19" r:id="rId1" xr:uid="{8B29D165-A493-48F3-B663-85CB453EE758}"/>
-    <hyperlink ref="H19" r:id="rId2" xr:uid="{3DC1B296-F88E-408E-956F-0351AD5F515E}"/>
+    <hyperlink ref="J25" r:id="rId1" xr:uid="{8B29D165-A493-48F3-B663-85CB453EE758}"/>
+    <hyperlink ref="H25" r:id="rId2" xr:uid="{3DC1B296-F88E-408E-956F-0351AD5F515E}"/>
+    <hyperlink ref="J20" r:id="rId3" xr:uid="{EA845FCE-F931-471E-B7AD-CCDF4F57AEA4}"/>
+    <hyperlink ref="J21" r:id="rId4" xr:uid="{E1E2866D-3A5C-4D33-8B50-C6AA8A296518}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -2394,7 +2709,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1237FDC8-82EB-4B1F-9280-B2359248B6FE}">
           <x14:formula1>
-            <xm:f>'Scenario Definition Progress'!$B$4:$G$4</xm:f>
+            <xm:f>'Scenario Definition Progress'!$B$4:$I$4</xm:f>
           </x14:formula1>
           <xm:sqref>D1:D1048576</xm:sqref>
         </x14:dataValidation>
@@ -2416,22 +2731,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="43.5">
@@ -2439,13 +2754,13 @@
         <v>49</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="E2">
         <v>2021</v>
@@ -2453,30 +2768,30 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="B3" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B4" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="D4" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F4" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -2490,7 +2805,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7501F0-08E1-4A63-A382-F6741C91E79A}">
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M106"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -2499,6 +2814,7 @@
     <col min="5" max="5" width="60.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="10.140625" customWidth="1"/>
     <col min="13" max="13" width="50.42578125" customWidth="1"/>
   </cols>
@@ -4748,6 +5064,1356 @@
       </c>
       <c r="M65" s="5" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="15">
+      <c r="A66" t="s">
+        <v>2</v>
+      </c>
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" t="s">
+        <v>27</v>
+      </c>
+      <c r="D66" t="s">
+        <v>27</v>
+      </c>
+      <c r="E66" t="s">
+        <v>17</v>
+      </c>
+      <c r="F66" t="s">
+        <v>29</v>
+      </c>
+      <c r="G66" t="s">
+        <v>30</v>
+      </c>
+      <c r="I66" t="s">
+        <v>47</v>
+      </c>
+      <c r="J66" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="M66" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="43.5">
+      <c r="A67" t="s">
+        <v>2</v>
+      </c>
+      <c r="B67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" t="s">
+        <v>33</v>
+      </c>
+      <c r="D67" t="s">
+        <v>28</v>
+      </c>
+      <c r="E67" t="s">
+        <v>14</v>
+      </c>
+      <c r="F67" t="s">
+        <v>34</v>
+      </c>
+      <c r="G67" t="s">
+        <v>35</v>
+      </c>
+      <c r="H67">
+        <v>2021</v>
+      </c>
+      <c r="I67" t="s">
+        <v>49</v>
+      </c>
+      <c r="J67">
+        <f>61.2*J73</f>
+        <v>32.803200000000004</v>
+      </c>
+      <c r="M67" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="43.5">
+      <c r="A68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" t="s">
+        <v>37</v>
+      </c>
+      <c r="D68" t="s">
+        <v>28</v>
+      </c>
+      <c r="E68" t="s">
+        <v>14</v>
+      </c>
+      <c r="F68" t="s">
+        <v>34</v>
+      </c>
+      <c r="G68" t="s">
+        <v>35</v>
+      </c>
+      <c r="H68">
+        <v>2021</v>
+      </c>
+      <c r="I68" t="s">
+        <v>49</v>
+      </c>
+      <c r="J68">
+        <f>34.2*J74</f>
+        <v>11.491200000000001</v>
+      </c>
+      <c r="M68" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="43.5">
+      <c r="A69" t="s">
+        <v>2</v>
+      </c>
+      <c r="B69" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" t="s">
+        <v>38</v>
+      </c>
+      <c r="D69" t="s">
+        <v>28</v>
+      </c>
+      <c r="E69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69" t="s">
+        <v>34</v>
+      </c>
+      <c r="G69" t="s">
+        <v>35</v>
+      </c>
+      <c r="H69">
+        <v>2021</v>
+      </c>
+      <c r="I69" t="s">
+        <v>49</v>
+      </c>
+      <c r="J69">
+        <f>52.4*J75</f>
+        <v>23.475200000000001</v>
+      </c>
+      <c r="M69" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="43.5">
+      <c r="A70" t="s">
+        <v>2</v>
+      </c>
+      <c r="B70" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" t="s">
+        <v>39</v>
+      </c>
+      <c r="D70" t="s">
+        <v>28</v>
+      </c>
+      <c r="E70" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" t="s">
+        <v>34</v>
+      </c>
+      <c r="G70" t="s">
+        <v>35</v>
+      </c>
+      <c r="H70">
+        <v>2021</v>
+      </c>
+      <c r="I70" t="s">
+        <v>49</v>
+      </c>
+      <c r="J70">
+        <f>60.7*J76</f>
+        <v>33.142200000000003</v>
+      </c>
+      <c r="M70" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="43.5">
+      <c r="A71" t="s">
+        <v>2</v>
+      </c>
+      <c r="B71" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" t="s">
+        <v>40</v>
+      </c>
+      <c r="D71" t="s">
+        <v>28</v>
+      </c>
+      <c r="E71" t="s">
+        <v>14</v>
+      </c>
+      <c r="F71" t="s">
+        <v>34</v>
+      </c>
+      <c r="G71" t="s">
+        <v>35</v>
+      </c>
+      <c r="H71">
+        <v>2021</v>
+      </c>
+      <c r="I71" t="s">
+        <v>49</v>
+      </c>
+      <c r="J71">
+        <f>73.7*J77</f>
+        <v>46.652100000000004</v>
+      </c>
+      <c r="M71" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="43.5">
+      <c r="A72" t="s">
+        <v>2</v>
+      </c>
+      <c r="B72" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" t="s">
+        <v>41</v>
+      </c>
+      <c r="D72" t="s">
+        <v>28</v>
+      </c>
+      <c r="E72" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" t="s">
+        <v>34</v>
+      </c>
+      <c r="G72" t="s">
+        <v>35</v>
+      </c>
+      <c r="H72">
+        <v>2021</v>
+      </c>
+      <c r="I72" t="s">
+        <v>49</v>
+      </c>
+      <c r="J72">
+        <f>79.5*J78</f>
+        <v>53.742000000000004</v>
+      </c>
+      <c r="M72" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="29.25">
+      <c r="A73" t="s">
+        <v>2</v>
+      </c>
+      <c r="B73" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" t="s">
+        <v>33</v>
+      </c>
+      <c r="D73" t="s">
+        <v>28</v>
+      </c>
+      <c r="E73" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" t="s">
+        <v>29</v>
+      </c>
+      <c r="G73" t="s">
+        <v>30</v>
+      </c>
+      <c r="I73" t="s">
+        <v>84</v>
+      </c>
+      <c r="J73" s="21">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="M73" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13">
+      <c r="A74" t="s">
+        <v>2</v>
+      </c>
+      <c r="B74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" t="s">
+        <v>37</v>
+      </c>
+      <c r="D74" t="s">
+        <v>28</v>
+      </c>
+      <c r="E74" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74" t="s">
+        <v>29</v>
+      </c>
+      <c r="G74" t="s">
+        <v>30</v>
+      </c>
+      <c r="I74" t="s">
+        <v>84</v>
+      </c>
+      <c r="J74" s="21">
+        <v>0.33600000000000002</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
+      <c r="A75" t="s">
+        <v>2</v>
+      </c>
+      <c r="B75" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" t="s">
+        <v>38</v>
+      </c>
+      <c r="D75" t="s">
+        <v>28</v>
+      </c>
+      <c r="E75" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75" t="s">
+        <v>29</v>
+      </c>
+      <c r="G75" t="s">
+        <v>30</v>
+      </c>
+      <c r="I75" t="s">
+        <v>84</v>
+      </c>
+      <c r="J75" s="21">
+        <v>0.44800000000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13">
+      <c r="A76" t="s">
+        <v>2</v>
+      </c>
+      <c r="B76" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" t="s">
+        <v>39</v>
+      </c>
+      <c r="D76" t="s">
+        <v>28</v>
+      </c>
+      <c r="E76" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" t="s">
+        <v>29</v>
+      </c>
+      <c r="G76" t="s">
+        <v>30</v>
+      </c>
+      <c r="I76" t="s">
+        <v>84</v>
+      </c>
+      <c r="J76" s="21">
+        <v>0.54600000000000004</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
+      <c r="A77" t="s">
+        <v>2</v>
+      </c>
+      <c r="B77" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" t="s">
+        <v>40</v>
+      </c>
+      <c r="D77" t="s">
+        <v>28</v>
+      </c>
+      <c r="E77" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77" t="s">
+        <v>29</v>
+      </c>
+      <c r="G77" t="s">
+        <v>30</v>
+      </c>
+      <c r="I77" t="s">
+        <v>84</v>
+      </c>
+      <c r="J77" s="21">
+        <v>0.63300000000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13">
+      <c r="A78" t="s">
+        <v>2</v>
+      </c>
+      <c r="B78" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" t="s">
+        <v>41</v>
+      </c>
+      <c r="D78" t="s">
+        <v>28</v>
+      </c>
+      <c r="E78" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" t="s">
+        <v>29</v>
+      </c>
+      <c r="G78" t="s">
+        <v>30</v>
+      </c>
+      <c r="I78" t="s">
+        <v>84</v>
+      </c>
+      <c r="J78" s="21">
+        <v>0.67600000000000005</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="29.25">
+      <c r="A79" t="s">
+        <v>2</v>
+      </c>
+      <c r="B79" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" t="s">
+        <v>33</v>
+      </c>
+      <c r="D79" t="s">
+        <v>28</v>
+      </c>
+      <c r="E79" t="s">
+        <v>14</v>
+      </c>
+      <c r="F79" t="s">
+        <v>42</v>
+      </c>
+      <c r="G79" t="s">
+        <v>35</v>
+      </c>
+      <c r="H79">
+        <v>2021</v>
+      </c>
+      <c r="I79" t="s">
+        <v>49</v>
+      </c>
+      <c r="J79">
+        <f>(84.6-30.5)/1.35</f>
+        <v>40.074074074074069</v>
+      </c>
+      <c r="M79" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13">
+      <c r="A80" t="s">
+        <v>2</v>
+      </c>
+      <c r="B80" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" t="s">
+        <v>37</v>
+      </c>
+      <c r="D80" t="s">
+        <v>28</v>
+      </c>
+      <c r="E80" t="s">
+        <v>14</v>
+      </c>
+      <c r="F80" t="s">
+        <v>42</v>
+      </c>
+      <c r="G80" t="s">
+        <v>35</v>
+      </c>
+      <c r="H80">
+        <v>2021</v>
+      </c>
+      <c r="I80" t="s">
+        <v>49</v>
+      </c>
+      <c r="J80">
+        <f>(47.2-13.7)/1.35</f>
+        <v>24.814814814814813</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13">
+      <c r="A81" t="s">
+        <v>2</v>
+      </c>
+      <c r="B81" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" t="s">
+        <v>38</v>
+      </c>
+      <c r="D81" t="s">
+        <v>28</v>
+      </c>
+      <c r="E81" t="s">
+        <v>14</v>
+      </c>
+      <c r="F81" t="s">
+        <v>42</v>
+      </c>
+      <c r="G81" t="s">
+        <v>35</v>
+      </c>
+      <c r="H81">
+        <v>2021</v>
+      </c>
+      <c r="I81" t="s">
+        <v>49</v>
+      </c>
+      <c r="J81">
+        <f>(71.4-26.4)/1.35</f>
+        <v>33.333333333333336</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13">
+      <c r="A82" t="s">
+        <v>2</v>
+      </c>
+      <c r="B82" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" t="s">
+        <v>39</v>
+      </c>
+      <c r="D82" t="s">
+        <v>28</v>
+      </c>
+      <c r="E82" t="s">
+        <v>14</v>
+      </c>
+      <c r="F82" t="s">
+        <v>42</v>
+      </c>
+      <c r="G82" t="s">
+        <v>35</v>
+      </c>
+      <c r="H82">
+        <v>2021</v>
+      </c>
+      <c r="I82" t="s">
+        <v>49</v>
+      </c>
+      <c r="J82">
+        <f>(81.1-33.8)/1.35</f>
+        <v>35.037037037037031</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13">
+      <c r="A83" t="s">
+        <v>2</v>
+      </c>
+      <c r="B83" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" t="s">
+        <v>40</v>
+      </c>
+      <c r="D83" t="s">
+        <v>28</v>
+      </c>
+      <c r="E83" t="s">
+        <v>14</v>
+      </c>
+      <c r="F83" t="s">
+        <v>42</v>
+      </c>
+      <c r="G83" t="s">
+        <v>35</v>
+      </c>
+      <c r="H83">
+        <v>2021</v>
+      </c>
+      <c r="I83" t="s">
+        <v>49</v>
+      </c>
+      <c r="J83">
+        <f>(96.3-45.3)/1.35</f>
+        <v>37.777777777777779</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13">
+      <c r="A84" t="s">
+        <v>2</v>
+      </c>
+      <c r="B84" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" t="s">
+        <v>41</v>
+      </c>
+      <c r="D84" t="s">
+        <v>28</v>
+      </c>
+      <c r="E84" t="s">
+        <v>14</v>
+      </c>
+      <c r="F84" t="s">
+        <v>42</v>
+      </c>
+      <c r="G84" t="s">
+        <v>35</v>
+      </c>
+      <c r="H84">
+        <v>2021</v>
+      </c>
+      <c r="I84" t="s">
+        <v>49</v>
+      </c>
+      <c r="J84">
+        <f>(103.1-50.4)/1.35</f>
+        <v>39.037037037037031</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="43.5">
+      <c r="A85" t="s">
+        <v>2</v>
+      </c>
+      <c r="B85" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" t="s">
+        <v>33</v>
+      </c>
+      <c r="D85" t="s">
+        <v>33</v>
+      </c>
+      <c r="E85" t="s">
+        <v>16</v>
+      </c>
+      <c r="F85" t="s">
+        <v>34</v>
+      </c>
+      <c r="G85" t="s">
+        <v>35</v>
+      </c>
+      <c r="H85">
+        <v>2021</v>
+      </c>
+      <c r="I85" t="s">
+        <v>49</v>
+      </c>
+      <c r="J85">
+        <f>38.3*J101</f>
+        <v>20.5288</v>
+      </c>
+      <c r="M85" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="43.5">
+      <c r="A86" t="s">
+        <v>2</v>
+      </c>
+      <c r="B86" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" t="s">
+        <v>33</v>
+      </c>
+      <c r="D86" t="s">
+        <v>28</v>
+      </c>
+      <c r="E86" t="s">
+        <v>16</v>
+      </c>
+      <c r="F86" t="s">
+        <v>34</v>
+      </c>
+      <c r="G86" t="s">
+        <v>35</v>
+      </c>
+      <c r="H86">
+        <v>2021</v>
+      </c>
+      <c r="I86" t="s">
+        <v>49</v>
+      </c>
+      <c r="J86">
+        <f>35.5*J101</f>
+        <v>19.028000000000002</v>
+      </c>
+      <c r="M86" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="43.5">
+      <c r="A87" t="s">
+        <v>2</v>
+      </c>
+      <c r="B87" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" t="s">
+        <v>33</v>
+      </c>
+      <c r="D87" t="s">
+        <v>77</v>
+      </c>
+      <c r="E87" t="s">
+        <v>16</v>
+      </c>
+      <c r="F87" t="s">
+        <v>34</v>
+      </c>
+      <c r="G87" t="s">
+        <v>35</v>
+      </c>
+      <c r="H87">
+        <v>2021</v>
+      </c>
+      <c r="I87" t="s">
+        <v>49</v>
+      </c>
+      <c r="J87">
+        <f>41*J101</f>
+        <v>21.976000000000003</v>
+      </c>
+      <c r="M87" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13">
+      <c r="A88" t="s">
+        <v>2</v>
+      </c>
+      <c r="B88" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" t="s">
+        <v>37</v>
+      </c>
+      <c r="D88" t="s">
+        <v>27</v>
+      </c>
+      <c r="E88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F88" t="s">
+        <v>34</v>
+      </c>
+      <c r="G88" t="s">
+        <v>35</v>
+      </c>
+      <c r="H88">
+        <v>2021</v>
+      </c>
+      <c r="I88" t="s">
+        <v>49</v>
+      </c>
+      <c r="J88">
+        <v>11.491200000000001</v>
+      </c>
+      <c r="M88" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13">
+      <c r="A89" t="s">
+        <v>2</v>
+      </c>
+      <c r="B89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" t="s">
+        <v>38</v>
+      </c>
+      <c r="D89" t="s">
+        <v>27</v>
+      </c>
+      <c r="E89" t="s">
+        <v>16</v>
+      </c>
+      <c r="F89" t="s">
+        <v>34</v>
+      </c>
+      <c r="G89" t="s">
+        <v>35</v>
+      </c>
+      <c r="H89">
+        <v>2021</v>
+      </c>
+      <c r="I89" t="s">
+        <v>49</v>
+      </c>
+      <c r="J89">
+        <v>23.475200000000001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13">
+      <c r="A90" t="s">
+        <v>2</v>
+      </c>
+      <c r="B90" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" t="s">
+        <v>39</v>
+      </c>
+      <c r="D90" t="s">
+        <v>27</v>
+      </c>
+      <c r="E90" t="s">
+        <v>16</v>
+      </c>
+      <c r="F90" t="s">
+        <v>34</v>
+      </c>
+      <c r="G90" t="s">
+        <v>35</v>
+      </c>
+      <c r="H90">
+        <v>2021</v>
+      </c>
+      <c r="I90" t="s">
+        <v>49</v>
+      </c>
+      <c r="J90">
+        <v>33.142200000000003</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13">
+      <c r="A91" t="s">
+        <v>2</v>
+      </c>
+      <c r="B91" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" t="s">
+        <v>40</v>
+      </c>
+      <c r="D91" t="s">
+        <v>27</v>
+      </c>
+      <c r="E91" t="s">
+        <v>16</v>
+      </c>
+      <c r="F91" t="s">
+        <v>34</v>
+      </c>
+      <c r="G91" t="s">
+        <v>35</v>
+      </c>
+      <c r="H91">
+        <v>2021</v>
+      </c>
+      <c r="I91" t="s">
+        <v>49</v>
+      </c>
+      <c r="J91">
+        <v>46.652100000000004</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13">
+      <c r="A92" t="s">
+        <v>2</v>
+      </c>
+      <c r="B92" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" t="s">
+        <v>41</v>
+      </c>
+      <c r="D92" t="s">
+        <v>27</v>
+      </c>
+      <c r="E92" t="s">
+        <v>16</v>
+      </c>
+      <c r="F92" t="s">
+        <v>34</v>
+      </c>
+      <c r="G92" t="s">
+        <v>35</v>
+      </c>
+      <c r="H92">
+        <v>2021</v>
+      </c>
+      <c r="I92" t="s">
+        <v>49</v>
+      </c>
+      <c r="J92">
+        <v>53.742000000000004</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="29.25">
+      <c r="A93" t="s">
+        <v>2</v>
+      </c>
+      <c r="B93" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" t="s">
+        <v>33</v>
+      </c>
+      <c r="D93" t="s">
+        <v>33</v>
+      </c>
+      <c r="E93" t="s">
+        <v>16</v>
+      </c>
+      <c r="F93" t="s">
+        <v>42</v>
+      </c>
+      <c r="G93" t="s">
+        <v>35</v>
+      </c>
+      <c r="H93">
+        <v>2021</v>
+      </c>
+      <c r="I93" t="s">
+        <v>49</v>
+      </c>
+      <c r="J93">
+        <f>(53.6-19)/1.35</f>
+        <v>25.62962962962963</v>
+      </c>
+      <c r="M93" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="29.25">
+      <c r="A94" t="s">
+        <v>2</v>
+      </c>
+      <c r="B94" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" t="s">
+        <v>33</v>
+      </c>
+      <c r="D94" t="s">
+        <v>28</v>
+      </c>
+      <c r="E94" t="s">
+        <v>16</v>
+      </c>
+      <c r="F94" t="s">
+        <v>42</v>
+      </c>
+      <c r="G94" t="s">
+        <v>35</v>
+      </c>
+      <c r="H94">
+        <v>2021</v>
+      </c>
+      <c r="I94" t="s">
+        <v>49</v>
+      </c>
+      <c r="J94">
+        <f>(49.5-17.1)/1.35</f>
+        <v>23.999999999999996</v>
+      </c>
+      <c r="M94" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="29.25">
+      <c r="A95" t="s">
+        <v>2</v>
+      </c>
+      <c r="B95" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" t="s">
+        <v>33</v>
+      </c>
+      <c r="D95" t="s">
+        <v>77</v>
+      </c>
+      <c r="E95" t="s">
+        <v>16</v>
+      </c>
+      <c r="F95" t="s">
+        <v>42</v>
+      </c>
+      <c r="G95" t="s">
+        <v>35</v>
+      </c>
+      <c r="H95">
+        <v>2021</v>
+      </c>
+      <c r="I95" t="s">
+        <v>49</v>
+      </c>
+      <c r="J95">
+        <f>(57.6-20.7)/1.35</f>
+        <v>27.333333333333336</v>
+      </c>
+      <c r="M95" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13">
+      <c r="A96" t="s">
+        <v>2</v>
+      </c>
+      <c r="B96" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" t="s">
+        <v>37</v>
+      </c>
+      <c r="D96" t="s">
+        <v>27</v>
+      </c>
+      <c r="E96" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" t="s">
+        <v>42</v>
+      </c>
+      <c r="G96" t="s">
+        <v>35</v>
+      </c>
+      <c r="H96">
+        <v>2021</v>
+      </c>
+      <c r="I96" t="s">
+        <v>49</v>
+      </c>
+      <c r="J96">
+        <f>(47.2-13.7)/1.35</f>
+        <v>24.814814814814813</v>
+      </c>
+      <c r="M96" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13">
+      <c r="A97" t="s">
+        <v>2</v>
+      </c>
+      <c r="B97" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" t="s">
+        <v>38</v>
+      </c>
+      <c r="D97" t="s">
+        <v>27</v>
+      </c>
+      <c r="E97" t="s">
+        <v>16</v>
+      </c>
+      <c r="F97" t="s">
+        <v>42</v>
+      </c>
+      <c r="G97" t="s">
+        <v>35</v>
+      </c>
+      <c r="H97">
+        <v>2021</v>
+      </c>
+      <c r="I97" t="s">
+        <v>49</v>
+      </c>
+      <c r="J97">
+        <f>(71.4-26.4)/1.35</f>
+        <v>33.333333333333336</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13">
+      <c r="A98" t="s">
+        <v>2</v>
+      </c>
+      <c r="B98" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" t="s">
+        <v>39</v>
+      </c>
+      <c r="D98" t="s">
+        <v>27</v>
+      </c>
+      <c r="E98" t="s">
+        <v>16</v>
+      </c>
+      <c r="F98" t="s">
+        <v>42</v>
+      </c>
+      <c r="G98" t="s">
+        <v>35</v>
+      </c>
+      <c r="H98">
+        <v>2021</v>
+      </c>
+      <c r="I98" t="s">
+        <v>49</v>
+      </c>
+      <c r="J98">
+        <f>(81.1-33.8)/1.35</f>
+        <v>35.037037037037031</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13">
+      <c r="A99" t="s">
+        <v>2</v>
+      </c>
+      <c r="B99" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" t="s">
+        <v>40</v>
+      </c>
+      <c r="D99" t="s">
+        <v>27</v>
+      </c>
+      <c r="E99" t="s">
+        <v>16</v>
+      </c>
+      <c r="F99" t="s">
+        <v>42</v>
+      </c>
+      <c r="G99" t="s">
+        <v>35</v>
+      </c>
+      <c r="H99">
+        <v>2021</v>
+      </c>
+      <c r="I99" t="s">
+        <v>49</v>
+      </c>
+      <c r="J99">
+        <f>(96.3-45.3)/1.35</f>
+        <v>37.777777777777779</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13">
+      <c r="A100" t="s">
+        <v>2</v>
+      </c>
+      <c r="B100" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" t="s">
+        <v>41</v>
+      </c>
+      <c r="D100" t="s">
+        <v>27</v>
+      </c>
+      <c r="E100" t="s">
+        <v>16</v>
+      </c>
+      <c r="F100" t="s">
+        <v>42</v>
+      </c>
+      <c r="G100" t="s">
+        <v>35</v>
+      </c>
+      <c r="H100">
+        <v>2021</v>
+      </c>
+      <c r="I100" t="s">
+        <v>49</v>
+      </c>
+      <c r="J100">
+        <f>(103.1-50.4)/1.35</f>
+        <v>39.037037037037031</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" ht="29.25">
+      <c r="A101" t="s">
+        <v>2</v>
+      </c>
+      <c r="B101" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" t="s">
+        <v>33</v>
+      </c>
+      <c r="D101" t="s">
+        <v>27</v>
+      </c>
+      <c r="E101" t="s">
+        <v>15</v>
+      </c>
+      <c r="F101" t="s">
+        <v>29</v>
+      </c>
+      <c r="G101" t="s">
+        <v>30</v>
+      </c>
+      <c r="I101" t="s">
+        <v>84</v>
+      </c>
+      <c r="J101" s="21">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="M101" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13">
+      <c r="A102" t="s">
+        <v>2</v>
+      </c>
+      <c r="B102" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" t="s">
+        <v>37</v>
+      </c>
+      <c r="D102" t="s">
+        <v>27</v>
+      </c>
+      <c r="E102" t="s">
+        <v>15</v>
+      </c>
+      <c r="F102" t="s">
+        <v>29</v>
+      </c>
+      <c r="G102" t="s">
+        <v>30</v>
+      </c>
+      <c r="I102" t="s">
+        <v>84</v>
+      </c>
+      <c r="J102" s="21">
+        <v>0.33600000000000002</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13">
+      <c r="A103" t="s">
+        <v>2</v>
+      </c>
+      <c r="B103" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" t="s">
+        <v>38</v>
+      </c>
+      <c r="D103" t="s">
+        <v>27</v>
+      </c>
+      <c r="E103" t="s">
+        <v>15</v>
+      </c>
+      <c r="F103" t="s">
+        <v>29</v>
+      </c>
+      <c r="G103" t="s">
+        <v>30</v>
+      </c>
+      <c r="I103" t="s">
+        <v>84</v>
+      </c>
+      <c r="J103" s="21">
+        <v>0.44800000000000001</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13">
+      <c r="A104" t="s">
+        <v>2</v>
+      </c>
+      <c r="B104" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" t="s">
+        <v>39</v>
+      </c>
+      <c r="D104" t="s">
+        <v>27</v>
+      </c>
+      <c r="E104" t="s">
+        <v>15</v>
+      </c>
+      <c r="F104" t="s">
+        <v>29</v>
+      </c>
+      <c r="G104" t="s">
+        <v>30</v>
+      </c>
+      <c r="I104" t="s">
+        <v>84</v>
+      </c>
+      <c r="J104" s="21">
+        <v>0.54600000000000004</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13">
+      <c r="A105" t="s">
+        <v>2</v>
+      </c>
+      <c r="B105" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" t="s">
+        <v>40</v>
+      </c>
+      <c r="D105" t="s">
+        <v>27</v>
+      </c>
+      <c r="E105" t="s">
+        <v>15</v>
+      </c>
+      <c r="F105" t="s">
+        <v>29</v>
+      </c>
+      <c r="G105" t="s">
+        <v>30</v>
+      </c>
+      <c r="I105" t="s">
+        <v>84</v>
+      </c>
+      <c r="J105" s="21">
+        <v>0.63300000000000001</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13">
+      <c r="A106" t="s">
+        <v>2</v>
+      </c>
+      <c r="B106" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" t="s">
+        <v>41</v>
+      </c>
+      <c r="D106" t="s">
+        <v>27</v>
+      </c>
+      <c r="E106" t="s">
+        <v>15</v>
+      </c>
+      <c r="F106" t="s">
+        <v>29</v>
+      </c>
+      <c r="G106" t="s">
+        <v>30</v>
+      </c>
+      <c r="I106" t="s">
+        <v>84</v>
+      </c>
+      <c r="J106" s="21">
+        <v>0.67600000000000005</v>
       </c>
     </row>
   </sheetData>
@@ -4789,7 +6455,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EC50408-61D8-4A10-93E8-9867356C2F54}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="52.42578125" bestFit="1" customWidth="1"/>
@@ -4797,10 +6463,10 @@
     <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="15.5703125" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:17" ht="15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4816,14 +6482,18 @@
       <c r="G1" s="33"/>
       <c r="H1" s="33"/>
       <c r="I1" s="33"/>
-      <c r="J1" s="34" t="s">
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+    </row>
+    <row r="2" spans="1:17" ht="15">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -4845,37 +6515,51 @@
       <c r="K2" s="33"/>
       <c r="L2" s="33"/>
       <c r="M2" s="33"/>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+    </row>
+    <row r="3" spans="1:17" ht="15">
       <c r="A3" s="3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C3" s="33"/>
       <c r="D3" s="33" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E3" s="33"/>
       <c r="F3" s="33" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G3" s="33"/>
       <c r="H3" s="33" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I3" s="33"/>
       <c r="J3" s="33" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="K3" s="33"/>
       <c r="L3" s="33" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="M3" s="33"/>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="O3" s="33"/>
+      <c r="P3" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q3" s="33"/>
+    </row>
+    <row r="4" spans="1:17" ht="15">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -4915,8 +6599,20 @@
       <c r="M4" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="15">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -4927,160 +6623,199 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:17" ht="15">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F6" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G6" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H6" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "Total",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A6, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$944, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$944, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$944, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$944, "Total",  'Country-Vehicle-Fort Extraction'!$E$2:$E$944, $A6, 'Country-Vehicle-Fort Extraction'!$J$2:$J$944, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="I6" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "&lt;&gt;All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A6, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$944, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$944, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$944, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$944, "&lt;&gt;All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$944, $A6, 'Country-Vehicle-Fort Extraction'!$J$2:$J$944, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Complete</v>
       </c>
       <c r="J6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K6" t="s">
+        <v>93</v>
+      </c>
+      <c r="L6" t="s">
+        <v>93</v>
+      </c>
+      <c r="M6" t="s">
+        <v>93</v>
+      </c>
+      <c r="N6" t="s">
         <v>13</v>
       </c>
-      <c r="K6" t="s">
+      <c r="O6" t="s">
         <v>13</v>
       </c>
-      <c r="L6" t="s">
+      <c r="P6" t="s">
         <v>13</v>
       </c>
-      <c r="M6" t="s">
+      <c r="Q6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:17" ht="15">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F7" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G7" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "Total",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$944, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$944, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$944, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$944, "Total",  'Country-Vehicle-Fort Extraction'!$E$2:$E$944, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$944, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="I7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "&lt;&gt;Total",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$944, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$944, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$944, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$944, "&lt;&gt;Total",  'Country-Vehicle-Fort Extraction'!$E$2:$E$944, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$944, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
-      <c r="J7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, J$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, J$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, J$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+      <c r="J7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K7" t="s">
+        <v>93</v>
+      </c>
+      <c r="L7" t="s">
+        <v>93</v>
+      </c>
+      <c r="M7" t="s">
+        <v>93</v>
+      </c>
+      <c r="N7" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$944, N$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$944, N$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$944, N$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$944, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$944, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$944, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
-      <c r="K7" t="s">
-        <v>89</v>
-      </c>
-      <c r="L7" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, J$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, J$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, L$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+      <c r="O7" t="s">
+        <v>96</v>
+      </c>
+      <c r="P7" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$944, N$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$944, N$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$944, P$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$944, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$944, $A7, 'Country-Vehicle-Fort Extraction'!$J$2:$J$944, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
-      <c r="M7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="Q7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="15">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F8" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G8" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H8" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "Total",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A8, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$944, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$944, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$944, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$944, "Total",  'Country-Vehicle-Fort Extraction'!$E$2:$E$944, $A8, 'Country-Vehicle-Fort Extraction'!$J$2:$J$944, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="I8" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "&lt;&gt;Total",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A8, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$944, F$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$944, F$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$944, H$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$944, "&lt;&gt;Total",  'Country-Vehicle-Fort Extraction'!$E$2:$E$944, $A8, 'Country-Vehicle-Fort Extraction'!$J$2:$J$944, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
-      <c r="J8" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, J$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, J$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, J$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A8, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+      <c r="J8" t="s">
+        <v>93</v>
+      </c>
+      <c r="K8" t="s">
+        <v>93</v>
+      </c>
+      <c r="L8" t="s">
+        <v>93</v>
+      </c>
+      <c r="M8" t="s">
+        <v>93</v>
+      </c>
+      <c r="N8" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$944, N$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$944, N$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$944, N$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$944, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$944, $A8, 'Country-Vehicle-Fort Extraction'!$J$2:$J$944, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
-      <c r="K8" t="s">
-        <v>89</v>
-      </c>
-      <c r="L8" t="str">
-        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$940, J$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$940, J$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$940, L$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$940, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$940, $A8, 'Country-Vehicle-Fort Extraction'!$J$2:$J$940, "&lt;&gt;") = 0, "Missing", "Complete")</f>
+      <c r="O8" t="s">
+        <v>96</v>
+      </c>
+      <c r="P8" t="str">
+        <f>IF(COUNTIFS('Country-Vehicle-Fort Extraction'!$A$2:$A$944, N$1,  'Country-Vehicle-Fort Extraction'!$B$2:$B$944, N$2,  'Country-Vehicle-Fort Extraction'!$C$2:$C$944, P$3, 'Country-Vehicle-Fort Extraction'!$D$2:$D$944, "All",  'Country-Vehicle-Fort Extraction'!$E$2:$E$944, $A8, 'Country-Vehicle-Fort Extraction'!$J$2:$J$944, "&lt;&gt;") = 0, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
-      <c r="M8" t="s">
-        <v>89</v>
+      <c r="Q8" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
+  <mergeCells count="15">
+    <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P3:Q3"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F1:I1"/>
     <mergeCell ref="F2:I2"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="F1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B6:M6 I6:M7 B7:I7">
+  <conditionalFormatting sqref="B6:Q7">
     <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"Missing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:M8">
+  <conditionalFormatting sqref="H8:I8 N8:Q8">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Missing"</formula>
     </cfRule>
@@ -5091,7 +6826,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC26D125-533B-4E2C-8B10-83B96EF6CBCB}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -5111,7 +6846,7 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>10</v>
@@ -5149,13 +6884,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F2" t="s">
         <v>29</v>
@@ -5178,19 +6913,19 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
         <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F3" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="I3" t="s">
         <v>47</v>
@@ -5199,21 +6934,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" ht="15">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F4" t="s">
         <v>29</v>
@@ -5225,57 +6960,59 @@
         <v>47</v>
       </c>
       <c r="J4" s="7">
-        <v>0.61875637104994907</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15">
       <c r="A5" t="s">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="I5" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="7">
-        <v>0.51921079958463134</v>
-      </c>
-      <c r="L5" s="9"/>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="J5" s="10">
+        <v>0</v>
+      </c>
+      <c r="L5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15">
       <c r="A6" t="s">
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F6" t="s">
         <v>29</v>
@@ -5287,39 +7024,43 @@
         <v>47</v>
       </c>
       <c r="J6" s="7">
-        <v>0.58409785932721714</v>
-      </c>
-      <c r="L6" s="9"/>
-    </row>
-    <row r="7" spans="1:12">
+        <v>0</v>
+      </c>
+      <c r="L6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15">
       <c r="A7" t="s">
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="I7" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="7">
-        <v>0.63810483870967738</v>
-      </c>
-      <c r="L7" s="9"/>
+      <c r="J7" s="10">
+        <v>0</v>
+      </c>
+      <c r="L7" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
@@ -5329,13 +7070,13 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F8" t="s">
         <v>29</v>
@@ -5347,9 +7088,11 @@
         <v>47</v>
       </c>
       <c r="J8" s="7">
-        <v>0.66937119675456391</v>
-      </c>
-      <c r="L8" s="9"/>
+        <v>0.61875637104994907</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
@@ -5359,13 +7102,13 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F9" t="s">
         <v>29</v>
@@ -5377,11 +7120,11 @@
         <v>47</v>
       </c>
       <c r="J9" s="7">
-        <v>0.69979716024340777</v>
+        <v>0.51921079958463134</v>
       </c>
       <c r="L9" s="9"/>
     </row>
-    <row r="10" spans="1:12" ht="101.45">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -5389,29 +7132,27 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="I10" t="s">
         <v>47</v>
       </c>
-      <c r="J10" s="10">
-        <v>420</v>
-      </c>
-      <c r="L10" s="32" t="s">
-        <v>94</v>
-      </c>
+      <c r="J10" s="7">
+        <v>0.58409785932721714</v>
+      </c>
+      <c r="L10" s="9"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
@@ -5421,13 +7162,13 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F11" t="s">
         <v>29</v>
@@ -5439,11 +7180,9 @@
         <v>47</v>
       </c>
       <c r="J11" s="7">
-        <v>0</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>95</v>
-      </c>
+        <v>0.63810483870967738</v>
+      </c>
+      <c r="L11" s="9"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
@@ -5453,90 +7192,88 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="E12" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F12" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="I12" t="s">
         <v>47</v>
       </c>
-      <c r="J12" s="10">
-        <v>0</v>
+      <c r="J12" s="7">
+        <v>0.66937119675456391</v>
       </c>
       <c r="L12" s="9"/>
     </row>
-    <row r="13" spans="1:12" ht="43.5">
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E13" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" t="s">
+        <v>47</v>
+      </c>
+      <c r="J13" s="7">
+        <v>0.69979716024340777</v>
+      </c>
+      <c r="L13" s="9"/>
+    </row>
+    <row r="14" spans="1:12" ht="101.45">
+      <c r="A14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
         <v>91</v>
-      </c>
-      <c r="G13" t="s">
-        <v>92</v>
-      </c>
-      <c r="I13" t="s">
-        <v>96</v>
-      </c>
-      <c r="J13">
-        <v>42.5</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="43.5">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" t="s">
-        <v>83</v>
       </c>
       <c r="D14" t="s">
         <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F14" t="s">
-        <v>91</v>
-      </c>
-      <c r="G14" t="s">
-        <v>92</v>
+        <v>98</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>99</v>
       </c>
       <c r="I14" t="s">
-        <v>96</v>
-      </c>
-      <c r="J14">
-        <v>0.125</v>
+        <v>47</v>
+      </c>
+      <c r="J14" s="10">
+        <v>420</v>
       </c>
       <c r="L14" s="32" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -5547,13 +7284,13 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
         <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F15" t="s">
         <v>29</v>
@@ -5564,11 +7301,11 @@
       <c r="I15" t="s">
         <v>47</v>
       </c>
-      <c r="J15" s="20">
+      <c r="J15" s="7">
         <v>0</v>
       </c>
-      <c r="L15" t="s">
-        <v>99</v>
+      <c r="L15" s="9" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -5579,31 +7316,29 @@
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
         <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="I16" t="s">
         <v>47</v>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="10">
         <v>0</v>
       </c>
-      <c r="L16" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="L16" s="9"/>
+    </row>
+    <row r="17" spans="1:12" ht="43.5">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -5611,28 +7346,31 @@
         <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
         <v>27</v>
       </c>
       <c r="E17" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F17" t="s">
-        <v>29</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J17" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="L17" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+        <v>98</v>
+      </c>
+      <c r="G17" t="s">
+        <v>99</v>
+      </c>
+      <c r="I17" t="s">
+        <v>104</v>
+      </c>
+      <c r="J17">
+        <v>42.5</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="43.5">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -5640,42 +7378,45 @@
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
         <v>27</v>
       </c>
       <c r="E18" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J18" s="7">
-        <v>0.8</v>
-      </c>
-      <c r="L18" t="s">
-        <v>100</v>
+        <v>98</v>
+      </c>
+      <c r="G18" t="s">
+        <v>99</v>
+      </c>
+      <c r="I18" t="s">
+        <v>104</v>
+      </c>
+      <c r="J18">
+        <v>0.125</v>
+      </c>
+      <c r="L18" s="32" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
         <v>27</v>
       </c>
       <c r="E19" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F19" t="s">
         <v>29</v>
@@ -5683,11 +7424,191 @@
       <c r="G19" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J19" s="7">
+      <c r="I19" t="s">
+        <v>47</v>
+      </c>
+      <c r="J19" s="20">
+        <v>0</v>
+      </c>
+      <c r="L19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" t="s">
+        <v>47</v>
+      </c>
+      <c r="J20" s="20">
+        <v>0</v>
+      </c>
+      <c r="L20" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J21" s="7">
         <v>0.8</v>
       </c>
-      <c r="L19" t="s">
-        <v>100</v>
+      <c r="L21" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F22" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J22" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="L22" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" t="s">
+        <v>97</v>
+      </c>
+      <c r="F23" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J23" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="L23" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15">
+      <c r="A24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" t="s">
+        <v>97</v>
+      </c>
+      <c r="F24" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J24" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="L24" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15">
+      <c r="A25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" t="s">
+        <v>91</v>
+      </c>
+      <c r="D25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25" t="s">
+        <v>29</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J25" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="L25" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -5787,30 +7708,30 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="4" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F4" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G4" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B5" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$2:$A$980, B$1,  'Country Extraction'!$B$2:$B$980, "All",  'Country Extraction'!$C$2:$C$980, $A5) = 0, "Missing", "Complete")</f>
@@ -5839,7 +7760,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B6" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$2:$A$980, B$1,  'Country Extraction'!$B$2:$B$980, "All",  'Country Extraction'!$C$2:$C$980, $A6) = 0, "Missing", "Complete")</f>
@@ -5868,226 +7789,226 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F7" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G7" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F8" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G8" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="H9" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" t="s">
         <v>111</v>
-      </c>
-      <c r="B10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" t="s">
-        <v>102</v>
       </c>
       <c r="E10" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$1:$A$995, F$1, 'Country Extraction'!$B$1:$B$995, "&lt;&gt;All", 'Country Extraction'!$C$1:$C$995, $A10, 'Country Extraction'!$H$1:$H$995, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="F10" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G10" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$1:$A$995, H$1, 'Country Extraction'!$B$1:$B$995, "&lt;&gt;All", 'Country Extraction'!$C$1:$C$995, $A10, 'Country Extraction'!$H$1:$H$995, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E11" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$1:$A$995, F$1, 'Country Extraction'!$B$1:$B$995, "&lt;&gt;All", 'Country Extraction'!$C$1:$C$995, $A11, 'Country Extraction'!$H$1:$H$995, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="F11" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G11" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="H11" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F12" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G12" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F13" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G13" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="H13" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E14" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F14" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G14" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="H14" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C15" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$1:$A$995, D$1, 'Country Extraction'!$B$1:$B$995, "&lt;&gt;All", 'Country Extraction'!$C$1:$C$995, $A15, 'Country Extraction'!$H$1:$H$995, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E15" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$1:$A$995, F$1, 'Country Extraction'!$B$1:$B$995, "&lt;&gt;All", 'Country Extraction'!$C$1:$C$995, $A15, 'Country Extraction'!$H$1:$H$995, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
         <v>Missing</v>
       </c>
       <c r="F15" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G15" t="str">
         <f>IF(COUNTIFS('Country Extraction'!$A$1:$A$995, H$1, 'Country Extraction'!$B$1:$B$995, "&lt;&gt;All", 'Country Extraction'!$C$1:$C$995, $A15, 'Country Extraction'!$H$1:$H$995, "&lt;&gt;") &lt; 5, "Missing", "Complete")</f>
@@ -6158,19 +8079,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="32.25" customHeight="1">
@@ -6181,16 +8102,16 @@
         <v>37</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E3" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G3" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6201,13 +8122,13 @@
         <v>38</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G4" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6218,13 +8139,13 @@
         <v>39</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G5" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6235,13 +8156,13 @@
         <v>40</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G6" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6252,115 +8173,115 @@
         <v>41</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G7" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E8" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G8" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s">
         <v>37</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G9" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E10" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G10" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B11" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G11" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B12" t="s">
         <v>40</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E12" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G12" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B13" t="s">
         <v>41</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E13" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G13" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6368,16 +8289,16 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E14" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G14" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6388,13 +8309,13 @@
         <v>37</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E15" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G15" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -6405,13 +8326,13 @@
         <v>38</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E16" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G16" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -6422,13 +8343,13 @@
         <v>39</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E17" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G17" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -6439,13 +8360,13 @@
         <v>40</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E18" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G18" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -6456,13 +8377,13 @@
         <v>41</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E19" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G19" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.95">
@@ -6470,19 +8391,19 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G20" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -6493,16 +8414,16 @@
         <v>37</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G21" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -6513,13 +8434,13 @@
         <v>38</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G22" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -6530,13 +8451,13 @@
         <v>39</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G23" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -6547,13 +8468,13 @@
         <v>40</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G24" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -6564,115 +8485,115 @@
         <v>41</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G25" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G26" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G27" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B28" t="s">
         <v>38</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G28" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B29" t="s">
         <v>39</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G29" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B30" t="s">
         <v>40</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G30" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B31" t="s">
         <v>41</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G31" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -6680,16 +8601,16 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G32" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -6700,13 +8621,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G33" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -6717,13 +8638,13 @@
         <v>38</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G34" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -6734,13 +8655,13 @@
         <v>39</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G35" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -6751,13 +8672,13 @@
         <v>40</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G36" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -6768,13 +8689,13 @@
         <v>41</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G37" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -6782,13 +8703,13 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -6799,10 +8720,10 @@
         <v>37</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -6813,10 +8734,10 @@
         <v>38</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -6827,10 +8748,10 @@
         <v>39</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -6841,10 +8762,10 @@
         <v>40</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -6855,94 +8776,94 @@
         <v>41</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B44" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B45" t="s">
         <v>37</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G45" s="14" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B46" t="s">
         <v>38</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B47" t="s">
         <v>39</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B48" t="s">
         <v>40</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B49" t="s">
         <v>41</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -6950,13 +8871,13 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -6967,10 +8888,10 @@
         <v>37</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G51" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -6981,10 +8902,10 @@
         <v>38</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G52" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -6995,10 +8916,10 @@
         <v>39</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G53" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -7009,10 +8930,10 @@
         <v>40</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G54" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -7023,10 +8944,10 @@
         <v>41</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G55" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -7034,13 +8955,13 @@
         <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C56" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="G56" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="43.5">
@@ -7051,10 +8972,10 @@
         <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15.95">
@@ -7065,10 +8986,10 @@
         <v>38</v>
       </c>
       <c r="C58" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="J58" s="12" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="15.95">
@@ -7079,7 +9000,7 @@
         <v>39</v>
       </c>
       <c r="C59" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="J59" s="12"/>
     </row>
@@ -7091,7 +9012,7 @@
         <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -7102,76 +9023,76 @@
         <v>41</v>
       </c>
       <c r="C61" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B62" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C62" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="G62" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B63" t="s">
         <v>37</v>
       </c>
       <c r="C63" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B64" t="s">
         <v>38</v>
       </c>
       <c r="C64" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B65" t="s">
         <v>39</v>
       </c>
       <c r="C65" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B66" t="s">
         <v>40</v>
       </c>
       <c r="C66" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B67" t="s">
         <v>41</v>
       </c>
       <c r="C67" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -7179,13 +9100,13 @@
         <v>3</v>
       </c>
       <c r="B68" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C68" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="G68" s="15" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -7196,7 +9117,7 @@
         <v>37</v>
       </c>
       <c r="C69" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -7207,7 +9128,7 @@
         <v>38</v>
       </c>
       <c r="C70" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -7218,7 +9139,7 @@
         <v>39</v>
       </c>
       <c r="C71" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -7229,7 +9150,7 @@
         <v>40</v>
       </c>
       <c r="C72" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -7240,7 +9161,7 @@
         <v>41</v>
       </c>
       <c r="C73" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="29.45">
@@ -7248,36 +9169,36 @@
         <v>1</v>
       </c>
       <c r="B74" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C74" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D74" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="G74" s="12" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="J74" s="14" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B75" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C75" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D75" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="J75" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -7285,13 +9206,13 @@
         <v>3</v>
       </c>
       <c r="B76" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C76" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D76" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -7367,10 +9288,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C3" t="str">
         <f>IF(COUNTIFS('Vehicle Extraction'!$A$2:$A$904, C$1,  'Vehicle Extraction'!$B$2:$B$904, $A3) = 0, "Missing", "Complete")</f>
@@ -7383,10 +9304,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C4" t="str">
         <f>IF(COUNTIFS('Vehicle Extraction'!$A$2:$A$904, C$1,  'Vehicle Extraction'!$B$2:$B$904, $A4) = 0, "Missing", "Complete")</f>
@@ -7455,28 +9376,28 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="E2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G2" s="26">
         <v>3.25</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -7484,28 +9405,28 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="E3">
         <v>2021</v>
       </c>
       <c r="F3" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G3">
         <v>4.4000000000000004</v>
       </c>
       <c r="H3" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -7513,28 +9434,28 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="E4">
         <v>2012</v>
       </c>
       <c r="F4" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G4">
         <v>4.2</v>
       </c>
       <c r="H4" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -7542,28 +9463,28 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C5" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D5" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="E5">
         <v>2013</v>
       </c>
       <c r="F5" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G5">
         <v>1.67</v>
       </c>
       <c r="H5" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -7571,28 +9492,28 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D6" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="E6">
         <v>2013</v>
       </c>
       <c r="F6" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G6">
         <v>1.67</v>
       </c>
       <c r="H6" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -7664,7 +9585,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="26" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -7677,59 +9598,59 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="26" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D3" s="26">
         <v>2018</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F3" s="26">
         <v>4.3</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="I3" s="23"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="26" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="D4" s="26">
         <v>2015</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="F4" s="26">
         <v>6</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H4" s="23"/>
       <c r="I4" s="23"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="26" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B5" s="26"/>
       <c r="C5" s="26"/>
@@ -7742,18 +9663,18 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="26" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="G6" s="26"/>
       <c r="H6" s="23"/>
@@ -7761,18 +9682,18 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="26" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
       <c r="E7" s="26" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="G7" s="26"/>
       <c r="H7" s="23"/>
@@ -7780,22 +9701,22 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="26" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
       <c r="E8" s="26" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="23" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="I8" s="23"/>
     </row>
@@ -7874,6 +9795,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="19a3940c-c740-4699-845a-46837f99845a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100447C4EFE3BCDC24F9D43FB479AF7E97A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="710ccc9eba0c031f4d3c8297a7da4be2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="19a3940c-c740-4699-845a-46837f99845a" xmlns:ns3="539a68f6-d0ac-4a73-9041-e1fa437c4cee" xmlns:ns4="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a67399e28ae6312d8947be2cafff42c1" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="19a3940c-c740-4699-845a-46837f99845a"/>
@@ -8127,17 +10059,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ab06a5aa-8e31-4bdb-9b13-38c58a92ec8a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="19a3940c-c740-4699-845a-46837f99845a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -8148,11 +10069,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{302FEEF7-88D6-41D4-B999-EFF8511D95B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4173999B-2FEB-4E5B-A6C7-6E33DD5EA2F7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4173999B-2FEB-4E5B-A6C7-6E33DD5EA2F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{302FEEF7-88D6-41D4-B999-EFF8511D95B1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
